--- a/project_list.xlsx
+++ b/project_list.xlsx
@@ -4481,7 +4481,7 @@
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="7" max="7" width="15.8" customWidth="1"/>
     <col min="8" max="8" width="18.7" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4530,7 +4530,6 @@
       <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E2"/>
       <c r="I2" t="s">
         <v>14</v>
       </c>

--- a/project_list.xlsx
+++ b/project_list.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3484" uniqueCount="1211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3103" uniqueCount="1152">
   <si>
     <t>项目名称</t>
   </si>
@@ -89,70 +89,70 @@
     <t>1400</t>
   </si>
   <si>
+    <t>Australia - AUS AC ergy Joel 1000MWh</t>
+  </si>
+  <si>
+    <t>-36.619838,143.258422</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>Australia - AUS Beryl 200MWh</t>
+  </si>
+  <si>
+    <t>-31.324162,146.465953</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Australia - AUS FRV Axedale 100MWh</t>
+  </si>
+  <si>
+    <t>-36.787213,144.502109</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Australia - AUS NEO 800MWh</t>
+  </si>
+  <si>
+    <t>-35.666962,147.036484</t>
+  </si>
+  <si>
+    <t>800</t>
+  </si>
+  <si>
+    <t>Australia - BrightNight Mortlake 1.4 GWh</t>
+  </si>
+  <si>
+    <t>-38.049389,142.723333</t>
+  </si>
+  <si>
+    <t>Australia - EMMS Cooba Solar Farm 880MWh</t>
+  </si>
+  <si>
+    <t>-36.638062,144.770266</t>
+  </si>
+  <si>
+    <t>880</t>
+  </si>
+  <si>
+    <t>Australia-Accture Tronox Cooljarloo 200MW 800MWh BESS Project</t>
+  </si>
+  <si>
+    <t>-30.648611,115.457778</t>
+  </si>
+  <si>
+    <t>Australia-AUS LSbp Goulburn River Standalone BESS</t>
+  </si>
+  <si>
+    <t>-32.293889,150.104222</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>Australia - AUS AC ergy Joel 1000MWh</t>
-  </si>
-  <si>
-    <t>-36.619838,143.258422</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>Australia - AUS Beryl 200MWh</t>
-  </si>
-  <si>
-    <t>-31.324162,146.465953</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>Australia - AUS FRV Axedale 100MWh</t>
-  </si>
-  <si>
-    <t>-36.787213,144.502109</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>Australia - AUS NEO 800MWh</t>
-  </si>
-  <si>
-    <t>-35.666962,147.036484</t>
-  </si>
-  <si>
-    <t>800</t>
-  </si>
-  <si>
-    <t>Australia - BrightNight Mortlake 1.4 GWh</t>
-  </si>
-  <si>
-    <t>-38.049389,142.723333</t>
-  </si>
-  <si>
-    <t>Australia - EMMS Cooba Solar Farm 880MWh</t>
-  </si>
-  <si>
-    <t>-36.638062,144.770266</t>
-  </si>
-  <si>
-    <t>880</t>
-  </si>
-  <si>
-    <t>Australia-Accture Tronox Cooljarloo 200MW 800MWh BESS Project</t>
-  </si>
-  <si>
-    <t>-30.648611,115.457778</t>
-  </si>
-  <si>
-    <t>Australia-AUS LSbp Goulburn River Standalone BESS</t>
-  </si>
-  <si>
-    <t>-32.293889,150.104222</t>
   </si>
   <si>
     <t>Australia-AUS LSbp Sandy Creek BESS</t>
@@ -3662,231 +3662,6 @@
   <si>
     <t>-37.59901, -72.53589</t>
   </si>
-  <si>
-    <t>Bahia Blanca Warehouse</t>
-  </si>
-  <si>
-    <t>-38.71831, -62.26634</t>
-  </si>
-  <si>
-    <t>Generator*1</t>
-  </si>
-  <si>
-    <t>Operating</t>
-  </si>
-  <si>
-    <t>Warehouse</t>
-  </si>
-  <si>
-    <t>Merida Warehouse</t>
-  </si>
-  <si>
-    <t>20.96737, -89.59258</t>
-  </si>
-  <si>
-    <t>Gearbox*1
-Generator*1</t>
-  </si>
-  <si>
-    <t>P-1551 Libmanan blade yard</t>
-  </si>
-  <si>
-    <t>Blade*3</t>
-  </si>
-  <si>
-    <t>P-1259 Monsoon业主库</t>
-  </si>
-  <si>
-    <t>Blade*5（客户物权）
-Gearbox*1（客户物权）
-Generator*1（客户物权）
-Main Bearing*1
-Pitch Bearing*3
-Converter*1（客户物权）</t>
-  </si>
-  <si>
-    <t>Philippines NDC</t>
-  </si>
-  <si>
-    <t>13.94503, 121.1312</t>
-  </si>
-  <si>
-    <t>预计5-6月落地</t>
-  </si>
-  <si>
-    <t>under construction</t>
-  </si>
-  <si>
-    <t>德农阳光</t>
-  </si>
-  <si>
-    <t>Vienam</t>
-  </si>
-  <si>
-    <t>Blade*2(156)</t>
-  </si>
-  <si>
-    <t>P-0583华电得乐blade yard</t>
-  </si>
-  <si>
-    <t>Blade*3(141)</t>
-  </si>
-  <si>
-    <t>Vienam major component NDC</t>
-  </si>
-  <si>
-    <t>10.55476, 106.40525</t>
-  </si>
-  <si>
-    <t>Blade*2(156)
-Gearbox*9
-Generator*2
-Pitch Bearing*18
-Pad-mounted transformer *3
-Converter*5</t>
-  </si>
-  <si>
-    <t>Kazakhstan major component NDC</t>
-  </si>
-  <si>
-    <t>43.23797, 76.88286</t>
-  </si>
-  <si>
-    <t>Gearbox*1(121/2.5)+1(141/3.2)+1(156/4.8)+1(200/6.25)
-Generator*1(121/2.5)+1(141/3.2)+1(156/4.8)+1(200/6.25)
-Pitch Bearing*3(121/2.5)+3(141/3.2)+3(156/4.8)+6(200/6.25)
-Converter*1(121/2.5)+1(141/3.2)+1(156/4.8)+1(200/6.25)
-Pad-mounted transformer *1(156/4.8)</t>
-  </si>
-  <si>
-    <t>P-0459 札纳塔斯一期blade yard</t>
-  </si>
-  <si>
-    <t>blade*3(121/2.5)</t>
-  </si>
-  <si>
-    <t>P-0783 Universal East blade yard</t>
-  </si>
-  <si>
-    <t>blade*3(141/3.2)</t>
-  </si>
-  <si>
-    <t>P-0980 札纳塔斯二期blade yard</t>
-  </si>
-  <si>
-    <t>blade*3(156/4.8)</t>
-  </si>
-  <si>
-    <t>P-1450 Universal Mezgilder Qushteri blade yard</t>
-  </si>
-  <si>
-    <t>blade*3(200/6.25)</t>
-  </si>
-  <si>
-    <t>P-1287 Dzhankeldy project warehouse</t>
-  </si>
-  <si>
-    <t>blade*2(171/6.5)
-Pad-mounted transformer *2(171/6.5)</t>
-  </si>
-  <si>
-    <t>P-1288 Bash project warehouse</t>
-  </si>
-  <si>
-    <t>P-1385 Nukus project warehouse</t>
-  </si>
-  <si>
-    <t>blade*2(171/6.5)
-Pad-mounted transformer *1(171/6.5)</t>
-  </si>
-  <si>
-    <t>Uzbekistan NDC</t>
-  </si>
-  <si>
-    <t>41.29822, 69.23852</t>
-  </si>
-  <si>
-    <t>Gearbox*1(171/6.5)
-Main Bearing*1(171/6.5与200/6.25共用）
-Pitch Bearing*3(171/6.5与200/6.25共用）</t>
-  </si>
-  <si>
-    <t>CWS Dijon Warehouse</t>
-  </si>
-  <si>
-    <t>47.34888, 5.06474</t>
-  </si>
-  <si>
-    <t>Generator*1（131/2.5）</t>
-  </si>
-  <si>
-    <t>Colmar Harbour</t>
-  </si>
-  <si>
-    <t>48.08036, 7.37604</t>
-  </si>
-  <si>
-    <t>Blade*3
-Gearbox*1（131/2.5）</t>
-  </si>
-  <si>
-    <t>P-0152 MOZURA project blade yard</t>
-  </si>
-  <si>
-    <t>Blade*1</t>
-  </si>
-  <si>
-    <t>P-0998 ACWA 240MW project warehouse</t>
-  </si>
-  <si>
-    <t>Blade*3
-Gearbox*1(171/6.5)
-Generator*1(171/6.5)
-Pitch Bearing*3(171/6.5）
-Pad-mounted transformer *1(171/6.5)
-Converter*1(171/6.5)</t>
-  </si>
-  <si>
-    <t>P-1349 AMEA 500MW project warehouse</t>
-  </si>
-  <si>
-    <t>Blade*3（客户物权）
-Gearbox*2（客户物权）
-Generator*1（客户物权）
-Main Bearing*1（客户物权）
-Pitch Bearing*3
-Pad-mounted transformer *1(客户物权）
-Converter*1（客户物权）
-Switchgear*1（客户物权）</t>
-  </si>
-  <si>
-    <t>P-1334 Dakhla project warehouse</t>
-  </si>
-  <si>
-    <t>Blade*3(171/6.5)
-Gearbox*1(171/6.5)
-Generator*1(171/6.5)
-Pitch Bearing*6(171/6.5）
-Pad-mounted transformer *1(171/6.5)
-Converter*1(171/6.5)
-Switchgear*1(171/6.5)</t>
-  </si>
-  <si>
-    <t>P-1309 NEOM project blade yard</t>
-  </si>
-  <si>
-    <r>
-      <t>Blade*6+1(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>报废）</t>
-    </r>
-  </si>
 </sst>
 </file>
 
@@ -3898,7 +3673,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -4122,11 +3897,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Cambria"/>
@@ -4139,7 +3909,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4167,12 +3937,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF9E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFEEF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4363,7 +4127,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -4517,21 +4281,6 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -4654,7 +4403,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4666,120 +4415,120 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4909,33 +4658,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="13" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5414,7 +5136,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J498"/>
+  <dimension ref="A1:J474"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="46.3666666666667" style="1" customWidth="1"/>
@@ -5493,9 +5215,7 @@
       <c r="D3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E3" s="1"/>
       <c r="I3" s="1" t="s">
         <v>14</v>
       </c>
@@ -5505,20 +5225,18 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E4" s="1"/>
       <c r="I4" s="1" t="s">
         <v>14</v>
       </c>
@@ -5528,20 +5246,18 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E5" s="1"/>
       <c r="I5" s="1" t="s">
         <v>14</v>
       </c>
@@ -5551,20 +5267,18 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E6" s="1"/>
       <c r="I6" s="1" t="s">
         <v>14</v>
       </c>
@@ -5574,20 +5288,18 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="E7" s="1"/>
       <c r="I7" s="1" t="s">
         <v>14</v>
       </c>
@@ -5597,10 +5309,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>18</v>
@@ -5608,9 +5320,7 @@
       <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E8" s="1"/>
       <c r="I8" s="1" t="s">
         <v>14</v>
       </c>
@@ -5620,20 +5330,18 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E9" s="1"/>
       <c r="I9" s="1" t="s">
         <v>14</v>
       </c>
@@ -5643,20 +5351,18 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="E10" s="1"/>
       <c r="I10" s="1" t="s">
         <v>14</v>
       </c>
@@ -5666,20 +5372,18 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E11" s="1"/>
       <c r="I11" s="1" t="s">
         <v>14</v>
       </c>
@@ -5698,11 +5402,9 @@
         <v>18</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E12" s="1"/>
       <c r="I12" s="1" t="s">
         <v>14</v>
       </c>
@@ -5723,9 +5425,7 @@
       <c r="D13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E13" s="1"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -5746,9 +5446,7 @@
       <c r="D14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E14" s="1"/>
       <c r="I14" s="1" t="s">
         <v>14</v>
       </c>
@@ -5767,11 +5465,9 @@
         <v>52</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E15" s="1"/>
       <c r="I15" s="1" t="s">
         <v>14</v>
       </c>
@@ -5792,9 +5488,7 @@
       <c r="D16" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E16" s="1"/>
       <c r="I16" s="1" t="s">
         <v>14</v>
       </c>
@@ -5815,9 +5509,7 @@
       <c r="D17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E17" s="1"/>
       <c r="I17" s="1" t="s">
         <v>14</v>
       </c>
@@ -5838,9 +5530,7 @@
       <c r="D18" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E18" s="1"/>
       <c r="I18" s="1" t="s">
         <v>14</v>
       </c>
@@ -5861,9 +5551,7 @@
       <c r="D19" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E19" s="1"/>
       <c r="I19" s="1" t="s">
         <v>14</v>
       </c>
@@ -5884,9 +5572,7 @@
       <c r="D20" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E20" s="1"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -5907,9 +5593,7 @@
       <c r="D21" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E21" s="1"/>
       <c r="I21" s="1" t="s">
         <v>14</v>
       </c>
@@ -5930,9 +5614,7 @@
       <c r="D22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E22" s="1"/>
       <c r="I22" s="1" t="s">
         <v>14</v>
       </c>
@@ -5953,9 +5635,7 @@
       <c r="D23" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E23" s="1"/>
       <c r="I23" s="1" t="s">
         <v>14</v>
       </c>
@@ -5974,11 +5654,9 @@
         <v>78</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E24" s="1"/>
       <c r="I24" s="1" t="s">
         <v>14</v>
       </c>
@@ -5999,9 +5677,7 @@
       <c r="D25" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E25" s="1"/>
       <c r="I25" s="1" t="s">
         <v>14</v>
       </c>
@@ -6022,9 +5698,7 @@
       <c r="D26" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E26" s="1"/>
       <c r="I26" s="1" t="s">
         <v>14</v>
       </c>
@@ -6045,9 +5719,7 @@
       <c r="D27" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E27" s="1"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -6066,11 +5738,9 @@
         <v>78</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E28" s="1"/>
       <c r="I28" s="1" t="s">
         <v>93</v>
       </c>
@@ -6091,9 +5761,7 @@
       <c r="D29" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E29" s="1"/>
       <c r="I29" s="1" t="s">
         <v>14</v>
       </c>
@@ -6114,9 +5782,7 @@
       <c r="D30" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E30" s="1"/>
       <c r="I30" s="1" t="s">
         <v>14</v>
       </c>
@@ -6135,11 +5801,9 @@
         <v>78</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E31" s="1"/>
       <c r="I31" s="1" t="s">
         <v>14</v>
       </c>
@@ -6158,11 +5822,9 @@
         <v>78</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E32" s="1"/>
       <c r="I32" s="1" t="s">
         <v>14</v>
       </c>
@@ -6181,11 +5843,9 @@
         <v>78</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E33" s="1"/>
       <c r="I33" s="1" t="s">
         <v>14</v>
       </c>
@@ -6204,11 +5864,9 @@
         <v>78</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E34" s="1"/>
       <c r="I34" s="1" t="s">
         <v>14</v>
       </c>
@@ -6227,11 +5885,9 @@
         <v>78</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E35" s="1"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -6252,9 +5908,7 @@
       <c r="D36" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E36" s="1"/>
       <c r="I36" s="1" t="s">
         <v>14</v>
       </c>
@@ -6275,9 +5929,7 @@
       <c r="D37" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E37" s="1"/>
       <c r="I37" s="1" t="s">
         <v>14</v>
       </c>
@@ -6296,11 +5948,9 @@
         <v>78</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E38" s="1"/>
       <c r="I38" s="1" t="s">
         <v>14</v>
       </c>
@@ -6319,11 +5969,9 @@
         <v>78</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E39" s="1"/>
       <c r="I39" s="1" t="s">
         <v>14</v>
       </c>
@@ -6342,11 +5990,9 @@
         <v>78</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E40" s="1"/>
       <c r="I40" s="1" t="s">
         <v>14</v>
       </c>
@@ -6367,9 +6013,7 @@
       <c r="D41" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E41" s="1"/>
       <c r="I41" s="1" t="s">
         <v>14</v>
       </c>
@@ -6388,11 +6032,9 @@
         <v>124</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E42" s="1"/>
       <c r="I42" s="1" t="s">
         <v>14</v>
       </c>
@@ -6411,11 +6053,9 @@
         <v>124</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E43" s="1"/>
       <c r="I43" s="1" t="s">
         <v>14</v>
       </c>
@@ -6434,11 +6074,9 @@
         <v>124</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E44" s="1"/>
       <c r="I44" s="1" t="s">
         <v>14</v>
       </c>
@@ -6457,11 +6095,9 @@
         <v>124</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E45" s="1"/>
       <c r="I45" s="1" t="s">
         <v>14</v>
       </c>
@@ -6482,9 +6118,7 @@
       <c r="D46" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E46" s="1"/>
       <c r="I46" s="1" t="s">
         <v>14</v>
       </c>
@@ -6505,9 +6139,7 @@
       <c r="D47" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E47" s="1"/>
       <c r="I47" s="1" t="s">
         <v>14</v>
       </c>
@@ -6528,9 +6160,7 @@
       <c r="D48" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E48" s="1"/>
       <c r="I48" s="1" t="s">
         <v>14</v>
       </c>
@@ -6549,11 +6179,9 @@
         <v>133</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E49" s="1"/>
       <c r="I49" s="1" t="s">
         <v>14</v>
       </c>
@@ -6574,9 +6202,7 @@
       <c r="D50" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E50" s="1"/>
       <c r="I50" s="1" t="s">
         <v>14</v>
       </c>
@@ -6597,9 +6223,7 @@
       <c r="D51" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E51" s="1"/>
       <c r="I51" s="1" t="s">
         <v>14</v>
       </c>
@@ -6618,11 +6242,9 @@
         <v>133</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E52" s="1"/>
       <c r="I52" s="1" t="s">
         <v>14</v>
       </c>
@@ -6643,9 +6265,7 @@
       <c r="D53" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E53" s="1"/>
       <c r="I53" s="1" t="s">
         <v>14</v>
       </c>
@@ -6666,9 +6286,7 @@
       <c r="D54" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E54" s="1"/>
       <c r="I54" s="1" t="s">
         <v>14</v>
       </c>
@@ -6687,11 +6305,9 @@
         <v>133</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E55" s="1"/>
       <c r="I55" s="1" t="s">
         <v>14</v>
       </c>
@@ -6712,9 +6328,7 @@
       <c r="D56" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E56" s="1"/>
       <c r="I56" s="1" t="s">
         <v>14</v>
       </c>
@@ -6735,9 +6349,7 @@
       <c r="D57" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E57" s="1"/>
       <c r="I57" s="1" t="s">
         <v>14</v>
       </c>
@@ -6756,11 +6368,9 @@
         <v>133</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E58" s="1"/>
       <c r="I58" s="1" t="s">
         <v>14</v>
       </c>
@@ -6779,11 +6389,9 @@
         <v>153</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E59" s="1"/>
       <c r="I59" s="1" t="s">
         <v>14</v>
       </c>
@@ -6802,11 +6410,9 @@
         <v>156</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E60" s="1"/>
       <c r="I60" s="1" t="s">
         <v>14</v>
       </c>
@@ -6825,11 +6431,9 @@
         <v>156</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E61" s="1"/>
       <c r="I61" s="1" t="s">
         <v>14</v>
       </c>
@@ -6850,9 +6454,7 @@
       <c r="D62" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E62" s="1"/>
       <c r="I62" s="1" t="s">
         <v>14</v>
       </c>
@@ -6871,11 +6473,9 @@
         <v>156</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E63" s="1"/>
       <c r="I63" s="1" t="s">
         <v>14</v>
       </c>
@@ -6896,9 +6496,7 @@
       <c r="D64" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E64" s="1"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -6919,9 +6517,7 @@
       <c r="D65" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E65" s="1"/>
       <c r="I65" s="1" t="s">
         <v>14</v>
       </c>
@@ -6942,9 +6538,7 @@
       <c r="D66" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E66" s="1"/>
       <c r="I66" s="1" t="s">
         <v>14</v>
       </c>
@@ -6965,9 +6559,7 @@
       <c r="D67" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E67" s="1"/>
       <c r="I67" s="1" t="s">
         <v>14</v>
       </c>
@@ -6986,11 +6578,9 @@
         <v>175</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E68" s="1"/>
       <c r="I68" s="1" t="s">
         <v>14</v>
       </c>
@@ -7009,11 +6599,9 @@
         <v>175</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E69" s="1"/>
       <c r="I69" s="1" t="s">
         <v>14</v>
       </c>
@@ -7034,9 +6622,7 @@
       <c r="D70" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E70" s="1"/>
       <c r="I70" s="1" t="s">
         <v>14</v>
       </c>
@@ -7057,9 +6643,7 @@
       <c r="D71" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E71" s="1"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -7080,9 +6664,7 @@
       <c r="D72" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E72" s="1"/>
       <c r="I72" s="1" t="s">
         <v>14</v>
       </c>
@@ -7103,9 +6685,7 @@
       <c r="D73" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E73" s="1"/>
       <c r="I73" s="1" t="s">
         <v>14</v>
       </c>
@@ -7124,11 +6704,9 @@
         <v>189</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E74" s="1"/>
       <c r="I74" s="1" t="s">
         <v>14</v>
       </c>
@@ -7149,9 +6727,7 @@
       <c r="D75" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E75" s="1"/>
       <c r="I75" s="1" t="s">
         <v>14</v>
       </c>
@@ -7172,9 +6748,7 @@
       <c r="D76" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E76" s="1"/>
       <c r="I76" s="1" t="s">
         <v>14</v>
       </c>
@@ -7195,9 +6769,7 @@
       <c r="D77" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E77" s="1"/>
       <c r="I77" s="1" t="s">
         <v>14</v>
       </c>
@@ -7218,9 +6790,7 @@
       <c r="D78" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E78" s="1"/>
       <c r="I78" s="1" t="s">
         <v>14</v>
       </c>
@@ -7239,11 +6809,9 @@
         <v>189</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E79" s="1"/>
       <c r="I79" s="1" t="s">
         <v>14</v>
       </c>
@@ -7264,9 +6832,7 @@
       <c r="D80" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E80" s="1"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -7285,11 +6851,9 @@
         <v>189</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E81" s="1"/>
       <c r="I81" s="1" t="s">
         <v>14</v>
       </c>
@@ -7310,9 +6874,7 @@
       <c r="D82" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E82" s="1"/>
       <c r="I82" s="1" t="s">
         <v>14</v>
       </c>
@@ -7331,11 +6893,9 @@
         <v>189</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E83" s="1"/>
       <c r="I83" s="1" t="s">
         <v>14</v>
       </c>
@@ -7354,11 +6914,9 @@
         <v>189</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E84" s="1"/>
       <c r="I84" s="1" t="s">
         <v>14</v>
       </c>
@@ -7379,9 +6937,7 @@
       <c r="D85" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="E85" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E85" s="1"/>
       <c r="I85" s="1" t="s">
         <v>14</v>
       </c>
@@ -7402,9 +6958,7 @@
       <c r="D86" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E86" s="1"/>
       <c r="I86" s="1" t="s">
         <v>14</v>
       </c>
@@ -7425,9 +6979,7 @@
       <c r="D87" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E87" s="1"/>
       <c r="I87" s="1" t="s">
         <v>14</v>
       </c>
@@ -7448,9 +7000,7 @@
       <c r="D88" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E88" s="1"/>
       <c r="I88" s="1" t="s">
         <v>14</v>
       </c>
@@ -7471,9 +7021,7 @@
       <c r="D89" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E89" s="1"/>
       <c r="I89" s="1" t="s">
         <v>14</v>
       </c>
@@ -7492,11 +7040,9 @@
         <v>235</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E90" s="1"/>
       <c r="I90" s="1" t="s">
         <v>14</v>
       </c>
@@ -7515,11 +7061,9 @@
         <v>235</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E91" s="1"/>
       <c r="I91" s="1" t="s">
         <v>14</v>
       </c>
@@ -7538,11 +7082,9 @@
         <v>235</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E92" s="1"/>
       <c r="I92" s="1" t="s">
         <v>14</v>
       </c>
@@ -7561,11 +7103,9 @@
         <v>235</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E93" s="1"/>
       <c r="I93" s="1" t="s">
         <v>14</v>
       </c>
@@ -7584,11 +7124,9 @@
         <v>235</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E94" s="1"/>
       <c r="I94" s="1" t="s">
         <v>14</v>
       </c>
@@ -7607,11 +7145,9 @@
         <v>235</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E95" s="1"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -7630,11 +7166,9 @@
         <v>248</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E96" s="1"/>
       <c r="I96" s="1" t="s">
         <v>14</v>
       </c>
@@ -7653,11 +7187,9 @@
         <v>248</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E97" s="1"/>
       <c r="I97" s="1" t="s">
         <v>14</v>
       </c>
@@ -7678,9 +7210,7 @@
       <c r="D98" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="E98" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E98" s="1"/>
       <c r="I98" s="1" t="s">
         <v>14</v>
       </c>
@@ -7701,9 +7231,7 @@
       <c r="D99" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="E99" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E99" s="1"/>
       <c r="I99" s="1" t="s">
         <v>14</v>
       </c>
@@ -7722,11 +7250,9 @@
         <v>253</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E100" s="1"/>
       <c r="I100" s="1" t="s">
         <v>14</v>
       </c>
@@ -7745,11 +7271,9 @@
         <v>262</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E101" s="1"/>
       <c r="I101" s="1" t="s">
         <v>14</v>
       </c>
@@ -7768,11 +7292,9 @@
         <v>262</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E102" s="1"/>
       <c r="I102" s="1" t="s">
         <v>14</v>
       </c>
@@ -7793,9 +7315,7 @@
       <c r="D103" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E103" s="1"/>
       <c r="I103" s="1" t="s">
         <v>14</v>
       </c>
@@ -7814,11 +7334,9 @@
         <v>262</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E104" s="1"/>
       <c r="I104" s="1" t="s">
         <v>14</v>
       </c>
@@ -7837,11 +7355,9 @@
         <v>262</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E105" s="1"/>
       <c r="I105" s="1" t="s">
         <v>14</v>
       </c>
@@ -7862,9 +7378,7 @@
       <c r="D106" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E106" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E106" s="1"/>
       <c r="I106" s="1" t="s">
         <v>14</v>
       </c>
@@ -7885,9 +7399,7 @@
       <c r="D107" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="E107" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E107" s="1"/>
       <c r="I107" s="1" t="s">
         <v>14</v>
       </c>
@@ -7906,11 +7418,9 @@
         <v>12</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E108" s="1"/>
       <c r="I108" s="1" t="s">
         <v>14</v>
       </c>
@@ -7931,9 +7441,7 @@
       <c r="D109" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E109" s="1"/>
       <c r="I109" s="1" t="s">
         <v>14</v>
       </c>
@@ -7954,9 +7462,7 @@
       <c r="D110" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E110" s="1"/>
       <c r="I110" s="1" t="s">
         <v>14</v>
       </c>
@@ -7977,9 +7483,7 @@
       <c r="D111" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="E111" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E111" s="1"/>
       <c r="I111" s="1" t="s">
         <v>14</v>
       </c>
@@ -8000,9 +7504,7 @@
       <c r="D112" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E112" s="1"/>
       <c r="I112" s="1" t="s">
         <v>14</v>
       </c>
@@ -8023,9 +7525,7 @@
       <c r="D113" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E113" s="1"/>
       <c r="I113" s="1" t="s">
         <v>14</v>
       </c>
@@ -8044,11 +7544,9 @@
         <v>289</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="E114" s="1"/>
       <c r="I114" s="1" t="s">
         <v>14</v>
       </c>
@@ -8067,11 +7565,9 @@
         <v>292</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E115" s="1"/>
       <c r="I115" s="1" t="s">
         <v>14</v>
       </c>
@@ -8090,11 +7586,9 @@
         <v>295</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E116" s="1"/>
       <c r="I116" s="1" t="s">
         <v>14</v>
       </c>
@@ -8113,11 +7607,9 @@
         <v>295</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E117" s="1"/>
       <c r="I117" s="1" t="s">
         <v>14</v>
       </c>
@@ -8136,11 +7628,9 @@
         <v>295</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E118" s="1"/>
       <c r="I118" s="1" t="s">
         <v>14</v>
       </c>
@@ -8161,9 +7651,7 @@
       <c r="D119" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="E119" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E119" s="1"/>
       <c r="I119" s="1" t="s">
         <v>14</v>
       </c>
@@ -8182,11 +7670,9 @@
         <v>295</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E120" s="1"/>
       <c r="I120" s="1" t="s">
         <v>14</v>
       </c>
@@ -8207,9 +7693,7 @@
       <c r="D121" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="E121" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E121" s="1"/>
       <c r="I121" s="1" t="s">
         <v>14</v>
       </c>
@@ -8228,11 +7712,9 @@
         <v>295</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E122" s="1"/>
       <c r="I122" s="1" t="s">
         <v>14</v>
       </c>
@@ -8251,11 +7733,9 @@
         <v>295</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E123" s="1"/>
       <c r="I123" s="1" t="s">
         <v>14</v>
       </c>
@@ -8276,9 +7756,7 @@
       <c r="D124" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E124" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E124" s="1"/>
       <c r="I124" s="1" t="s">
         <v>14</v>
       </c>
@@ -8299,9 +7777,7 @@
       <c r="D125" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E125" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E125" s="1"/>
       <c r="I125" s="1" t="s">
         <v>14</v>
       </c>
@@ -8322,9 +7798,7 @@
       <c r="D126" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="E126" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E126" s="1"/>
       <c r="I126" s="1" t="s">
         <v>14</v>
       </c>
@@ -8345,9 +7819,7 @@
       <c r="D127" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="E127" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E127" s="1"/>
       <c r="I127" s="1" t="s">
         <v>14</v>
       </c>
@@ -8366,11 +7838,9 @@
         <v>321</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E128" s="1"/>
       <c r="I128" s="1" t="s">
         <v>14</v>
       </c>
@@ -8389,11 +7859,9 @@
         <v>321</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E129" s="1"/>
       <c r="I129" s="1" t="s">
         <v>14</v>
       </c>
@@ -8414,9 +7882,7 @@
       <c r="D130" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="E130" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E130" s="1"/>
       <c r="I130" s="1" t="s">
         <v>14</v>
       </c>
@@ -8437,9 +7903,7 @@
       <c r="D131" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="E131" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E131" s="1"/>
       <c r="I131" s="1" t="s">
         <v>14</v>
       </c>
@@ -8460,9 +7924,7 @@
       <c r="D132" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="E132" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E132" s="1"/>
       <c r="I132" s="1" t="s">
         <v>14</v>
       </c>
@@ -8483,9 +7945,7 @@
       <c r="D133" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="E133" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E133" s="1"/>
       <c r="I133" s="1" t="s">
         <v>14</v>
       </c>
@@ -8504,11 +7964,9 @@
         <v>321</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E134" s="1"/>
       <c r="I134" s="1" t="s">
         <v>14</v>
       </c>
@@ -8529,9 +7987,7 @@
       <c r="D135" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="E135" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E135" s="1"/>
       <c r="I135" s="1" t="s">
         <v>14</v>
       </c>
@@ -8552,9 +8008,7 @@
       <c r="D136" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E136" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E136" s="1"/>
       <c r="I136" s="1" t="s">
         <v>14</v>
       </c>
@@ -8575,9 +8029,7 @@
       <c r="D137" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="E137" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E137" s="1"/>
       <c r="I137" s="1" t="s">
         <v>14</v>
       </c>
@@ -8596,11 +8048,9 @@
         <v>346</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E138" s="1"/>
       <c r="I138" s="1" t="s">
         <v>14</v>
       </c>
@@ -8621,9 +8071,7 @@
       <c r="D139" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="E139" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E139" s="1"/>
       <c r="I139" s="1" t="s">
         <v>14</v>
       </c>
@@ -8644,9 +8092,7 @@
       <c r="D140" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="E140" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E140" s="1"/>
       <c r="I140" s="1" t="s">
         <v>14</v>
       </c>
@@ -8667,9 +8113,7 @@
       <c r="D141" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="E141" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E141" s="1"/>
       <c r="I141" s="1" t="s">
         <v>14</v>
       </c>
@@ -8690,9 +8134,7 @@
       <c r="D142" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E142" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E142" s="1"/>
       <c r="I142" s="1" t="s">
         <v>14</v>
       </c>
@@ -8713,9 +8155,7 @@
       <c r="D143" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E143" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E143" s="1"/>
       <c r="I143" s="1" t="s">
         <v>14</v>
       </c>
@@ -8736,9 +8176,7 @@
       <c r="D144" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="E144" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E144" s="1"/>
       <c r="I144" s="1" t="s">
         <v>14</v>
       </c>
@@ -8759,9 +8197,7 @@
       <c r="D145" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="E145" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E145" s="1"/>
       <c r="I145" s="1" t="s">
         <v>14</v>
       </c>
@@ -8782,9 +8218,7 @@
       <c r="D146" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="E146" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E146" s="1"/>
       <c r="I146" s="1" t="s">
         <v>93</v>
       </c>
@@ -8805,9 +8239,7 @@
       <c r="D147" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E147" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E147" s="1"/>
       <c r="I147" s="1" t="s">
         <v>93</v>
       </c>
@@ -8828,9 +8260,7 @@
       <c r="D148" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E148" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E148" s="1"/>
       <c r="I148" s="1" t="s">
         <v>93</v>
       </c>
@@ -8851,9 +8281,7 @@
       <c r="D149" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="E149" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E149" s="1"/>
       <c r="I149" s="1" t="s">
         <v>93</v>
       </c>
@@ -8874,9 +8302,7 @@
       <c r="D150" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E150" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E150" s="1"/>
       <c r="I150" s="1" t="s">
         <v>93</v>
       </c>
@@ -8897,9 +8323,7 @@
       <c r="D151" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="E151" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E151" s="1"/>
       <c r="I151" s="1" t="s">
         <v>93</v>
       </c>
@@ -8920,9 +8344,7 @@
       <c r="D152" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E152" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E152" s="1"/>
       <c r="I152" s="1" t="s">
         <v>93</v>
       </c>
@@ -8943,9 +8365,7 @@
       <c r="D153" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E153" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E153" s="1"/>
       <c r="I153" s="1" t="s">
         <v>93</v>
       </c>
@@ -8966,9 +8386,7 @@
       <c r="D154" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="E154" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E154" s="1"/>
       <c r="I154" s="1" t="s">
         <v>93</v>
       </c>
@@ -8989,9 +8407,7 @@
       <c r="D155" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E155" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E155" s="1"/>
       <c r="I155" s="1" t="s">
         <v>93</v>
       </c>
@@ -9012,9 +8428,7 @@
       <c r="D156" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="E156" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E156" s="1"/>
       <c r="I156" s="1" t="s">
         <v>93</v>
       </c>
@@ -9035,9 +8449,7 @@
       <c r="D157" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E157" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E157" s="1"/>
       <c r="I157" s="1" t="s">
         <v>93</v>
       </c>
@@ -9058,9 +8470,7 @@
       <c r="D158" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E158" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E158" s="1"/>
       <c r="I158" s="1" t="s">
         <v>93</v>
       </c>
@@ -9081,9 +8491,7 @@
       <c r="D159" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="E159" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E159" s="1"/>
       <c r="I159" s="1" t="s">
         <v>93</v>
       </c>
@@ -9104,9 +8512,7 @@
       <c r="D160" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E160" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E160" s="1"/>
       <c r="I160" s="1" t="s">
         <v>93</v>
       </c>
@@ -9127,9 +8533,7 @@
       <c r="D161" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E161" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E161" s="1"/>
       <c r="I161" s="1" t="s">
         <v>14</v>
       </c>
@@ -9150,9 +8554,7 @@
       <c r="D162" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="E162" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E162" s="1"/>
       <c r="I162" s="1" t="s">
         <v>14</v>
       </c>
@@ -9173,9 +8575,7 @@
       <c r="D163" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E163" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E163" s="1"/>
       <c r="I163" s="1" t="s">
         <v>14</v>
       </c>
@@ -9196,9 +8596,7 @@
       <c r="D164" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="E164" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E164" s="1"/>
       <c r="I164" s="1" t="s">
         <v>14</v>
       </c>
@@ -9219,9 +8617,7 @@
       <c r="D165" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E165" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E165" s="1"/>
       <c r="I165" s="1" t="s">
         <v>14</v>
       </c>
@@ -9240,11 +8636,9 @@
         <v>391</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E166" s="1"/>
       <c r="I166" s="1" t="s">
         <v>14</v>
       </c>
@@ -9265,9 +8659,7 @@
       <c r="D167" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="E167" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E167" s="1"/>
       <c r="I167" s="1" t="s">
         <v>14</v>
       </c>
@@ -9288,9 +8680,7 @@
       <c r="D168" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="E168" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E168" s="1"/>
       <c r="I168" s="1" t="s">
         <v>14</v>
       </c>
@@ -9311,9 +8701,7 @@
       <c r="D169" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="E169" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E169" s="1"/>
       <c r="I169" s="1" t="s">
         <v>14</v>
       </c>
@@ -9334,9 +8722,7 @@
       <c r="D170" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="E170" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E170" s="1"/>
       <c r="I170" s="1" t="s">
         <v>14</v>
       </c>
@@ -9357,9 +8743,7 @@
       <c r="D171" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="E171" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E171" s="1"/>
       <c r="I171" s="1" t="s">
         <v>14</v>
       </c>
@@ -9378,11 +8762,9 @@
         <v>391</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E172" s="1"/>
       <c r="I172" s="1" t="s">
         <v>14</v>
       </c>
@@ -9403,9 +8785,7 @@
       <c r="D173" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E173" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E173" s="1"/>
       <c r="I173" s="1" t="s">
         <v>14</v>
       </c>
@@ -9426,9 +8806,7 @@
       <c r="D174" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E174" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E174" s="1"/>
       <c r="I174" s="1" t="s">
         <v>14</v>
       </c>
@@ -9447,11 +8825,9 @@
         <v>391</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E175" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E175" s="1"/>
       <c r="I175" s="1" t="s">
         <v>14</v>
       </c>
@@ -9470,11 +8846,9 @@
         <v>391</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E176" s="1"/>
       <c r="I176" s="1" t="s">
         <v>14</v>
       </c>
@@ -9493,11 +8867,9 @@
         <v>391</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E177" s="1"/>
       <c r="I177" s="1" t="s">
         <v>14</v>
       </c>
@@ -9516,11 +8888,9 @@
         <v>391</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E178" s="1"/>
       <c r="I178" s="1" t="s">
         <v>14</v>
       </c>
@@ -9541,9 +8911,7 @@
       <c r="D179" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E179" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E179" s="1"/>
       <c r="I179" s="1" t="s">
         <v>14</v>
       </c>
@@ -9564,9 +8932,7 @@
       <c r="D180" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="E180" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E180" s="1"/>
       <c r="I180" s="1" t="s">
         <v>14</v>
       </c>
@@ -9587,9 +8953,7 @@
       <c r="D181" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E181" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E181" s="1"/>
       <c r="I181" s="1" t="s">
         <v>14</v>
       </c>
@@ -9608,11 +8972,9 @@
         <v>438</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E182" s="1"/>
       <c r="I182" s="1" t="s">
         <v>14</v>
       </c>
@@ -9633,9 +8995,7 @@
       <c r="D183" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="E183" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E183" s="1"/>
       <c r="I183" s="1" t="s">
         <v>14</v>
       </c>
@@ -9656,9 +9016,7 @@
       <c r="D184" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E184" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E184" s="1"/>
       <c r="I184" s="1" t="s">
         <v>14</v>
       </c>
@@ -9677,11 +9035,9 @@
         <v>438</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E185" s="1"/>
       <c r="I185" s="1" t="s">
         <v>14</v>
       </c>
@@ -9702,9 +9058,7 @@
       <c r="D186" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E186" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E186" s="1"/>
       <c r="I186" s="1" t="s">
         <v>14</v>
       </c>
@@ -9723,11 +9077,9 @@
         <v>438</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E187" s="1"/>
       <c r="I187" s="1" t="s">
         <v>14</v>
       </c>
@@ -9748,9 +9100,7 @@
       <c r="D188" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E188" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E188" s="1"/>
       <c r="I188" s="1" t="s">
         <v>14</v>
       </c>
@@ -9771,9 +9121,7 @@
       <c r="D189" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="E189" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E189" s="1"/>
       <c r="I189" s="1" t="s">
         <v>14</v>
       </c>
@@ -9794,9 +9142,7 @@
       <c r="D190" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="E190" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E190" s="1"/>
       <c r="I190" s="1" t="s">
         <v>14</v>
       </c>
@@ -9817,9 +9163,7 @@
       <c r="D191" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="E191" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E191" s="1"/>
       <c r="I191" s="1" t="s">
         <v>14</v>
       </c>
@@ -9840,9 +9184,7 @@
       <c r="D192" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="E192" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E192" s="1"/>
       <c r="I192" s="1" t="s">
         <v>14</v>
       </c>
@@ -9863,9 +9205,7 @@
       <c r="D193" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="E193" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E193" s="1"/>
       <c r="I193" s="1" t="s">
         <v>14</v>
       </c>
@@ -9886,9 +9226,7 @@
       <c r="D194" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="E194" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E194" s="1"/>
       <c r="I194" s="1" t="s">
         <v>14</v>
       </c>
@@ -9909,9 +9247,7 @@
       <c r="D195" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="E195" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E195" s="1"/>
       <c r="I195" s="1" t="s">
         <v>14</v>
       </c>
@@ -9932,9 +9268,7 @@
       <c r="D196" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="E196" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E196" s="1"/>
       <c r="I196" s="1" t="s">
         <v>14</v>
       </c>
@@ -9955,9 +9289,7 @@
       <c r="D197" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="E197" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E197" s="1"/>
       <c r="I197" s="1" t="s">
         <v>14</v>
       </c>
@@ -9978,9 +9310,7 @@
       <c r="D198" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E198" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E198" s="1"/>
       <c r="I198" s="1" t="s">
         <v>14</v>
       </c>
@@ -9999,11 +9329,9 @@
         <v>457</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="E199" s="1"/>
       <c r="I199" s="1" t="s">
         <v>14</v>
       </c>
@@ -10024,9 +9352,7 @@
       <c r="D200" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E200" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E200" s="1"/>
       <c r="I200" s="1" t="s">
         <v>14</v>
       </c>
@@ -10045,11 +9371,9 @@
         <v>484</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E201" s="1"/>
       <c r="I201" s="1" t="s">
         <v>14</v>
       </c>
@@ -10068,11 +9392,9 @@
         <v>484</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E202" s="1"/>
       <c r="I202" s="1" t="s">
         <v>14</v>
       </c>
@@ -10091,11 +9413,9 @@
         <v>484</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E203" s="1"/>
       <c r="I203" s="1" t="s">
         <v>14</v>
       </c>
@@ -10114,11 +9434,9 @@
         <v>484</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E204" s="1"/>
       <c r="I204" s="1" t="s">
         <v>93</v>
       </c>
@@ -10137,11 +9455,9 @@
         <v>484</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E205" s="1"/>
       <c r="I205" s="1" t="s">
         <v>14</v>
       </c>
@@ -10160,11 +9476,9 @@
         <v>484</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E206" s="1"/>
       <c r="I206" s="1" t="s">
         <v>14</v>
       </c>
@@ -10183,11 +9497,9 @@
         <v>484</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E207" s="1"/>
       <c r="I207" s="1" t="s">
         <v>14</v>
       </c>
@@ -10206,11 +9518,9 @@
         <v>484</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E208" s="1"/>
       <c r="I208" s="1" t="s">
         <v>14</v>
       </c>
@@ -10229,11 +9539,9 @@
         <v>484</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E209" s="1"/>
       <c r="I209" s="1" t="s">
         <v>14</v>
       </c>
@@ -10254,9 +9562,7 @@
       <c r="D210" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="E210" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E210" s="1"/>
       <c r="I210" s="1" t="s">
         <v>14</v>
       </c>
@@ -10275,11 +9581,9 @@
         <v>484</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E211" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E211" s="1"/>
       <c r="I211" s="1" t="s">
         <v>14</v>
       </c>
@@ -10300,9 +9604,7 @@
       <c r="D212" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E212" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E212" s="1"/>
       <c r="I212" s="1" t="s">
         <v>14</v>
       </c>
@@ -10321,11 +9623,9 @@
         <v>484</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E213" s="1"/>
       <c r="I213" s="1" t="s">
         <v>93</v>
       </c>
@@ -10346,9 +9646,7 @@
       <c r="D214" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="E214" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E214" s="1"/>
       <c r="I214" s="1" t="s">
         <v>93</v>
       </c>
@@ -10367,11 +9665,9 @@
         <v>484</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E215" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E215" s="1"/>
       <c r="I215" s="1" t="s">
         <v>14</v>
       </c>
@@ -10392,9 +9688,7 @@
       <c r="D216" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="E216" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E216" s="1"/>
       <c r="I216" s="1" t="s">
         <v>14</v>
       </c>
@@ -10413,11 +9707,9 @@
         <v>484</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E217" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E217" s="1"/>
       <c r="I217" s="1" t="s">
         <v>14</v>
       </c>
@@ -10436,11 +9728,9 @@
         <v>484</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E218" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E218" s="1"/>
       <c r="I218" s="1" t="s">
         <v>14</v>
       </c>
@@ -10459,11 +9749,9 @@
         <v>484</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E219" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E219" s="1"/>
       <c r="I219" s="1" t="s">
         <v>14</v>
       </c>
@@ -10482,11 +9770,9 @@
         <v>484</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E220" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E220" s="1"/>
       <c r="I220" s="1" t="s">
         <v>14</v>
       </c>
@@ -10505,11 +9791,9 @@
         <v>484</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E221" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E221" s="1"/>
       <c r="I221" s="1" t="s">
         <v>14</v>
       </c>
@@ -10528,11 +9812,9 @@
         <v>484</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E222" s="1"/>
       <c r="I222" s="1" t="s">
         <v>93</v>
       </c>
@@ -10551,11 +9833,9 @@
         <v>484</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E223" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="E223" s="1"/>
       <c r="I223" s="1" t="s">
         <v>14</v>
       </c>
@@ -10576,9 +9856,7 @@
       <c r="D224" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E224" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E224" s="1"/>
       <c r="I224" s="1" t="s">
         <v>14</v>
       </c>
@@ -10599,9 +9877,7 @@
       <c r="D225" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="E225" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E225" s="1"/>
       <c r="I225" s="1" t="s">
         <v>93</v>
       </c>
@@ -10622,9 +9898,7 @@
       <c r="D226" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E226" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E226" s="1"/>
       <c r="I226" s="1" t="s">
         <v>93</v>
       </c>
@@ -10645,9 +9919,7 @@
       <c r="D227" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="E227" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E227" s="1"/>
       <c r="I227" s="1" t="s">
         <v>93</v>
       </c>
@@ -10668,9 +9940,7 @@
       <c r="D228" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="E228" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E228" s="1"/>
       <c r="I228" s="1" t="s">
         <v>93</v>
       </c>
@@ -10691,9 +9961,7 @@
       <c r="D229" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="E229" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E229" s="1"/>
       <c r="I229" s="1" t="s">
         <v>93</v>
       </c>
@@ -10714,9 +9982,7 @@
       <c r="D230" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E230" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E230" s="1"/>
       <c r="I230" s="1" t="s">
         <v>93</v>
       </c>
@@ -10737,9 +10003,7 @@
       <c r="D231" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="E231" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E231" s="1"/>
       <c r="I231" s="1" t="s">
         <v>93</v>
       </c>
@@ -10760,9 +10024,7 @@
       <c r="D232" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="E232" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E232" s="1"/>
       <c r="I232" s="1" t="s">
         <v>93</v>
       </c>
@@ -10783,9 +10045,7 @@
       <c r="D233" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="E233" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E233" s="1"/>
       <c r="I233" s="1" t="s">
         <v>93</v>
       </c>
@@ -10806,9 +10066,7 @@
       <c r="D234" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E234" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E234" s="1"/>
       <c r="I234" s="1" t="s">
         <v>93</v>
       </c>
@@ -10829,9 +10087,7 @@
       <c r="D235" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="E235" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E235" s="1"/>
       <c r="I235" s="1" t="s">
         <v>93</v>
       </c>
@@ -10850,11 +10106,9 @@
         <v>553</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E236" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E236" s="1"/>
       <c r="I236" s="1" t="s">
         <v>14</v>
       </c>
@@ -10873,11 +10127,9 @@
         <v>553</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E237" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="E237" s="1"/>
       <c r="I237" s="1" t="s">
         <v>14</v>
       </c>
@@ -10898,9 +10150,7 @@
       <c r="D238" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E238" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E238" s="1"/>
       <c r="I238" s="1" t="s">
         <v>14</v>
       </c>
@@ -10919,11 +10169,9 @@
         <v>553</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E239" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E239" s="1"/>
       <c r="I239" s="1" t="s">
         <v>14</v>
       </c>
@@ -10944,9 +10192,7 @@
       <c r="D240" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E240" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E240" s="1"/>
       <c r="I240" s="1" t="s">
         <v>14</v>
       </c>
@@ -10965,11 +10211,9 @@
         <v>553</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E241" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="E241" s="1"/>
       <c r="I241" s="1" t="s">
         <v>14</v>
       </c>
@@ -10990,9 +10234,7 @@
       <c r="D242" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="E242" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E242" s="1"/>
       <c r="I242" s="1" t="s">
         <v>93</v>
       </c>
@@ -11013,9 +10255,7 @@
       <c r="D243" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="E243" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E243" s="1"/>
       <c r="I243" s="1" t="s">
         <v>93</v>
       </c>
@@ -11036,9 +10276,7 @@
       <c r="D244" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="E244" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E244" s="1"/>
       <c r="I244" s="1" t="s">
         <v>93</v>
       </c>
@@ -11059,9 +10297,7 @@
       <c r="D245" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E245" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="E245" s="1"/>
       <c r="I245" s="1" t="s">
         <v>14</v>
       </c>
@@ -11080,11 +10316,9 @@
         <v>18</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E246" s="1">
-        <v>70000</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E246" s="1"/>
       <c r="H246" s="1" t="s">
         <v>573</v>
       </c>
@@ -11108,9 +10342,7 @@
       <c r="D247" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="E247" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E247" s="1"/>
       <c r="H247" s="1" t="s">
         <v>573</v>
       </c>
@@ -11134,9 +10366,7 @@
       <c r="D248" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="E248" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E248" s="1"/>
       <c r="H248" s="1" t="s">
         <v>573</v>
       </c>
@@ -11160,9 +10390,7 @@
       <c r="D249" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="E249" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E249" s="1"/>
       <c r="H249" s="1" t="s">
         <v>573</v>
       </c>
@@ -11186,9 +10414,7 @@
       <c r="D250" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E250" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E250" s="1"/>
       <c r="H250" s="1" t="s">
         <v>573</v>
       </c>
@@ -11212,9 +10438,7 @@
       <c r="D251" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E251" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E251" s="1"/>
       <c r="H251" s="1" t="s">
         <v>573</v>
       </c>
@@ -11238,9 +10462,7 @@
       <c r="D252" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="E252" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E252" s="1"/>
       <c r="H252" s="1" t="s">
         <v>573</v>
       </c>
@@ -11264,9 +10486,7 @@
       <c r="D253" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E253" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E253" s="1"/>
       <c r="H253" s="1" t="s">
         <v>573</v>
       </c>
@@ -11290,9 +10510,7 @@
       <c r="D254" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E254" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E254" s="1"/>
       <c r="H254" s="1" t="s">
         <v>595</v>
       </c>
@@ -11316,9 +10534,7 @@
       <c r="D255" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="E255" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E255" s="1"/>
       <c r="H255" s="1" t="s">
         <v>595</v>
       </c>
@@ -11342,9 +10558,7 @@
       <c r="D256" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="E256" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E256" s="1"/>
       <c r="H256" s="1" t="s">
         <v>602</v>
       </c>
@@ -11368,9 +10582,7 @@
       <c r="D257" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="E257" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E257" s="1"/>
       <c r="H257" s="1" t="s">
         <v>595</v>
       </c>
@@ -11394,9 +10606,7 @@
       <c r="D258" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E258" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E258" s="1"/>
       <c r="H258" s="1" t="s">
         <v>609</v>
       </c>
@@ -11420,9 +10630,7 @@
       <c r="D259" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E259" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E259" s="1"/>
       <c r="H259" s="1" t="s">
         <v>609</v>
       </c>
@@ -11446,9 +10654,7 @@
       <c r="D260" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="E260" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E260" s="1"/>
       <c r="H260" s="1" t="s">
         <v>595</v>
       </c>
@@ -11472,9 +10678,7 @@
       <c r="D261" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="E261" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E261" s="1"/>
       <c r="H261" s="1" t="s">
         <v>618</v>
       </c>
@@ -11498,9 +10702,7 @@
       <c r="D262" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E262" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E262" s="1"/>
       <c r="H262" s="1" t="s">
         <v>618</v>
       </c>
@@ -11524,9 +10726,7 @@
       <c r="D263" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="E263" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E263" s="1"/>
       <c r="H263" s="1" t="s">
         <v>618</v>
       </c>
@@ -11550,9 +10750,7 @@
       <c r="D264" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E264" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E264" s="1"/>
       <c r="H264" s="1" t="s">
         <v>618</v>
       </c>
@@ -11576,9 +10774,7 @@
       <c r="D265" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="E265" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E265" s="1"/>
       <c r="H265" s="1" t="s">
         <v>595</v>
       </c>
@@ -11602,9 +10798,7 @@
       <c r="D266" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="E266" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E266" s="1"/>
       <c r="H266" s="1" t="s">
         <v>595</v>
       </c>
@@ -11628,9 +10822,7 @@
       <c r="D267" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="E267" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E267" s="1"/>
       <c r="H267" s="1" t="s">
         <v>595</v>
       </c>
@@ -11654,9 +10846,7 @@
       <c r="D268" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="E268" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E268" s="1"/>
       <c r="H268" s="1" t="s">
         <v>595</v>
       </c>
@@ -11680,9 +10870,7 @@
       <c r="D269" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="E269" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E269" s="1"/>
       <c r="H269" s="1" t="s">
         <v>618</v>
       </c>
@@ -11706,9 +10894,7 @@
       <c r="D270" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="E270" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E270" s="1"/>
       <c r="H270" s="1" t="s">
         <v>618</v>
       </c>
@@ -11732,9 +10918,7 @@
       <c r="D271" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="E271" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E271" s="1"/>
       <c r="H271" s="1" t="s">
         <v>648</v>
       </c>
@@ -11758,9 +10942,7 @@
       <c r="D272" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="E272" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E272" s="1"/>
       <c r="H272" s="1" t="s">
         <v>648</v>
       </c>
@@ -11784,9 +10966,7 @@
       <c r="D273" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E273" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E273" s="1"/>
       <c r="H273" s="1" t="s">
         <v>654</v>
       </c>
@@ -11810,9 +10990,7 @@
       <c r="D274" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E274" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E274" s="1"/>
       <c r="H274" s="1" t="s">
         <v>654</v>
       </c>
@@ -11836,11 +11014,9 @@
       <c r="D275" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E275" s="1">
-        <v>70000</v>
-      </c>
+      <c r="E275" s="1"/>
       <c r="H275" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>14</v>
@@ -11862,9 +11038,7 @@
       <c r="D276" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="E276" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E276" s="1"/>
       <c r="H276" s="1" t="s">
         <v>662</v>
       </c>
@@ -11888,9 +11062,7 @@
       <c r="D277" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="E277" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E277" s="1"/>
       <c r="H277" s="1" t="s">
         <v>618</v>
       </c>
@@ -11914,9 +11086,7 @@
       <c r="D278" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="E278" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E278" s="1"/>
       <c r="H278" s="1" t="s">
         <v>618</v>
       </c>
@@ -11940,9 +11110,7 @@
       <c r="D279" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E279" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E279" s="1"/>
       <c r="H279" s="1" t="s">
         <v>595</v>
       </c>
@@ -11966,9 +11134,7 @@
       <c r="D280" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E280" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E280" s="1"/>
       <c r="H280" s="1" t="s">
         <v>618</v>
       </c>
@@ -11992,9 +11158,7 @@
       <c r="D281" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E281" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E281" s="1"/>
       <c r="H281" s="1" t="s">
         <v>595</v>
       </c>
@@ -12016,11 +11180,9 @@
         <v>676</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E282" s="1">
-        <v>85000</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E282" s="1"/>
       <c r="H282" s="1" t="s">
         <v>595</v>
       </c>
@@ -12042,11 +11204,9 @@
         <v>676</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E283" s="1">
-        <v>85000</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E283" s="1"/>
       <c r="H283" s="1" t="s">
         <v>595</v>
       </c>
@@ -12070,9 +11230,7 @@
       <c r="D284" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="E284" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E284" s="1"/>
       <c r="H284" s="1" t="s">
         <v>609</v>
       </c>
@@ -12096,11 +11254,9 @@
       <c r="D285" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="E285" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E285" s="1"/>
       <c r="H285" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>14</v>
@@ -12122,9 +11278,7 @@
       <c r="D286" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="E286" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E286" s="1"/>
       <c r="H286" s="1" t="s">
         <v>689</v>
       </c>
@@ -12148,9 +11302,7 @@
       <c r="D287" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E287" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E287" s="1"/>
       <c r="H287" s="1" t="s">
         <v>689</v>
       </c>
@@ -12174,9 +11326,7 @@
       <c r="D288" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="E288" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E288" s="1"/>
       <c r="H288" s="1" t="s">
         <v>689</v>
       </c>
@@ -12200,9 +11350,7 @@
       <c r="D289" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="E289" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E289" s="1"/>
       <c r="H289" s="1" t="s">
         <v>689</v>
       </c>
@@ -12226,11 +11374,9 @@
       <c r="D290" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="E290" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E290" s="1"/>
       <c r="H290" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I290" s="1" t="s">
         <v>14</v>
@@ -12252,9 +11398,7 @@
       <c r="D291" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="E291" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E291" s="1"/>
       <c r="H291" s="1" t="s">
         <v>609</v>
       </c>
@@ -12278,9 +11422,7 @@
       <c r="D292" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="E292" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E292" s="1"/>
       <c r="H292" s="1" t="s">
         <v>618</v>
       </c>
@@ -12304,9 +11446,7 @@
       <c r="D293" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="E293" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E293" s="1"/>
       <c r="H293" s="1" t="s">
         <v>618</v>
       </c>
@@ -12330,9 +11470,7 @@
       <c r="D294" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="E294" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E294" s="1"/>
       <c r="H294" s="1" t="s">
         <v>595</v>
       </c>
@@ -12356,9 +11494,7 @@
       <c r="D295" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E295" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E295" s="1"/>
       <c r="H295" s="1" t="s">
         <v>618</v>
       </c>
@@ -12382,9 +11518,7 @@
       <c r="D296" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="E296" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E296" s="1"/>
       <c r="H296" s="1" t="s">
         <v>662</v>
       </c>
@@ -12408,9 +11542,7 @@
       <c r="D297" s="3" t="s">
         <v>719</v>
       </c>
-      <c r="E297" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E297" s="1"/>
       <c r="H297" s="1" t="s">
         <v>618</v>
       </c>
@@ -12434,9 +11566,7 @@
       <c r="D298" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="E298" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E298" s="1"/>
       <c r="H298" s="1" t="s">
         <v>618</v>
       </c>
@@ -12460,9 +11590,7 @@
       <c r="D299" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E299" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E299" s="1"/>
       <c r="H299" s="1" t="s">
         <v>609</v>
       </c>
@@ -12486,9 +11614,7 @@
       <c r="D300" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="E300" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E300" s="1"/>
       <c r="H300" s="1" t="s">
         <v>595</v>
       </c>
@@ -12512,9 +11638,7 @@
       <c r="D301" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E301" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E301" s="1"/>
       <c r="H301" s="1" t="s">
         <v>731</v>
       </c>
@@ -12538,9 +11662,7 @@
       <c r="D302" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="E302" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E302" s="1"/>
       <c r="H302" s="1" t="s">
         <v>595</v>
       </c>
@@ -12564,9 +11686,7 @@
       <c r="D303" s="3" t="s">
         <v>738</v>
       </c>
-      <c r="E303" s="1">
-        <v>85000</v>
-      </c>
+      <c r="E303" s="1"/>
       <c r="H303" s="1" t="s">
         <v>739</v>
       </c>
@@ -12588,13 +11708,11 @@
         <v>253</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E304" s="1">
-        <v>85000</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E304" s="1"/>
       <c r="H304" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>14</v>
@@ -12616,9 +11734,7 @@
       <c r="D305" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E305" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E305" s="1"/>
       <c r="H305" s="1" t="s">
         <v>618</v>
       </c>
@@ -12640,11 +11756,9 @@
         <v>12</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E306" s="1">
-        <v>78000</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E306" s="1"/>
       <c r="H306" s="1" t="s">
         <v>618</v>
       </c>
@@ -12668,11 +11782,9 @@
       <c r="D307" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E307" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E307" s="1"/>
       <c r="H307" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>93</v>
@@ -12694,9 +11806,7 @@
       <c r="D308" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E308" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E308" s="1"/>
       <c r="H308" s="1" t="s">
         <v>618</v>
       </c>
@@ -12720,9 +11830,7 @@
       <c r="D309" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="E309" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E309" s="1"/>
       <c r="H309" s="1" t="s">
         <v>753</v>
       </c>
@@ -12746,9 +11854,7 @@
       <c r="D310" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="E310" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E310" s="1"/>
       <c r="H310" s="1" t="s">
         <v>618</v>
       </c>
@@ -12772,9 +11878,7 @@
       <c r="D311" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="E311" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E311" s="1"/>
       <c r="H311" s="1" t="s">
         <v>618</v>
       </c>
@@ -12798,11 +11902,9 @@
       <c r="D312" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="E312" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E312" s="1"/>
       <c r="H312" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>584</v>
@@ -12822,11 +11924,9 @@
         <v>292</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E313" s="1">
-        <v>78000</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E313" s="1"/>
       <c r="H313" s="1" t="s">
         <v>618</v>
       </c>
@@ -12850,11 +11950,9 @@
       <c r="D314" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="E314" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E314" s="1"/>
       <c r="H314" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>93</v>
@@ -12876,9 +11974,7 @@
       <c r="D315" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E315" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E315" s="1"/>
       <c r="H315" s="1" t="s">
         <v>648</v>
       </c>
@@ -12902,9 +11998,7 @@
       <c r="D316" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E316" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E316" s="1"/>
       <c r="H316" s="1" t="s">
         <v>648</v>
       </c>
@@ -12928,9 +12022,7 @@
       <c r="D317" s="3" t="s">
         <v>774</v>
       </c>
-      <c r="E317" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E317" s="1"/>
       <c r="H317" s="1" t="s">
         <v>609</v>
       </c>
@@ -12954,11 +12046,9 @@
       <c r="D318" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E318" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E318" s="1"/>
       <c r="H318" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>14</v>
@@ -12980,9 +12070,7 @@
       <c r="D319" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E319" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E319" s="1"/>
       <c r="H319" s="1" t="s">
         <v>595</v>
       </c>
@@ -13006,9 +12094,7 @@
       <c r="D320" s="3" t="s">
         <v>781</v>
       </c>
-      <c r="E320" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E320" s="1"/>
       <c r="H320" s="1" t="s">
         <v>618</v>
       </c>
@@ -13032,9 +12118,7 @@
       <c r="D321" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="E321" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E321" s="1"/>
       <c r="H321" s="1" t="s">
         <v>609</v>
       </c>
@@ -13058,11 +12142,9 @@
       <c r="D322" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="E322" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E322" s="1"/>
       <c r="H322" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I322" s="1" t="s">
         <v>14</v>
@@ -13084,9 +12166,7 @@
       <c r="D323" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="E323" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E323" s="1"/>
       <c r="H323" s="1" t="s">
         <v>618</v>
       </c>
@@ -13108,11 +12188,9 @@
         <v>321</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E324" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E324" s="1"/>
       <c r="H324" s="1" t="s">
         <v>654</v>
       </c>
@@ -13134,11 +12212,9 @@
         <v>321</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E325" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E325" s="1"/>
       <c r="H325" s="1" t="s">
         <v>654</v>
       </c>
@@ -13160,11 +12236,9 @@
         <v>321</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E326" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E326" s="1"/>
       <c r="H326" s="1" t="s">
         <v>654</v>
       </c>
@@ -13186,11 +12260,9 @@
         <v>343</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E327" s="1">
-        <v>78000</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E327" s="1"/>
       <c r="H327" s="1" t="s">
         <v>618</v>
       </c>
@@ -13214,9 +12286,7 @@
       <c r="D328" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E328" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E328" s="1"/>
       <c r="H328" s="1" t="s">
         <v>648</v>
       </c>
@@ -13240,9 +12310,7 @@
       <c r="D329" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E329" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E329" s="1"/>
       <c r="H329" s="1" t="s">
         <v>648</v>
       </c>
@@ -13266,11 +12334,9 @@
       <c r="D330" s="3" t="s">
         <v>804</v>
       </c>
-      <c r="E330" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E330" s="1"/>
       <c r="H330" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>14</v>
@@ -13290,13 +12356,11 @@
         <v>391</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E331" s="1">
-        <v>78000</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E331" s="1"/>
       <c r="H331" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I331" s="1" t="s">
         <v>14</v>
@@ -13318,9 +12382,7 @@
       <c r="D332" s="3" t="s">
         <v>809</v>
       </c>
-      <c r="E332" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E332" s="1"/>
       <c r="H332" s="1" t="s">
         <v>618</v>
       </c>
@@ -13344,9 +12406,7 @@
       <c r="D333" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="E333" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E333" s="1"/>
       <c r="H333" s="1" t="s">
         <v>648</v>
       </c>
@@ -13370,9 +12430,7 @@
       <c r="D334" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E334" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E334" s="1"/>
       <c r="H334" s="1" t="s">
         <v>689</v>
       </c>
@@ -13396,9 +12454,7 @@
       <c r="D335" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="E335" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E335" s="1"/>
       <c r="H335" s="1" t="s">
         <v>595</v>
       </c>
@@ -13422,11 +12478,9 @@
       <c r="D336" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E336" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E336" s="1"/>
       <c r="H336" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>14</v>
@@ -13448,11 +12502,9 @@
       <c r="D337" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E337" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E337" s="1"/>
       <c r="H337" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>14</v>
@@ -13474,11 +12526,9 @@
       <c r="D338" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E338" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E338" s="1"/>
       <c r="H338" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>14</v>
@@ -13500,11 +12550,9 @@
       <c r="D339" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E339" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E339" s="1"/>
       <c r="H339" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>14</v>
@@ -13526,11 +12574,9 @@
       <c r="D340" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E340" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E340" s="1"/>
       <c r="H340" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>14</v>
@@ -13552,9 +12598,7 @@
       <c r="D341" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E341" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E341" s="1"/>
       <c r="H341" s="1" t="s">
         <v>595</v>
       </c>
@@ -13578,9 +12622,7 @@
       <c r="D342" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E342" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E342" s="1"/>
       <c r="H342" s="1" t="s">
         <v>595</v>
       </c>
@@ -13604,9 +12646,7 @@
       <c r="D343" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E343" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E343" s="1"/>
       <c r="H343" s="1" t="s">
         <v>595</v>
       </c>
@@ -13630,9 +12670,7 @@
       <c r="D344" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E344" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E344" s="1"/>
       <c r="H344" s="1" t="s">
         <v>595</v>
       </c>
@@ -13656,9 +12694,7 @@
       <c r="D345" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E345" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E345" s="1"/>
       <c r="H345" s="1" t="s">
         <v>595</v>
       </c>
@@ -13682,9 +12718,7 @@
       <c r="D346" s="3" t="s">
         <v>838</v>
       </c>
-      <c r="E346" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E346" s="1"/>
       <c r="H346" s="1" t="s">
         <v>648</v>
       </c>
@@ -13708,9 +12742,7 @@
       <c r="D347" s="3" t="s">
         <v>781</v>
       </c>
-      <c r="E347" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E347" s="1"/>
       <c r="H347" s="1" t="s">
         <v>595</v>
       </c>
@@ -13734,9 +12766,7 @@
       <c r="D348" s="3" t="s">
         <v>843</v>
       </c>
-      <c r="E348" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E348" s="1"/>
       <c r="H348" s="1" t="s">
         <v>648</v>
       </c>
@@ -13760,9 +12790,7 @@
       <c r="D349" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="E349" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E349" s="1"/>
       <c r="H349" s="1" t="s">
         <v>689</v>
       </c>
@@ -13786,11 +12814,9 @@
       <c r="D350" s="3" t="s">
         <v>849</v>
       </c>
-      <c r="E350" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E350" s="1"/>
       <c r="H350" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>14</v>
@@ -13812,11 +12838,9 @@
       <c r="D351" s="3" t="s">
         <v>852</v>
       </c>
-      <c r="E351" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E351" s="1"/>
       <c r="H351" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>584</v>
@@ -13838,9 +12862,7 @@
       <c r="D352" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="E352" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E352" s="1"/>
       <c r="H352" s="1" t="s">
         <v>618</v>
       </c>
@@ -13862,11 +12884,9 @@
         <v>438</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E353" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E353" s="1"/>
       <c r="H353" s="1" t="s">
         <v>618</v>
       </c>
@@ -13888,11 +12908,9 @@
         <v>438</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E354" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E354" s="1"/>
       <c r="H354" s="1" t="s">
         <v>618</v>
       </c>
@@ -13914,11 +12932,9 @@
         <v>438</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E355" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E355" s="1"/>
       <c r="H355" s="1" t="s">
         <v>618</v>
       </c>
@@ -13940,11 +12956,9 @@
         <v>438</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E356" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E356" s="1"/>
       <c r="H356" s="1" t="s">
         <v>618</v>
       </c>
@@ -13966,11 +12980,9 @@
         <v>438</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E357" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E357" s="1"/>
       <c r="H357" s="1" t="s">
         <v>618</v>
       </c>
@@ -13992,11 +13004,9 @@
         <v>438</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E358" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E358" s="1"/>
       <c r="H358" s="1" t="s">
         <v>618</v>
       </c>
@@ -14018,13 +13028,11 @@
         <v>438</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E359" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E359" s="1"/>
       <c r="H359" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I359" s="1" t="s">
         <v>14</v>
@@ -14044,13 +13052,11 @@
         <v>438</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E360" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E360" s="1"/>
       <c r="H360" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I360" s="1" t="s">
         <v>14</v>
@@ -14070,13 +13076,11 @@
         <v>438</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E361" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E361" s="1"/>
       <c r="H361" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I361" s="1" t="s">
         <v>14</v>
@@ -14096,13 +13100,11 @@
         <v>438</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E362" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E362" s="1"/>
       <c r="H362" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I362" s="1" t="s">
         <v>14</v>
@@ -14122,13 +13124,11 @@
         <v>438</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E363" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E363" s="1"/>
       <c r="H363" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I363" s="1" t="s">
         <v>14</v>
@@ -14148,13 +13148,11 @@
         <v>438</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E364" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E364" s="1"/>
       <c r="H364" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I364" s="1" t="s">
         <v>14</v>
@@ -14174,13 +13172,11 @@
         <v>438</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E365" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E365" s="1"/>
       <c r="H365" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I365" s="1" t="s">
         <v>14</v>
@@ -14200,13 +13196,11 @@
         <v>438</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E366" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E366" s="1"/>
       <c r="H366" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I366" s="1" t="s">
         <v>14</v>
@@ -14226,13 +13220,11 @@
         <v>438</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E367" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E367" s="1"/>
       <c r="H367" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I367" s="1" t="s">
         <v>14</v>
@@ -14252,13 +13244,11 @@
         <v>438</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E368" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E368" s="1"/>
       <c r="H368" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I368" s="1" t="s">
         <v>14</v>
@@ -14278,13 +13268,11 @@
         <v>438</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E369" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E369" s="1"/>
       <c r="H369" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I369" s="1" t="s">
         <v>14</v>
@@ -14304,13 +13292,11 @@
         <v>438</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E370" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E370" s="1"/>
       <c r="H370" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I370" s="1" t="s">
         <v>14</v>
@@ -14330,13 +13316,11 @@
         <v>438</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E371" s="1">
-        <v>78000</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E371" s="1"/>
       <c r="H371" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I371" s="1" t="s">
         <v>14</v>
@@ -14358,9 +13342,7 @@
       <c r="D372" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E372" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E372" s="1"/>
       <c r="H372" s="1" t="s">
         <v>595</v>
       </c>
@@ -14384,9 +13366,7 @@
       <c r="D373" s="3" t="s">
         <v>898</v>
       </c>
-      <c r="E373" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E373" s="1"/>
       <c r="H373" s="1" t="s">
         <v>618</v>
       </c>
@@ -14410,11 +13390,9 @@
       <c r="D374" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="E374" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E374" s="1"/>
       <c r="H374" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I374" s="1" t="s">
         <v>14</v>
@@ -14436,9 +13414,7 @@
       <c r="D375" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E375" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E375" s="1"/>
       <c r="H375" s="1" t="s">
         <v>609</v>
       </c>
@@ -14462,9 +13438,7 @@
       <c r="D376" s="3" t="s">
         <v>905</v>
       </c>
-      <c r="E376" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E376" s="1"/>
       <c r="H376" s="1" t="s">
         <v>618</v>
       </c>
@@ -14488,9 +13462,7 @@
       <c r="D377" s="3" t="s">
         <v>908</v>
       </c>
-      <c r="E377" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E377" s="1"/>
       <c r="H377" s="1" t="s">
         <v>909</v>
       </c>
@@ -14514,9 +13486,7 @@
       <c r="D378" s="3" t="s">
         <v>912</v>
       </c>
-      <c r="E378" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E378" s="1"/>
       <c r="H378" s="1" t="s">
         <v>618</v>
       </c>
@@ -14540,9 +13510,7 @@
       <c r="D379" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="E379" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E379" s="1"/>
       <c r="H379" s="1" t="s">
         <v>618</v>
       </c>
@@ -14566,9 +13534,7 @@
       <c r="D380" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="E380" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E380" s="1"/>
       <c r="H380" s="1" t="s">
         <v>618</v>
       </c>
@@ -14592,9 +13558,7 @@
       <c r="D381" s="3" t="s">
         <v>920</v>
       </c>
-      <c r="E381" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E381" s="1"/>
       <c r="H381" s="1" t="s">
         <v>609</v>
       </c>
@@ -14616,11 +13580,9 @@
         <v>438</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E382" s="1">
-        <v>78000</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E382" s="1"/>
       <c r="H382" s="1" t="s">
         <v>618</v>
       </c>
@@ -14644,11 +13606,9 @@
       <c r="D383" s="3" t="s">
         <v>926</v>
       </c>
-      <c r="E383" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E383" s="1"/>
       <c r="H383" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I383" s="1" t="s">
         <v>14</v>
@@ -14670,9 +13630,7 @@
       <c r="D384" s="3" t="s">
         <v>929</v>
       </c>
-      <c r="E384" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E384" s="1"/>
       <c r="H384" s="1" t="s">
         <v>595</v>
       </c>
@@ -14696,9 +13654,7 @@
       <c r="D385" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E385" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E385" s="1"/>
       <c r="H385" s="1" t="s">
         <v>654</v>
       </c>
@@ -14722,11 +13678,9 @@
       <c r="D386" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="E386" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E386" s="1"/>
       <c r="H386" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I386" s="1" t="s">
         <v>14</v>
@@ -14748,11 +13702,9 @@
       <c r="D387" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E387" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E387" s="1"/>
       <c r="H387" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I387" s="1" t="s">
         <v>93</v>
@@ -14772,11 +13724,9 @@
         <v>570</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E388" s="1">
-        <v>78000</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E388" s="1"/>
       <c r="H388" s="1" t="s">
         <v>938</v>
       </c>
@@ -14800,9 +13750,7 @@
       <c r="D389" s="3" t="s">
         <v>941</v>
       </c>
-      <c r="E389" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E389" s="1"/>
       <c r="H389" s="1" t="s">
         <v>938</v>
       </c>
@@ -14826,9 +13774,7 @@
       <c r="D390" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E390" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E390" s="1"/>
       <c r="H390" s="1" t="s">
         <v>938</v>
       </c>
@@ -14852,9 +13798,7 @@
       <c r="D391" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E391" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E391" s="1"/>
       <c r="H391" s="1" t="s">
         <v>938</v>
       </c>
@@ -14878,9 +13822,7 @@
       <c r="D392" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="E392" s="1">
-        <v>78000</v>
-      </c>
+      <c r="E392" s="1"/>
       <c r="H392" s="1" t="s">
         <v>609</v>
       </c>
@@ -14902,13 +13844,11 @@
         <v>950</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E393" s="1">
-        <v>78000</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E393" s="1"/>
       <c r="H393" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I393" s="1" t="s">
         <v>14</v>
@@ -14928,13 +13868,11 @@
         <v>953</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E394" s="1">
-        <v>78000</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E394" s="1"/>
       <c r="H394" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I394" s="1" t="s">
         <v>14</v>
@@ -16953,7 +15891,7 @@
       <c r="A465" s="18" t="s">
         <v>1128</v>
       </c>
-      <c r="B465" s="53" t="s">
+      <c r="B465" s="44" t="s">
         <v>1129</v>
       </c>
       <c r="C465" s="20" t="s">
@@ -17238,570 +16176,6 @@
       </c>
       <c r="J474" s="42" t="s">
         <v>574</v>
-      </c>
-    </row>
-    <row r="475" customFormat="1" spans="1:10">
-      <c r="A475" s="44" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B475" s="45" t="s">
-        <v>1153</v>
-      </c>
-      <c r="C475" s="44" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D475" s="44"/>
-      <c r="E475" s="44"/>
-      <c r="F475" s="46"/>
-      <c r="G475" s="47" t="s">
-        <v>1154</v>
-      </c>
-      <c r="H475" s="44"/>
-      <c r="I475" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J475" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="476" customFormat="1" ht="27.6" spans="1:10">
-      <c r="A476" s="44" t="s">
-        <v>1157</v>
-      </c>
-      <c r="B476" s="45" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C476" s="44" t="s">
-        <v>253</v>
-      </c>
-      <c r="D476" s="44"/>
-      <c r="E476" s="44"/>
-      <c r="F476" s="46"/>
-      <c r="G476" s="47" t="s">
-        <v>1159</v>
-      </c>
-      <c r="H476" s="44"/>
-      <c r="I476" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J476" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="477" customFormat="1" spans="1:10">
-      <c r="A477" s="48" t="s">
-        <v>1160</v>
-      </c>
-      <c r="B477" s="45" t="s">
-        <v>971</v>
-      </c>
-      <c r="C477" s="44" t="s">
-        <v>292</v>
-      </c>
-      <c r="D477" s="44"/>
-      <c r="E477" s="44"/>
-      <c r="F477" s="46"/>
-      <c r="G477" s="47" t="s">
-        <v>1161</v>
-      </c>
-      <c r="H477" s="44"/>
-      <c r="I477" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J477" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="478" customFormat="1" ht="89" customHeight="1" spans="1:10">
-      <c r="A478" s="49" t="s">
-        <v>1162</v>
-      </c>
-      <c r="B478" s="49" t="s">
-        <v>955</v>
-      </c>
-      <c r="C478" s="49" t="s">
-        <v>722</v>
-      </c>
-      <c r="D478" s="44"/>
-      <c r="E478" s="44"/>
-      <c r="F478" s="46"/>
-      <c r="G478" s="47" t="s">
-        <v>1163</v>
-      </c>
-      <c r="H478" s="44"/>
-      <c r="I478" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J478" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="479" customFormat="1" ht="27.6" spans="1:10">
-      <c r="A479" s="44" t="s">
-        <v>1164</v>
-      </c>
-      <c r="B479" s="45" t="s">
-        <v>1165</v>
-      </c>
-      <c r="C479" s="44" t="s">
-        <v>292</v>
-      </c>
-      <c r="D479" s="44"/>
-      <c r="E479" s="44"/>
-      <c r="F479" s="46"/>
-      <c r="G479" s="47" t="s">
-        <v>1166</v>
-      </c>
-      <c r="H479" s="44"/>
-      <c r="I479" s="47" t="s">
-        <v>1167</v>
-      </c>
-      <c r="J479" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="480" customFormat="1" spans="1:10">
-      <c r="A480" s="44" t="s">
-        <v>1168</v>
-      </c>
-      <c r="B480" s="45"/>
-      <c r="C480" s="44" t="s">
-        <v>1169</v>
-      </c>
-      <c r="D480" s="44"/>
-      <c r="E480" s="44"/>
-      <c r="F480" s="46"/>
-      <c r="G480" s="47" t="s">
-        <v>1170</v>
-      </c>
-      <c r="H480" s="44"/>
-      <c r="I480" s="47"/>
-      <c r="J480" s="44"/>
-    </row>
-    <row r="481" customFormat="1" spans="1:10">
-      <c r="A481" s="44" t="s">
-        <v>1171</v>
-      </c>
-      <c r="B481" s="45"/>
-      <c r="C481" s="44" t="s">
-        <v>1169</v>
-      </c>
-      <c r="D481" s="44"/>
-      <c r="E481" s="44"/>
-      <c r="F481" s="46"/>
-      <c r="G481" s="47" t="s">
-        <v>1172</v>
-      </c>
-      <c r="H481" s="44"/>
-      <c r="I481" s="47"/>
-      <c r="J481" s="44"/>
-    </row>
-    <row r="482" customFormat="1" ht="112" customHeight="1" spans="1:10">
-      <c r="A482" s="44" t="s">
-        <v>1173</v>
-      </c>
-      <c r="B482" s="45" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C482" s="44" t="s">
-        <v>1169</v>
-      </c>
-      <c r="D482" s="44"/>
-      <c r="E482" s="44"/>
-      <c r="F482" s="46"/>
-      <c r="G482" s="47" t="s">
-        <v>1175</v>
-      </c>
-      <c r="H482" s="44"/>
-      <c r="I482" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J482" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="483" customFormat="1" ht="159" customHeight="1" spans="1:10">
-      <c r="A483" s="44" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B483" s="45" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C483" s="44" t="s">
-        <v>232</v>
-      </c>
-      <c r="D483" s="44"/>
-      <c r="E483" s="44"/>
-      <c r="F483" s="46"/>
-      <c r="G483" s="47" t="s">
-        <v>1178</v>
-      </c>
-      <c r="H483" s="44"/>
-      <c r="I483" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J483" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="484" customFormat="1" ht="14.4" spans="1:10">
-      <c r="A484" s="48" t="s">
-        <v>1179</v>
-      </c>
-      <c r="B484" s="44" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C484" s="44" t="s">
-        <v>232</v>
-      </c>
-      <c r="D484" s="44"/>
-      <c r="E484" s="44"/>
-      <c r="F484" s="46"/>
-      <c r="G484" s="47" t="s">
-        <v>1180</v>
-      </c>
-      <c r="H484" s="44"/>
-      <c r="I484" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J484" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="485" customFormat="1" spans="1:10">
-      <c r="A485" s="48" t="s">
-        <v>1181</v>
-      </c>
-      <c r="B485" s="44" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C485" s="44" t="s">
-        <v>232</v>
-      </c>
-      <c r="D485" s="44"/>
-      <c r="E485" s="44"/>
-      <c r="F485" s="46"/>
-      <c r="G485" s="47" t="s">
-        <v>1182</v>
-      </c>
-      <c r="H485" s="44"/>
-      <c r="I485" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J485" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="486" customFormat="1" ht="14.4" spans="1:10">
-      <c r="A486" s="48" t="s">
-        <v>1183</v>
-      </c>
-      <c r="B486" s="44" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C486" s="44" t="s">
-        <v>232</v>
-      </c>
-      <c r="D486" s="44"/>
-      <c r="E486" s="44"/>
-      <c r="F486" s="46"/>
-      <c r="G486" s="47" t="s">
-        <v>1184</v>
-      </c>
-      <c r="H486" s="44"/>
-      <c r="I486" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J486" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="487" customFormat="1" spans="1:10">
-      <c r="A487" s="48" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B487" s="44" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C487" s="44" t="s">
-        <v>232</v>
-      </c>
-      <c r="D487" s="44"/>
-      <c r="E487" s="44"/>
-      <c r="F487" s="46"/>
-      <c r="G487" s="47" t="s">
-        <v>1186</v>
-      </c>
-      <c r="H487" s="44"/>
-      <c r="I487" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J487" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="488" customFormat="1" ht="27.6" spans="1:10">
-      <c r="A488" s="44" t="s">
-        <v>1187</v>
-      </c>
-      <c r="B488" s="44" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C488" s="44" t="s">
-        <v>553</v>
-      </c>
-      <c r="D488" s="44"/>
-      <c r="E488" s="44"/>
-      <c r="F488" s="46"/>
-      <c r="G488" s="47" t="s">
-        <v>1188</v>
-      </c>
-      <c r="H488" s="44"/>
-      <c r="I488" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J488" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="489" customFormat="1" ht="27.6" spans="1:10">
-      <c r="A489" s="44" t="s">
-        <v>1189</v>
-      </c>
-      <c r="B489" s="44" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C489" s="44" t="s">
-        <v>553</v>
-      </c>
-      <c r="D489" s="44"/>
-      <c r="E489" s="44"/>
-      <c r="F489" s="46"/>
-      <c r="G489" s="47" t="s">
-        <v>1188</v>
-      </c>
-      <c r="H489" s="44"/>
-      <c r="I489" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J489" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="490" customFormat="1" ht="27.6" spans="1:10">
-      <c r="A490" s="44" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B490" s="44" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C490" s="44" t="s">
-        <v>553</v>
-      </c>
-      <c r="D490" s="44"/>
-      <c r="E490" s="44"/>
-      <c r="F490" s="46"/>
-      <c r="G490" s="47" t="s">
-        <v>1191</v>
-      </c>
-      <c r="H490" s="44"/>
-      <c r="I490" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J490" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="491" customFormat="1" ht="42.6" spans="1:10">
-      <c r="A491" s="44" t="s">
-        <v>1192</v>
-      </c>
-      <c r="B491" s="44" t="s">
-        <v>1193</v>
-      </c>
-      <c r="C491" s="44" t="s">
-        <v>553</v>
-      </c>
-      <c r="D491" s="44"/>
-      <c r="E491" s="44"/>
-      <c r="F491" s="46"/>
-      <c r="G491" s="47" t="s">
-        <v>1194</v>
-      </c>
-      <c r="H491" s="44"/>
-      <c r="I491" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J491" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="492" customFormat="1" ht="14.4" spans="1:10">
-      <c r="A492" s="44" t="s">
-        <v>1195</v>
-      </c>
-      <c r="B492" s="44" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C492" s="44" t="s">
-        <v>156</v>
-      </c>
-      <c r="D492" s="44"/>
-      <c r="E492" s="44"/>
-      <c r="F492" s="46"/>
-      <c r="G492" s="47" t="s">
-        <v>1197</v>
-      </c>
-      <c r="H492" s="44"/>
-      <c r="I492" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J492" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="493" customFormat="1" ht="28.2" spans="1:10">
-      <c r="A493" s="44" t="s">
-        <v>1198</v>
-      </c>
-      <c r="B493" s="44" t="s">
-        <v>1199</v>
-      </c>
-      <c r="C493" s="44" t="s">
-        <v>156</v>
-      </c>
-      <c r="D493" s="44"/>
-      <c r="E493" s="44"/>
-      <c r="F493" s="46"/>
-      <c r="G493" s="47" t="s">
-        <v>1200</v>
-      </c>
-      <c r="H493" s="44"/>
-      <c r="I493" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J493" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="494" customFormat="1" spans="1:10">
-      <c r="A494" s="44" t="s">
-        <v>1201</v>
-      </c>
-      <c r="B494" s="44" t="s">
-        <v>1109</v>
-      </c>
-      <c r="C494" s="50" t="s">
-        <v>1107</v>
-      </c>
-      <c r="D494" s="44"/>
-      <c r="E494" s="44"/>
-      <c r="F494" s="46"/>
-      <c r="G494" s="47" t="s">
-        <v>1202</v>
-      </c>
-      <c r="H494" s="44"/>
-      <c r="I494" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J494" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="495" customFormat="1" ht="83.4" spans="1:10">
-      <c r="A495" s="44" t="s">
-        <v>1203</v>
-      </c>
-      <c r="B495" s="44" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C495" s="44" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D495" s="44"/>
-      <c r="E495" s="44"/>
-      <c r="F495" s="46"/>
-      <c r="G495" s="47" t="s">
-        <v>1204</v>
-      </c>
-      <c r="H495" s="44"/>
-      <c r="I495" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J495" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="496" customFormat="1" ht="114.6" spans="1:10">
-      <c r="A496" s="44" t="s">
-        <v>1205</v>
-      </c>
-      <c r="B496" s="51" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C496" s="44" t="s">
-        <v>133</v>
-      </c>
-      <c r="D496" s="44"/>
-      <c r="E496" s="44"/>
-      <c r="F496" s="46"/>
-      <c r="G496" s="47" t="s">
-        <v>1206</v>
-      </c>
-      <c r="H496" s="44"/>
-      <c r="I496" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J496" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="497" customFormat="1" ht="97.2" spans="1:10">
-      <c r="A497" s="44" t="s">
-        <v>1207</v>
-      </c>
-      <c r="B497" s="51" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C497" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="D497" s="44"/>
-      <c r="E497" s="44"/>
-      <c r="F497" s="46"/>
-      <c r="G497" s="47" t="s">
-        <v>1208</v>
-      </c>
-      <c r="H497" s="44"/>
-      <c r="I497" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J497" s="44" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="498" customFormat="1" ht="29" customHeight="1" spans="1:10">
-      <c r="A498" s="44" t="s">
-        <v>1209</v>
-      </c>
-      <c r="B498" s="51" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C498" s="44" t="s">
-        <v>321</v>
-      </c>
-      <c r="D498" s="44"/>
-      <c r="E498" s="44"/>
-      <c r="F498" s="46"/>
-      <c r="G498" s="52" t="s">
-        <v>1210</v>
-      </c>
-      <c r="H498" s="44"/>
-      <c r="I498" s="44" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J498" s="44" t="s">
-        <v>1156</v>
       </c>
     </row>
   </sheetData>

--- a/project_list.xlsx
+++ b/project_list.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3103" uniqueCount="1152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3138" uniqueCount="1168">
   <si>
     <t>项目名称</t>
   </si>
@@ -1936,91 +1936,52 @@
     <t>12.520979,107.109840</t>
   </si>
   <si>
-    <t>Elemtal ergy-Canada-Boulder-Elkhart-94MW</t>
-  </si>
-  <si>
-    <t>49.955330,-120.244800</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>Everwind-Bear Lake-11wtg</t>
-  </si>
-  <si>
-    <t>44.783042,-64.211912</t>
+    <t>Chile-Faro del sur-380MWChile</t>
+  </si>
+  <si>
+    <t>-52.854132,-70.938997</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>Colbun-Chile-Horizonte expsion-180MW</t>
+  </si>
+  <si>
+    <t>-24.959448,-69.835625</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>gie-Chile-tre Rios-310MW</t>
+  </si>
+  <si>
+    <t>-37.604160,-72.421870</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Geradora Metropolitana-Chile-El Almdro-144MW_风机</t>
+  </si>
+  <si>
+    <t>-37.700642,-72.693102</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>OPDergy-Chile-Dañicalqui-95MWChile</t>
+  </si>
+  <si>
+    <t>-37.044454,-72.133284</t>
+  </si>
+  <si>
+    <t>95</t>
   </si>
   <si>
     <t>182/8.0</t>
-  </si>
-  <si>
-    <t>Everwind-Kmtnuk-63/2wtg</t>
-  </si>
-  <si>
-    <t>45.546079,-63.292279</t>
-  </si>
-  <si>
-    <t>Everwind-Upperafton-22wtg</t>
-  </si>
-  <si>
-    <t>45.542357,-61.669006</t>
-  </si>
-  <si>
-    <t>196</t>
-  </si>
-  <si>
-    <t>Everwind-Windy-63/2wtg</t>
-  </si>
-  <si>
-    <t>45.559363,-63.460979</t>
-  </si>
-  <si>
-    <t>Chile-Faro del sur-380MWChile</t>
-  </si>
-  <si>
-    <t>-52.854132,-70.938997</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>Colbun-Chile-Horizonte expsion-180MW</t>
-  </si>
-  <si>
-    <t>-24.959448,-69.835625</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>gie-Chile-tre Rios-310MW</t>
-  </si>
-  <si>
-    <t>-37.604160,-72.421870</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Geradora Metropolitana-Chile-El Almdro-144MW_风机</t>
-  </si>
-  <si>
-    <t>-37.700642,-72.693102</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>OPDergy-Chile-Dañicalqui-95MWChile</t>
-  </si>
-  <si>
-    <t>-37.044454,-72.133284</t>
-  </si>
-  <si>
-    <t>95</t>
   </si>
   <si>
     <t>cro-Croatia-Ljut-296MW</t>
@@ -3661,6 +3622,93 @@
   </si>
   <si>
     <t>-37.59901, -72.53589</t>
+  </si>
+  <si>
+    <t>Abraxas-Canada-green ammonia</t>
+  </si>
+  <si>
+    <t>49.30619,-55.631697</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Capstone Infrastructure-Canada-Highland Valley</t>
+  </si>
+  <si>
+    <t>49.282729,-123.120738</t>
+  </si>
+  <si>
+    <t>Capstone Infrastructure-Canada-Mount Mabel</t>
+  </si>
+  <si>
+    <t>48.428421,-123.365644</t>
+  </si>
+  <si>
+    <t>Capstone Infrastructure-Canada-Yeyus Energy</t>
+  </si>
+  <si>
+    <t>53.917064,-122.749672</t>
+  </si>
+  <si>
+    <t>Elemental Energy-Canada-Boulder-Elkhart</t>
+  </si>
+  <si>
+    <t>50.674522,-120.327267</t>
+  </si>
+  <si>
+    <t>Elemental Energy-Canada-Greyback</t>
+  </si>
+  <si>
+    <t>49.614055556,-119.368325</t>
+  </si>
+  <si>
+    <t>Elemental Energy-Canada-Nicola</t>
+  </si>
+  <si>
+    <t>49.952333,-119.9565</t>
+  </si>
+  <si>
+    <t>Everwind-Canada-Bear Lake</t>
+  </si>
+  <si>
+    <t>44.783028,-64.205083</t>
+  </si>
+  <si>
+    <t>Everwind-Canada-Kmtnuk</t>
+  </si>
+  <si>
+    <t>45.544588,-63.283732</t>
+  </si>
+  <si>
+    <t>Everwind-Canada-Upper Afton</t>
+  </si>
+  <si>
+    <t>45.559598,-61.674832</t>
+  </si>
+  <si>
+    <t>Everwind-Canada-Windy Ridge</t>
+  </si>
+  <si>
+    <t>45.550782,-63.434237</t>
+  </si>
+  <si>
+    <t>Innergex Renewable Energy-Canada-Hedley</t>
+  </si>
+  <si>
+    <t>49.5381,-120.0019</t>
+  </si>
+  <si>
+    <t>Innergex Renewable Energy-Canada-Stewart Creek</t>
+  </si>
+  <si>
+    <t>49.887952,-119.496011</t>
+  </si>
+  <si>
+    <t>Kruger Energy-Canada-Corner Brook</t>
+  </si>
+  <si>
+    <t>47.560539,-52.712830</t>
   </si>
 </sst>
 </file>
@@ -3886,6 +3934,18 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Cambria"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF262626"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -3894,18 +3954,6 @@
       <sz val="10"/>
       <color rgb="FF262626"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Cambria"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -4528,7 +4576,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4657,6 +4705,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -4969,8 +5026,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ProjectUploadTable" displayName="ProjectUploadTable" ref="A1:J474">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J474" etc:filterBottomFollowUsedRange="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ProjectUploadTable" displayName="ProjectUploadTable" ref="A1:J483">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J483" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="10">
     <tableColumn id="1" name="项目名称" dataDxfId="0"/>
     <tableColumn id="2" name="坐标(纬度,经度)" dataDxfId="1"/>
@@ -5136,7 +5193,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J474"/>
+  <dimension ref="A1:J483"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="46.3666666666667" style="1" customWidth="1"/>
@@ -5215,7 +5272,6 @@
       <c r="D3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="1"/>
       <c r="I3" s="1" t="s">
         <v>14</v>
       </c>
@@ -5236,7 +5292,6 @@
       <c r="D4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="1"/>
       <c r="I4" s="1" t="s">
         <v>14</v>
       </c>
@@ -5257,7 +5312,6 @@
       <c r="D5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="1"/>
       <c r="I5" s="1" t="s">
         <v>14</v>
       </c>
@@ -5278,7 +5332,6 @@
       <c r="D6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="1"/>
       <c r="I6" s="1" t="s">
         <v>14</v>
       </c>
@@ -5299,7 +5352,6 @@
       <c r="D7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="1"/>
       <c r="I7" s="1" t="s">
         <v>14</v>
       </c>
@@ -5320,7 +5372,6 @@
       <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="1"/>
       <c r="I8" s="1" t="s">
         <v>14</v>
       </c>
@@ -5341,7 +5392,6 @@
       <c r="D9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="1"/>
       <c r="I9" s="1" t="s">
         <v>14</v>
       </c>
@@ -5362,7 +5412,6 @@
       <c r="D10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="1"/>
       <c r="I10" s="1" t="s">
         <v>14</v>
       </c>
@@ -5383,7 +5432,6 @@
       <c r="D11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="1"/>
       <c r="I11" s="1" t="s">
         <v>14</v>
       </c>
@@ -5404,7 +5452,6 @@
       <c r="D12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="1"/>
       <c r="I12" s="1" t="s">
         <v>14</v>
       </c>
@@ -5425,7 +5472,6 @@
       <c r="D13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="1"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -5446,7 +5492,6 @@
       <c r="D14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="1"/>
       <c r="I14" s="1" t="s">
         <v>14</v>
       </c>
@@ -5467,7 +5512,6 @@
       <c r="D15" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="1"/>
       <c r="I15" s="1" t="s">
         <v>14</v>
       </c>
@@ -5488,7 +5532,6 @@
       <c r="D16" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="1"/>
       <c r="I16" s="1" t="s">
         <v>14</v>
       </c>
@@ -5509,7 +5552,6 @@
       <c r="D17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="1"/>
       <c r="I17" s="1" t="s">
         <v>14</v>
       </c>
@@ -5530,7 +5572,6 @@
       <c r="D18" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="1"/>
       <c r="I18" s="1" t="s">
         <v>14</v>
       </c>
@@ -5551,7 +5592,6 @@
       <c r="D19" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="1"/>
       <c r="I19" s="1" t="s">
         <v>14</v>
       </c>
@@ -5572,7 +5612,6 @@
       <c r="D20" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="1"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -5593,7 +5632,6 @@
       <c r="D21" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="1"/>
       <c r="I21" s="1" t="s">
         <v>14</v>
       </c>
@@ -5614,7 +5652,6 @@
       <c r="D22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="1"/>
       <c r="I22" s="1" t="s">
         <v>14</v>
       </c>
@@ -5635,7 +5672,6 @@
       <c r="D23" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="1"/>
       <c r="I23" s="1" t="s">
         <v>14</v>
       </c>
@@ -5656,7 +5692,6 @@
       <c r="D24" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="1"/>
       <c r="I24" s="1" t="s">
         <v>14</v>
       </c>
@@ -5677,7 +5712,6 @@
       <c r="D25" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E25" s="1"/>
       <c r="I25" s="1" t="s">
         <v>14</v>
       </c>
@@ -5698,7 +5732,6 @@
       <c r="D26" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E26" s="1"/>
       <c r="I26" s="1" t="s">
         <v>14</v>
       </c>
@@ -5719,7 +5752,6 @@
       <c r="D27" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="1"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -5740,7 +5772,6 @@
       <c r="D28" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="1"/>
       <c r="I28" s="1" t="s">
         <v>93</v>
       </c>
@@ -5761,7 +5792,6 @@
       <c r="D29" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E29" s="1"/>
       <c r="I29" s="1" t="s">
         <v>14</v>
       </c>
@@ -5782,7 +5812,6 @@
       <c r="D30" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E30" s="1"/>
       <c r="I30" s="1" t="s">
         <v>14</v>
       </c>
@@ -5803,7 +5832,6 @@
       <c r="D31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E31" s="1"/>
       <c r="I31" s="1" t="s">
         <v>14</v>
       </c>
@@ -5824,7 +5852,6 @@
       <c r="D32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E32" s="1"/>
       <c r="I32" s="1" t="s">
         <v>14</v>
       </c>
@@ -5845,7 +5872,6 @@
       <c r="D33" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E33" s="1"/>
       <c r="I33" s="1" t="s">
         <v>14</v>
       </c>
@@ -5866,7 +5892,6 @@
       <c r="D34" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E34" s="1"/>
       <c r="I34" s="1" t="s">
         <v>14</v>
       </c>
@@ -5887,7 +5912,6 @@
       <c r="D35" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E35" s="1"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -5908,7 +5932,6 @@
       <c r="D36" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E36" s="1"/>
       <c r="I36" s="1" t="s">
         <v>14</v>
       </c>
@@ -5929,7 +5952,6 @@
       <c r="D37" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="1"/>
       <c r="I37" s="1" t="s">
         <v>14</v>
       </c>
@@ -5950,7 +5972,6 @@
       <c r="D38" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E38" s="1"/>
       <c r="I38" s="1" t="s">
         <v>14</v>
       </c>
@@ -5971,7 +5992,6 @@
       <c r="D39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E39" s="1"/>
       <c r="I39" s="1" t="s">
         <v>14</v>
       </c>
@@ -5992,7 +6012,6 @@
       <c r="D40" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E40" s="1"/>
       <c r="I40" s="1" t="s">
         <v>14</v>
       </c>
@@ -6013,7 +6032,6 @@
       <c r="D41" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E41" s="1"/>
       <c r="I41" s="1" t="s">
         <v>14</v>
       </c>
@@ -6034,7 +6052,6 @@
       <c r="D42" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E42" s="1"/>
       <c r="I42" s="1" t="s">
         <v>14</v>
       </c>
@@ -6055,7 +6072,6 @@
       <c r="D43" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E43" s="1"/>
       <c r="I43" s="1" t="s">
         <v>14</v>
       </c>
@@ -6076,7 +6092,6 @@
       <c r="D44" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E44" s="1"/>
       <c r="I44" s="1" t="s">
         <v>14</v>
       </c>
@@ -6097,7 +6112,6 @@
       <c r="D45" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E45" s="1"/>
       <c r="I45" s="1" t="s">
         <v>14</v>
       </c>
@@ -6118,7 +6132,6 @@
       <c r="D46" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E46" s="1"/>
       <c r="I46" s="1" t="s">
         <v>14</v>
       </c>
@@ -6139,7 +6152,6 @@
       <c r="D47" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E47" s="1"/>
       <c r="I47" s="1" t="s">
         <v>14</v>
       </c>
@@ -6160,7 +6172,6 @@
       <c r="D48" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E48" s="1"/>
       <c r="I48" s="1" t="s">
         <v>14</v>
       </c>
@@ -6181,7 +6192,6 @@
       <c r="D49" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E49" s="1"/>
       <c r="I49" s="1" t="s">
         <v>14</v>
       </c>
@@ -6202,7 +6212,6 @@
       <c r="D50" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E50" s="1"/>
       <c r="I50" s="1" t="s">
         <v>14</v>
       </c>
@@ -6223,7 +6232,6 @@
       <c r="D51" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E51" s="1"/>
       <c r="I51" s="1" t="s">
         <v>14</v>
       </c>
@@ -6244,7 +6252,6 @@
       <c r="D52" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E52" s="1"/>
       <c r="I52" s="1" t="s">
         <v>14</v>
       </c>
@@ -6265,7 +6272,6 @@
       <c r="D53" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E53" s="1"/>
       <c r="I53" s="1" t="s">
         <v>14</v>
       </c>
@@ -6286,7 +6292,6 @@
       <c r="D54" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E54" s="1"/>
       <c r="I54" s="1" t="s">
         <v>14</v>
       </c>
@@ -6307,7 +6312,6 @@
       <c r="D55" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E55" s="1"/>
       <c r="I55" s="1" t="s">
         <v>14</v>
       </c>
@@ -6328,7 +6332,6 @@
       <c r="D56" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E56" s="1"/>
       <c r="I56" s="1" t="s">
         <v>14</v>
       </c>
@@ -6349,7 +6352,6 @@
       <c r="D57" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E57" s="1"/>
       <c r="I57" s="1" t="s">
         <v>14</v>
       </c>
@@ -6370,7 +6372,6 @@
       <c r="D58" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E58" s="1"/>
       <c r="I58" s="1" t="s">
         <v>14</v>
       </c>
@@ -6391,7 +6392,6 @@
       <c r="D59" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E59" s="1"/>
       <c r="I59" s="1" t="s">
         <v>14</v>
       </c>
@@ -6412,7 +6412,6 @@
       <c r="D60" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E60" s="1"/>
       <c r="I60" s="1" t="s">
         <v>14</v>
       </c>
@@ -6433,7 +6432,6 @@
       <c r="D61" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E61" s="1"/>
       <c r="I61" s="1" t="s">
         <v>14</v>
       </c>
@@ -6454,7 +6452,6 @@
       <c r="D62" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="E62" s="1"/>
       <c r="I62" s="1" t="s">
         <v>14</v>
       </c>
@@ -6475,7 +6472,6 @@
       <c r="D63" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E63" s="1"/>
       <c r="I63" s="1" t="s">
         <v>14</v>
       </c>
@@ -6496,7 +6492,6 @@
       <c r="D64" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E64" s="1"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -6517,7 +6512,6 @@
       <c r="D65" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E65" s="1"/>
       <c r="I65" s="1" t="s">
         <v>14</v>
       </c>
@@ -6538,7 +6532,6 @@
       <c r="D66" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E66" s="1"/>
       <c r="I66" s="1" t="s">
         <v>14</v>
       </c>
@@ -6559,7 +6552,6 @@
       <c r="D67" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E67" s="1"/>
       <c r="I67" s="1" t="s">
         <v>14</v>
       </c>
@@ -6580,7 +6572,6 @@
       <c r="D68" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E68" s="1"/>
       <c r="I68" s="1" t="s">
         <v>14</v>
       </c>
@@ -6601,7 +6592,6 @@
       <c r="D69" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E69" s="1"/>
       <c r="I69" s="1" t="s">
         <v>14</v>
       </c>
@@ -6622,7 +6612,6 @@
       <c r="D70" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="E70" s="1"/>
       <c r="I70" s="1" t="s">
         <v>14</v>
       </c>
@@ -6643,7 +6632,6 @@
       <c r="D71" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E71" s="1"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -6664,7 +6652,6 @@
       <c r="D72" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E72" s="1"/>
       <c r="I72" s="1" t="s">
         <v>14</v>
       </c>
@@ -6685,7 +6672,6 @@
       <c r="D73" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E73" s="1"/>
       <c r="I73" s="1" t="s">
         <v>14</v>
       </c>
@@ -6706,7 +6692,6 @@
       <c r="D74" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E74" s="1"/>
       <c r="I74" s="1" t="s">
         <v>14</v>
       </c>
@@ -6727,7 +6712,6 @@
       <c r="D75" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="E75" s="1"/>
       <c r="I75" s="1" t="s">
         <v>14</v>
       </c>
@@ -6748,7 +6732,6 @@
       <c r="D76" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E76" s="1"/>
       <c r="I76" s="1" t="s">
         <v>14</v>
       </c>
@@ -6769,7 +6752,6 @@
       <c r="D77" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E77" s="1"/>
       <c r="I77" s="1" t="s">
         <v>14</v>
       </c>
@@ -6790,7 +6772,6 @@
       <c r="D78" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E78" s="1"/>
       <c r="I78" s="1" t="s">
         <v>14</v>
       </c>
@@ -6811,7 +6792,6 @@
       <c r="D79" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E79" s="1"/>
       <c r="I79" s="1" t="s">
         <v>14</v>
       </c>
@@ -6832,7 +6812,6 @@
       <c r="D80" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E80" s="1"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -6853,7 +6832,6 @@
       <c r="D81" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E81" s="1"/>
       <c r="I81" s="1" t="s">
         <v>14</v>
       </c>
@@ -6874,7 +6852,6 @@
       <c r="D82" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E82" s="1"/>
       <c r="I82" s="1" t="s">
         <v>14</v>
       </c>
@@ -6895,7 +6872,6 @@
       <c r="D83" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E83" s="1"/>
       <c r="I83" s="1" t="s">
         <v>14</v>
       </c>
@@ -6916,7 +6892,6 @@
       <c r="D84" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E84" s="1"/>
       <c r="I84" s="1" t="s">
         <v>14</v>
       </c>
@@ -6937,7 +6912,6 @@
       <c r="D85" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="E85" s="1"/>
       <c r="I85" s="1" t="s">
         <v>14</v>
       </c>
@@ -6958,7 +6932,6 @@
       <c r="D86" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E86" s="1"/>
       <c r="I86" s="1" t="s">
         <v>14</v>
       </c>
@@ -6979,7 +6952,6 @@
       <c r="D87" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E87" s="1"/>
       <c r="I87" s="1" t="s">
         <v>14</v>
       </c>
@@ -7000,7 +6972,6 @@
       <c r="D88" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E88" s="1"/>
       <c r="I88" s="1" t="s">
         <v>14</v>
       </c>
@@ -7021,7 +6992,6 @@
       <c r="D89" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E89" s="1"/>
       <c r="I89" s="1" t="s">
         <v>14</v>
       </c>
@@ -7042,7 +7012,6 @@
       <c r="D90" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E90" s="1"/>
       <c r="I90" s="1" t="s">
         <v>14</v>
       </c>
@@ -7063,7 +7032,6 @@
       <c r="D91" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E91" s="1"/>
       <c r="I91" s="1" t="s">
         <v>14</v>
       </c>
@@ -7084,7 +7052,6 @@
       <c r="D92" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E92" s="1"/>
       <c r="I92" s="1" t="s">
         <v>14</v>
       </c>
@@ -7105,7 +7072,6 @@
       <c r="D93" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E93" s="1"/>
       <c r="I93" s="1" t="s">
         <v>14</v>
       </c>
@@ -7126,7 +7092,6 @@
       <c r="D94" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E94" s="1"/>
       <c r="I94" s="1" t="s">
         <v>14</v>
       </c>
@@ -7147,7 +7112,6 @@
       <c r="D95" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E95" s="1"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -7168,7 +7132,6 @@
       <c r="D96" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E96" s="1"/>
       <c r="I96" s="1" t="s">
         <v>14</v>
       </c>
@@ -7189,7 +7152,6 @@
       <c r="D97" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E97" s="1"/>
       <c r="I97" s="1" t="s">
         <v>14</v>
       </c>
@@ -7210,7 +7172,6 @@
       <c r="D98" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="E98" s="1"/>
       <c r="I98" s="1" t="s">
         <v>14</v>
       </c>
@@ -7231,7 +7192,6 @@
       <c r="D99" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="E99" s="1"/>
       <c r="I99" s="1" t="s">
         <v>14</v>
       </c>
@@ -7252,7 +7212,6 @@
       <c r="D100" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E100" s="1"/>
       <c r="I100" s="1" t="s">
         <v>14</v>
       </c>
@@ -7273,7 +7232,6 @@
       <c r="D101" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E101" s="1"/>
       <c r="I101" s="1" t="s">
         <v>14</v>
       </c>
@@ -7294,7 +7252,6 @@
       <c r="D102" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E102" s="1"/>
       <c r="I102" s="1" t="s">
         <v>14</v>
       </c>
@@ -7315,7 +7272,6 @@
       <c r="D103" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E103" s="1"/>
       <c r="I103" s="1" t="s">
         <v>14</v>
       </c>
@@ -7336,7 +7292,6 @@
       <c r="D104" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E104" s="1"/>
       <c r="I104" s="1" t="s">
         <v>14</v>
       </c>
@@ -7357,7 +7312,6 @@
       <c r="D105" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E105" s="1"/>
       <c r="I105" s="1" t="s">
         <v>14</v>
       </c>
@@ -7378,7 +7332,6 @@
       <c r="D106" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E106" s="1"/>
       <c r="I106" s="1" t="s">
         <v>14</v>
       </c>
@@ -7399,7 +7352,6 @@
       <c r="D107" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="E107" s="1"/>
       <c r="I107" s="1" t="s">
         <v>14</v>
       </c>
@@ -7420,7 +7372,6 @@
       <c r="D108" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E108" s="1"/>
       <c r="I108" s="1" t="s">
         <v>14</v>
       </c>
@@ -7441,7 +7392,6 @@
       <c r="D109" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="E109" s="1"/>
       <c r="I109" s="1" t="s">
         <v>14</v>
       </c>
@@ -7462,7 +7412,6 @@
       <c r="D110" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E110" s="1"/>
       <c r="I110" s="1" t="s">
         <v>14</v>
       </c>
@@ -7483,7 +7432,6 @@
       <c r="D111" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="E111" s="1"/>
       <c r="I111" s="1" t="s">
         <v>14</v>
       </c>
@@ -7504,7 +7452,6 @@
       <c r="D112" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E112" s="1"/>
       <c r="I112" s="1" t="s">
         <v>14</v>
       </c>
@@ -7525,7 +7472,6 @@
       <c r="D113" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="E113" s="1"/>
       <c r="I113" s="1" t="s">
         <v>14</v>
       </c>
@@ -7546,7 +7492,6 @@
       <c r="D114" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E114" s="1"/>
       <c r="I114" s="1" t="s">
         <v>14</v>
       </c>
@@ -7567,7 +7512,6 @@
       <c r="D115" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E115" s="1"/>
       <c r="I115" s="1" t="s">
         <v>14</v>
       </c>
@@ -7588,7 +7532,6 @@
       <c r="D116" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E116" s="1"/>
       <c r="I116" s="1" t="s">
         <v>14</v>
       </c>
@@ -7609,7 +7552,6 @@
       <c r="D117" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E117" s="1"/>
       <c r="I117" s="1" t="s">
         <v>14</v>
       </c>
@@ -7630,7 +7572,6 @@
       <c r="D118" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E118" s="1"/>
       <c r="I118" s="1" t="s">
         <v>14</v>
       </c>
@@ -7651,7 +7592,6 @@
       <c r="D119" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="E119" s="1"/>
       <c r="I119" s="1" t="s">
         <v>14</v>
       </c>
@@ -7672,7 +7612,6 @@
       <c r="D120" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E120" s="1"/>
       <c r="I120" s="1" t="s">
         <v>14</v>
       </c>
@@ -7693,7 +7632,6 @@
       <c r="D121" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="E121" s="1"/>
       <c r="I121" s="1" t="s">
         <v>14</v>
       </c>
@@ -7714,7 +7652,6 @@
       <c r="D122" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E122" s="1"/>
       <c r="I122" s="1" t="s">
         <v>14</v>
       </c>
@@ -7735,7 +7672,6 @@
       <c r="D123" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E123" s="1"/>
       <c r="I123" s="1" t="s">
         <v>14</v>
       </c>
@@ -7756,7 +7692,6 @@
       <c r="D124" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E124" s="1"/>
       <c r="I124" s="1" t="s">
         <v>14</v>
       </c>
@@ -7777,7 +7712,6 @@
       <c r="D125" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E125" s="1"/>
       <c r="I125" s="1" t="s">
         <v>14</v>
       </c>
@@ -7798,7 +7732,6 @@
       <c r="D126" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="E126" s="1"/>
       <c r="I126" s="1" t="s">
         <v>14</v>
       </c>
@@ -7819,7 +7752,6 @@
       <c r="D127" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="E127" s="1"/>
       <c r="I127" s="1" t="s">
         <v>14</v>
       </c>
@@ -7840,7 +7772,6 @@
       <c r="D128" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E128" s="1"/>
       <c r="I128" s="1" t="s">
         <v>14</v>
       </c>
@@ -7861,7 +7792,6 @@
       <c r="D129" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E129" s="1"/>
       <c r="I129" s="1" t="s">
         <v>14</v>
       </c>
@@ -7882,7 +7812,6 @@
       <c r="D130" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="E130" s="1"/>
       <c r="I130" s="1" t="s">
         <v>14</v>
       </c>
@@ -7903,7 +7832,6 @@
       <c r="D131" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="E131" s="1"/>
       <c r="I131" s="1" t="s">
         <v>14</v>
       </c>
@@ -7924,7 +7852,6 @@
       <c r="D132" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="E132" s="1"/>
       <c r="I132" s="1" t="s">
         <v>14</v>
       </c>
@@ -7945,7 +7872,6 @@
       <c r="D133" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="E133" s="1"/>
       <c r="I133" s="1" t="s">
         <v>14</v>
       </c>
@@ -7966,7 +7892,6 @@
       <c r="D134" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E134" s="1"/>
       <c r="I134" s="1" t="s">
         <v>14</v>
       </c>
@@ -7987,7 +7912,6 @@
       <c r="D135" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="E135" s="1"/>
       <c r="I135" s="1" t="s">
         <v>14</v>
       </c>
@@ -8008,7 +7932,6 @@
       <c r="D136" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E136" s="1"/>
       <c r="I136" s="1" t="s">
         <v>14</v>
       </c>
@@ -8029,7 +7952,6 @@
       <c r="D137" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="E137" s="1"/>
       <c r="I137" s="1" t="s">
         <v>14</v>
       </c>
@@ -8050,7 +7972,6 @@
       <c r="D138" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E138" s="1"/>
       <c r="I138" s="1" t="s">
         <v>14</v>
       </c>
@@ -8071,7 +7992,6 @@
       <c r="D139" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="E139" s="1"/>
       <c r="I139" s="1" t="s">
         <v>14</v>
       </c>
@@ -8092,7 +8012,6 @@
       <c r="D140" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="E140" s="1"/>
       <c r="I140" s="1" t="s">
         <v>14</v>
       </c>
@@ -8113,7 +8032,6 @@
       <c r="D141" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="E141" s="1"/>
       <c r="I141" s="1" t="s">
         <v>14</v>
       </c>
@@ -8134,7 +8052,6 @@
       <c r="D142" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E142" s="1"/>
       <c r="I142" s="1" t="s">
         <v>14</v>
       </c>
@@ -8155,7 +8072,6 @@
       <c r="D143" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E143" s="1"/>
       <c r="I143" s="1" t="s">
         <v>14</v>
       </c>
@@ -8176,7 +8092,6 @@
       <c r="D144" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="E144" s="1"/>
       <c r="I144" s="1" t="s">
         <v>14</v>
       </c>
@@ -8197,7 +8112,6 @@
       <c r="D145" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="E145" s="1"/>
       <c r="I145" s="1" t="s">
         <v>14</v>
       </c>
@@ -8218,7 +8132,6 @@
       <c r="D146" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="E146" s="1"/>
       <c r="I146" s="1" t="s">
         <v>93</v>
       </c>
@@ -8239,7 +8152,6 @@
       <c r="D147" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E147" s="1"/>
       <c r="I147" s="1" t="s">
         <v>93</v>
       </c>
@@ -8260,7 +8172,6 @@
       <c r="D148" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E148" s="1"/>
       <c r="I148" s="1" t="s">
         <v>93</v>
       </c>
@@ -8281,7 +8192,6 @@
       <c r="D149" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="E149" s="1"/>
       <c r="I149" s="1" t="s">
         <v>93</v>
       </c>
@@ -8302,7 +8212,6 @@
       <c r="D150" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E150" s="1"/>
       <c r="I150" s="1" t="s">
         <v>93</v>
       </c>
@@ -8323,7 +8232,6 @@
       <c r="D151" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="E151" s="1"/>
       <c r="I151" s="1" t="s">
         <v>93</v>
       </c>
@@ -8344,7 +8252,6 @@
       <c r="D152" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E152" s="1"/>
       <c r="I152" s="1" t="s">
         <v>93</v>
       </c>
@@ -8365,7 +8272,6 @@
       <c r="D153" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E153" s="1"/>
       <c r="I153" s="1" t="s">
         <v>93</v>
       </c>
@@ -8386,7 +8292,6 @@
       <c r="D154" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="E154" s="1"/>
       <c r="I154" s="1" t="s">
         <v>93</v>
       </c>
@@ -8407,7 +8312,6 @@
       <c r="D155" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E155" s="1"/>
       <c r="I155" s="1" t="s">
         <v>93</v>
       </c>
@@ -8428,7 +8332,6 @@
       <c r="D156" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="E156" s="1"/>
       <c r="I156" s="1" t="s">
         <v>93</v>
       </c>
@@ -8449,7 +8352,6 @@
       <c r="D157" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E157" s="1"/>
       <c r="I157" s="1" t="s">
         <v>93</v>
       </c>
@@ -8470,7 +8372,6 @@
       <c r="D158" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E158" s="1"/>
       <c r="I158" s="1" t="s">
         <v>93</v>
       </c>
@@ -8491,7 +8392,6 @@
       <c r="D159" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="E159" s="1"/>
       <c r="I159" s="1" t="s">
         <v>93</v>
       </c>
@@ -8512,7 +8412,6 @@
       <c r="D160" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E160" s="1"/>
       <c r="I160" s="1" t="s">
         <v>93</v>
       </c>
@@ -8533,7 +8432,6 @@
       <c r="D161" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E161" s="1"/>
       <c r="I161" s="1" t="s">
         <v>14</v>
       </c>
@@ -8554,7 +8452,6 @@
       <c r="D162" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="E162" s="1"/>
       <c r="I162" s="1" t="s">
         <v>14</v>
       </c>
@@ -8575,7 +8472,6 @@
       <c r="D163" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E163" s="1"/>
       <c r="I163" s="1" t="s">
         <v>14</v>
       </c>
@@ -8596,7 +8492,6 @@
       <c r="D164" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="E164" s="1"/>
       <c r="I164" s="1" t="s">
         <v>14</v>
       </c>
@@ -8617,7 +8512,6 @@
       <c r="D165" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E165" s="1"/>
       <c r="I165" s="1" t="s">
         <v>14</v>
       </c>
@@ -8638,7 +8532,6 @@
       <c r="D166" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E166" s="1"/>
       <c r="I166" s="1" t="s">
         <v>14</v>
       </c>
@@ -8659,7 +8552,6 @@
       <c r="D167" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="E167" s="1"/>
       <c r="I167" s="1" t="s">
         <v>14</v>
       </c>
@@ -8680,7 +8572,6 @@
       <c r="D168" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="E168" s="1"/>
       <c r="I168" s="1" t="s">
         <v>14</v>
       </c>
@@ -8701,7 +8592,6 @@
       <c r="D169" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="E169" s="1"/>
       <c r="I169" s="1" t="s">
         <v>14</v>
       </c>
@@ -8722,7 +8612,6 @@
       <c r="D170" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="E170" s="1"/>
       <c r="I170" s="1" t="s">
         <v>14</v>
       </c>
@@ -8743,7 +8632,6 @@
       <c r="D171" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="E171" s="1"/>
       <c r="I171" s="1" t="s">
         <v>14</v>
       </c>
@@ -8764,7 +8652,6 @@
       <c r="D172" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E172" s="1"/>
       <c r="I172" s="1" t="s">
         <v>14</v>
       </c>
@@ -8785,7 +8672,6 @@
       <c r="D173" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E173" s="1"/>
       <c r="I173" s="1" t="s">
         <v>14</v>
       </c>
@@ -8806,7 +8692,6 @@
       <c r="D174" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E174" s="1"/>
       <c r="I174" s="1" t="s">
         <v>14</v>
       </c>
@@ -8827,7 +8712,6 @@
       <c r="D175" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E175" s="1"/>
       <c r="I175" s="1" t="s">
         <v>14</v>
       </c>
@@ -8848,7 +8732,6 @@
       <c r="D176" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E176" s="1"/>
       <c r="I176" s="1" t="s">
         <v>14</v>
       </c>
@@ -8869,7 +8752,6 @@
       <c r="D177" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E177" s="1"/>
       <c r="I177" s="1" t="s">
         <v>14</v>
       </c>
@@ -8890,7 +8772,6 @@
       <c r="D178" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E178" s="1"/>
       <c r="I178" s="1" t="s">
         <v>14</v>
       </c>
@@ -8911,7 +8792,6 @@
       <c r="D179" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E179" s="1"/>
       <c r="I179" s="1" t="s">
         <v>14</v>
       </c>
@@ -8932,7 +8812,6 @@
       <c r="D180" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="E180" s="1"/>
       <c r="I180" s="1" t="s">
         <v>14</v>
       </c>
@@ -8953,7 +8832,6 @@
       <c r="D181" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E181" s="1"/>
       <c r="I181" s="1" t="s">
         <v>14</v>
       </c>
@@ -8974,7 +8852,6 @@
       <c r="D182" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E182" s="1"/>
       <c r="I182" s="1" t="s">
         <v>14</v>
       </c>
@@ -8995,7 +8872,6 @@
       <c r="D183" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="E183" s="1"/>
       <c r="I183" s="1" t="s">
         <v>14</v>
       </c>
@@ -9016,7 +8892,6 @@
       <c r="D184" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E184" s="1"/>
       <c r="I184" s="1" t="s">
         <v>14</v>
       </c>
@@ -9037,7 +8912,6 @@
       <c r="D185" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E185" s="1"/>
       <c r="I185" s="1" t="s">
         <v>14</v>
       </c>
@@ -9058,7 +8932,6 @@
       <c r="D186" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E186" s="1"/>
       <c r="I186" s="1" t="s">
         <v>14</v>
       </c>
@@ -9079,7 +8952,6 @@
       <c r="D187" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E187" s="1"/>
       <c r="I187" s="1" t="s">
         <v>14</v>
       </c>
@@ -9100,7 +8972,6 @@
       <c r="D188" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E188" s="1"/>
       <c r="I188" s="1" t="s">
         <v>14</v>
       </c>
@@ -9121,7 +8992,6 @@
       <c r="D189" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="E189" s="1"/>
       <c r="I189" s="1" t="s">
         <v>14</v>
       </c>
@@ -9142,7 +9012,6 @@
       <c r="D190" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="E190" s="1"/>
       <c r="I190" s="1" t="s">
         <v>14</v>
       </c>
@@ -9163,7 +9032,6 @@
       <c r="D191" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="E191" s="1"/>
       <c r="I191" s="1" t="s">
         <v>14</v>
       </c>
@@ -9184,7 +9052,6 @@
       <c r="D192" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="E192" s="1"/>
       <c r="I192" s="1" t="s">
         <v>14</v>
       </c>
@@ -9205,7 +9072,6 @@
       <c r="D193" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="E193" s="1"/>
       <c r="I193" s="1" t="s">
         <v>14</v>
       </c>
@@ -9226,7 +9092,6 @@
       <c r="D194" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="E194" s="1"/>
       <c r="I194" s="1" t="s">
         <v>14</v>
       </c>
@@ -9247,7 +9112,6 @@
       <c r="D195" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="E195" s="1"/>
       <c r="I195" s="1" t="s">
         <v>14</v>
       </c>
@@ -9268,7 +9132,6 @@
       <c r="D196" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="E196" s="1"/>
       <c r="I196" s="1" t="s">
         <v>14</v>
       </c>
@@ -9289,7 +9152,6 @@
       <c r="D197" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="E197" s="1"/>
       <c r="I197" s="1" t="s">
         <v>14</v>
       </c>
@@ -9310,7 +9172,6 @@
       <c r="D198" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E198" s="1"/>
       <c r="I198" s="1" t="s">
         <v>14</v>
       </c>
@@ -9331,7 +9192,6 @@
       <c r="D199" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E199" s="1"/>
       <c r="I199" s="1" t="s">
         <v>14</v>
       </c>
@@ -9352,7 +9212,6 @@
       <c r="D200" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E200" s="1"/>
       <c r="I200" s="1" t="s">
         <v>14</v>
       </c>
@@ -9373,7 +9232,6 @@
       <c r="D201" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E201" s="1"/>
       <c r="I201" s="1" t="s">
         <v>14</v>
       </c>
@@ -9394,7 +9252,6 @@
       <c r="D202" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E202" s="1"/>
       <c r="I202" s="1" t="s">
         <v>14</v>
       </c>
@@ -9415,7 +9272,6 @@
       <c r="D203" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E203" s="1"/>
       <c r="I203" s="1" t="s">
         <v>14</v>
       </c>
@@ -9436,7 +9292,6 @@
       <c r="D204" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E204" s="1"/>
       <c r="I204" s="1" t="s">
         <v>93</v>
       </c>
@@ -9457,7 +9312,6 @@
       <c r="D205" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E205" s="1"/>
       <c r="I205" s="1" t="s">
         <v>14</v>
       </c>
@@ -9478,7 +9332,6 @@
       <c r="D206" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E206" s="1"/>
       <c r="I206" s="1" t="s">
         <v>14</v>
       </c>
@@ -9499,7 +9352,6 @@
       <c r="D207" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E207" s="1"/>
       <c r="I207" s="1" t="s">
         <v>14</v>
       </c>
@@ -9520,7 +9372,6 @@
       <c r="D208" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E208" s="1"/>
       <c r="I208" s="1" t="s">
         <v>14</v>
       </c>
@@ -9541,7 +9392,6 @@
       <c r="D209" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E209" s="1"/>
       <c r="I209" s="1" t="s">
         <v>14</v>
       </c>
@@ -9562,7 +9412,6 @@
       <c r="D210" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="E210" s="1"/>
       <c r="I210" s="1" t="s">
         <v>14</v>
       </c>
@@ -9583,7 +9432,6 @@
       <c r="D211" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E211" s="1"/>
       <c r="I211" s="1" t="s">
         <v>14</v>
       </c>
@@ -9604,7 +9452,6 @@
       <c r="D212" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E212" s="1"/>
       <c r="I212" s="1" t="s">
         <v>14</v>
       </c>
@@ -9625,7 +9472,6 @@
       <c r="D213" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E213" s="1"/>
       <c r="I213" s="1" t="s">
         <v>93</v>
       </c>
@@ -9646,7 +9492,6 @@
       <c r="D214" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="E214" s="1"/>
       <c r="I214" s="1" t="s">
         <v>93</v>
       </c>
@@ -9667,7 +9512,6 @@
       <c r="D215" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E215" s="1"/>
       <c r="I215" s="1" t="s">
         <v>14</v>
       </c>
@@ -9688,7 +9532,6 @@
       <c r="D216" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="E216" s="1"/>
       <c r="I216" s="1" t="s">
         <v>14</v>
       </c>
@@ -9709,7 +9552,6 @@
       <c r="D217" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E217" s="1"/>
       <c r="I217" s="1" t="s">
         <v>14</v>
       </c>
@@ -9730,7 +9572,6 @@
       <c r="D218" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E218" s="1"/>
       <c r="I218" s="1" t="s">
         <v>14</v>
       </c>
@@ -9751,7 +9592,6 @@
       <c r="D219" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E219" s="1"/>
       <c r="I219" s="1" t="s">
         <v>14</v>
       </c>
@@ -9772,7 +9612,6 @@
       <c r="D220" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E220" s="1"/>
       <c r="I220" s="1" t="s">
         <v>14</v>
       </c>
@@ -9793,7 +9632,6 @@
       <c r="D221" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E221" s="1"/>
       <c r="I221" s="1" t="s">
         <v>14</v>
       </c>
@@ -9814,7 +9652,6 @@
       <c r="D222" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E222" s="1"/>
       <c r="I222" s="1" t="s">
         <v>93</v>
       </c>
@@ -9835,7 +9672,6 @@
       <c r="D223" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E223" s="1"/>
       <c r="I223" s="1" t="s">
         <v>14</v>
       </c>
@@ -9856,7 +9692,6 @@
       <c r="D224" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E224" s="1"/>
       <c r="I224" s="1" t="s">
         <v>14</v>
       </c>
@@ -9877,7 +9712,6 @@
       <c r="D225" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="E225" s="1"/>
       <c r="I225" s="1" t="s">
         <v>93</v>
       </c>
@@ -9898,7 +9732,6 @@
       <c r="D226" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E226" s="1"/>
       <c r="I226" s="1" t="s">
         <v>93</v>
       </c>
@@ -9919,7 +9752,6 @@
       <c r="D227" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="E227" s="1"/>
       <c r="I227" s="1" t="s">
         <v>93</v>
       </c>
@@ -9940,7 +9772,6 @@
       <c r="D228" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="E228" s="1"/>
       <c r="I228" s="1" t="s">
         <v>93</v>
       </c>
@@ -9961,7 +9792,6 @@
       <c r="D229" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="E229" s="1"/>
       <c r="I229" s="1" t="s">
         <v>93</v>
       </c>
@@ -9982,7 +9812,6 @@
       <c r="D230" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E230" s="1"/>
       <c r="I230" s="1" t="s">
         <v>93</v>
       </c>
@@ -10003,7 +9832,6 @@
       <c r="D231" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="E231" s="1"/>
       <c r="I231" s="1" t="s">
         <v>93</v>
       </c>
@@ -10024,7 +9852,6 @@
       <c r="D232" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="E232" s="1"/>
       <c r="I232" s="1" t="s">
         <v>93</v>
       </c>
@@ -10045,7 +9872,6 @@
       <c r="D233" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="E233" s="1"/>
       <c r="I233" s="1" t="s">
         <v>93</v>
       </c>
@@ -10066,7 +9892,6 @@
       <c r="D234" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E234" s="1"/>
       <c r="I234" s="1" t="s">
         <v>93</v>
       </c>
@@ -10087,7 +9912,6 @@
       <c r="D235" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="E235" s="1"/>
       <c r="I235" s="1" t="s">
         <v>93</v>
       </c>
@@ -10108,7 +9932,6 @@
       <c r="D236" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E236" s="1"/>
       <c r="I236" s="1" t="s">
         <v>14</v>
       </c>
@@ -10129,7 +9952,6 @@
       <c r="D237" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E237" s="1"/>
       <c r="I237" s="1" t="s">
         <v>14</v>
       </c>
@@ -10150,7 +9972,6 @@
       <c r="D238" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E238" s="1"/>
       <c r="I238" s="1" t="s">
         <v>14</v>
       </c>
@@ -10171,7 +9992,6 @@
       <c r="D239" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E239" s="1"/>
       <c r="I239" s="1" t="s">
         <v>14</v>
       </c>
@@ -10192,7 +10012,6 @@
       <c r="D240" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E240" s="1"/>
       <c r="I240" s="1" t="s">
         <v>14</v>
       </c>
@@ -10213,7 +10032,6 @@
       <c r="D241" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E241" s="1"/>
       <c r="I241" s="1" t="s">
         <v>14</v>
       </c>
@@ -10234,7 +10052,6 @@
       <c r="D242" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="E242" s="1"/>
       <c r="I242" s="1" t="s">
         <v>93</v>
       </c>
@@ -10255,7 +10072,6 @@
       <c r="D243" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="E243" s="1"/>
       <c r="I243" s="1" t="s">
         <v>93</v>
       </c>
@@ -10276,7 +10092,6 @@
       <c r="D244" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="E244" s="1"/>
       <c r="I244" s="1" t="s">
         <v>93</v>
       </c>
@@ -10297,7 +10112,6 @@
       <c r="D245" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E245" s="1"/>
       <c r="I245" s="1" t="s">
         <v>14</v>
       </c>
@@ -10318,7 +10132,6 @@
       <c r="D246" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E246" s="1"/>
       <c r="H246" s="1" t="s">
         <v>573</v>
       </c>
@@ -10342,7 +10155,6 @@
       <c r="D247" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="E247" s="1"/>
       <c r="H247" s="1" t="s">
         <v>573</v>
       </c>
@@ -10366,7 +10178,6 @@
       <c r="D248" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="E248" s="1"/>
       <c r="H248" s="1" t="s">
         <v>573</v>
       </c>
@@ -10390,7 +10201,6 @@
       <c r="D249" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="E249" s="1"/>
       <c r="H249" s="1" t="s">
         <v>573</v>
       </c>
@@ -10414,7 +10224,6 @@
       <c r="D250" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E250" s="1"/>
       <c r="H250" s="1" t="s">
         <v>573</v>
       </c>
@@ -10438,7 +10247,6 @@
       <c r="D251" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E251" s="1"/>
       <c r="H251" s="1" t="s">
         <v>573</v>
       </c>
@@ -10462,7 +10270,6 @@
       <c r="D252" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="E252" s="1"/>
       <c r="H252" s="1" t="s">
         <v>573</v>
       </c>
@@ -10486,7 +10293,6 @@
       <c r="D253" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E253" s="1"/>
       <c r="H253" s="1" t="s">
         <v>573</v>
       </c>
@@ -10510,7 +10316,6 @@
       <c r="D254" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E254" s="1"/>
       <c r="H254" s="1" t="s">
         <v>595</v>
       </c>
@@ -10534,7 +10339,6 @@
       <c r="D255" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="E255" s="1"/>
       <c r="H255" s="1" t="s">
         <v>595</v>
       </c>
@@ -10558,7 +10362,6 @@
       <c r="D256" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="E256" s="1"/>
       <c r="H256" s="1" t="s">
         <v>602</v>
       </c>
@@ -10582,7 +10385,6 @@
       <c r="D257" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="E257" s="1"/>
       <c r="H257" s="1" t="s">
         <v>595</v>
       </c>
@@ -10606,7 +10408,6 @@
       <c r="D258" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E258" s="1"/>
       <c r="H258" s="1" t="s">
         <v>609</v>
       </c>
@@ -10630,7 +10431,6 @@
       <c r="D259" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E259" s="1"/>
       <c r="H259" s="1" t="s">
         <v>609</v>
       </c>
@@ -10649,12 +10449,11 @@
         <v>613</v>
       </c>
       <c r="C260" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D260" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="D260" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="E260" s="1"/>
       <c r="H260" s="1" t="s">
         <v>595</v>
       </c>
@@ -10667,20 +10466,19 @@
     </row>
     <row r="261" spans="1:10">
       <c r="A261" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="B261" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="B261" s="3" t="s">
+      <c r="C261" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D261" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="C261" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="D261" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="E261" s="1"/>
       <c r="H261" s="1" t="s">
-        <v>618</v>
+        <v>595</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>14</v>
@@ -10691,20 +10489,19 @@
     </row>
     <row r="262" spans="1:10">
       <c r="A262" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B262" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="B262" s="3" t="s">
+      <c r="C262" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D262" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="C262" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="D262" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E262" s="1"/>
       <c r="H262" s="1" t="s">
-        <v>618</v>
+        <v>595</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>14</v>
@@ -10721,14 +10518,13 @@
         <v>622</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>614</v>
+        <v>78</v>
       </c>
       <c r="D263" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="E263" s="1"/>
       <c r="H263" s="1" t="s">
-        <v>618</v>
+        <v>595</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>14</v>
@@ -10745,14 +10541,13 @@
         <v>625</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>614</v>
+        <v>78</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E264" s="1"/>
+        <v>626</v>
+      </c>
       <c r="H264" s="1" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>14</v>
@@ -10763,20 +10558,19 @@
     </row>
     <row r="265" spans="1:10">
       <c r="A265" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B265" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="H265" s="1" t="s">
         <v>627</v>
-      </c>
-      <c r="C265" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D265" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="E265" s="1"/>
-      <c r="H265" s="1" t="s">
-        <v>595</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>14</v>
@@ -10787,20 +10581,19 @@
     </row>
     <row r="266" spans="1:10">
       <c r="A266" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B266" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="C266" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="C266" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="D266" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="E266" s="1"/>
+        <v>634</v>
+      </c>
       <c r="H266" s="1" t="s">
-        <v>595</v>
+        <v>635</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>14</v>
@@ -10811,20 +10604,19 @@
     </row>
     <row r="267" spans="1:10">
       <c r="A267" s="1" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>78</v>
+        <v>630</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="E267" s="1"/>
+        <v>638</v>
+      </c>
       <c r="H267" s="1" t="s">
-        <v>595</v>
+        <v>635</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>14</v>
@@ -10835,20 +10627,19 @@
     </row>
     <row r="268" spans="1:10">
       <c r="A268" s="1" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="E268" s="1"/>
+        <v>134</v>
+      </c>
       <c r="H268" s="1" t="s">
-        <v>595</v>
+        <v>641</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>14</v>
@@ -10859,20 +10650,19 @@
     </row>
     <row r="269" spans="1:10">
       <c r="A269" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="E269" s="1"/>
+        <v>229</v>
+      </c>
       <c r="H269" s="1" t="s">
-        <v>618</v>
+        <v>641</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>14</v>
@@ -10883,20 +10673,19 @@
     </row>
     <row r="270" spans="1:10">
       <c r="A270" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>643</v>
+        <v>133</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="E270" s="1"/>
+        <v>229</v>
+      </c>
       <c r="H270" s="1" t="s">
-        <v>618</v>
+        <v>41</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>14</v>
@@ -10907,20 +10696,19 @@
     </row>
     <row r="271" spans="1:10">
       <c r="A271" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>643</v>
+        <v>133</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="E271" s="1"/>
+        <v>648</v>
+      </c>
       <c r="H271" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>14</v>
@@ -10931,20 +10719,19 @@
     </row>
     <row r="272" spans="1:10">
       <c r="A272" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="E272" s="1"/>
+        <v>318</v>
+      </c>
       <c r="H272" s="1" t="s">
-        <v>648</v>
+        <v>627</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>14</v>
@@ -10955,20 +10742,19 @@
     </row>
     <row r="273" spans="1:10">
       <c r="A273" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E273" s="1"/>
+        <v>655</v>
+      </c>
       <c r="H273" s="1" t="s">
-        <v>654</v>
+        <v>627</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>14</v>
@@ -10979,20 +10765,19 @@
     </row>
     <row r="274" spans="1:10">
       <c r="A274" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E274" s="1"/>
+        <v>75</v>
+      </c>
       <c r="H274" s="1" t="s">
-        <v>654</v>
+        <v>595</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>14</v>
@@ -11003,20 +10788,19 @@
     </row>
     <row r="275" spans="1:10">
       <c r="A275" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>133</v>
+        <v>660</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E275" s="1"/>
+        <v>485</v>
+      </c>
       <c r="H275" s="1" t="s">
-        <v>41</v>
+        <v>627</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>14</v>
@@ -11027,20 +10811,19 @@
     </row>
     <row r="276" spans="1:10">
       <c r="A276" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>133</v>
+        <v>663</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="E276" s="1"/>
+        <v>485</v>
+      </c>
       <c r="H276" s="1" t="s">
-        <v>662</v>
+        <v>595</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>14</v>
@@ -11051,20 +10834,19 @@
     </row>
     <row r="277" spans="1:10">
       <c r="A277" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="C277" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="B277" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="C277" s="1" t="s">
-        <v>665</v>
-      </c>
       <c r="D277" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="E277" s="1"/>
+        <v>25</v>
+      </c>
       <c r="H277" s="1" t="s">
-        <v>618</v>
+        <v>595</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>14</v>
@@ -11081,14 +10863,13 @@
         <v>667</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>153</v>
+        <v>663</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="E278" s="1"/>
+        <v>25</v>
+      </c>
       <c r="H278" s="1" t="s">
-        <v>618</v>
+        <v>595</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>14</v>
@@ -11099,20 +10880,19 @@
     </row>
     <row r="279" spans="1:10">
       <c r="A279" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B279" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="B279" s="3" t="s">
+      <c r="C279" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="C279" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="D279" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E279" s="1"/>
+        <v>671</v>
+      </c>
       <c r="H279" s="1" t="s">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>14</v>
@@ -11123,20 +10903,19 @@
     </row>
     <row r="280" spans="1:10">
       <c r="A280" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D280" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="B280" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="C280" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="D280" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="E280" s="1"/>
       <c r="H280" s="1" t="s">
-        <v>618</v>
+        <v>41</v>
       </c>
       <c r="I280" s="1" t="s">
         <v>14</v>
@@ -11153,14 +10932,13 @@
         <v>675</v>
       </c>
       <c r="C281" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="H281" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="D281" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="E281" s="1"/>
-      <c r="H281" s="1" t="s">
-        <v>595</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>14</v>
@@ -11177,14 +10955,13 @@
         <v>678</v>
       </c>
       <c r="C282" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="H282" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="D282" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E282" s="1"/>
-      <c r="H282" s="1" t="s">
-        <v>595</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>14</v>
@@ -11201,14 +10978,13 @@
         <v>680</v>
       </c>
       <c r="C283" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="H283" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="D283" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E283" s="1"/>
-      <c r="H283" s="1" t="s">
-        <v>595</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>14</v>
@@ -11219,20 +10995,19 @@
     </row>
     <row r="284" spans="1:10">
       <c r="A284" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>683</v>
+        <v>189</v>
       </c>
       <c r="D284" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="E284" s="1"/>
       <c r="H284" s="1" t="s">
-        <v>609</v>
+        <v>676</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>14</v>
@@ -11249,12 +11024,11 @@
         <v>686</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>683</v>
+        <v>189</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="E285" s="1"/>
+        <v>355</v>
+      </c>
       <c r="H285" s="1" t="s">
         <v>41</v>
       </c>
@@ -11276,11 +11050,10 @@
         <v>189</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="E286" s="1"/>
+        <v>689</v>
+      </c>
       <c r="H286" s="1" t="s">
-        <v>689</v>
+        <v>609</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>14</v>
@@ -11300,11 +11073,10 @@
         <v>189</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E287" s="1"/>
+        <v>355</v>
+      </c>
       <c r="H287" s="1" t="s">
-        <v>689</v>
+        <v>627</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>14</v>
@@ -11326,9 +11098,8 @@
       <c r="D288" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="E288" s="1"/>
       <c r="H288" s="1" t="s">
-        <v>689</v>
+        <v>627</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>14</v>
@@ -11350,12 +11121,11 @@
       <c r="D289" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="E289" s="1"/>
       <c r="H289" s="1" t="s">
-        <v>689</v>
+        <v>595</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>14</v>
+        <v>584</v>
       </c>
       <c r="J289" s="1" t="s">
         <v>574</v>
@@ -11369,17 +11139,16 @@
         <v>699</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>189</v>
+        <v>232</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="E290" s="1"/>
+        <v>485</v>
+      </c>
       <c r="H290" s="1" t="s">
-        <v>41</v>
+        <v>627</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="J290" s="1" t="s">
         <v>574</v>
@@ -11393,14 +11162,13 @@
         <v>701</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>189</v>
+        <v>232</v>
       </c>
       <c r="D291" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="E291" s="1"/>
       <c r="H291" s="1" t="s">
-        <v>609</v>
+        <v>649</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>14</v>
@@ -11417,14 +11185,13 @@
         <v>704</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>189</v>
+        <v>705</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="E292" s="1"/>
+        <v>706</v>
+      </c>
       <c r="H292" s="1" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>14</v>
@@ -11435,20 +11202,19 @@
     </row>
     <row r="293" spans="1:10">
       <c r="A293" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>189</v>
+        <v>709</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="E293" s="1"/>
+        <v>183</v>
+      </c>
       <c r="H293" s="1" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="I293" s="1" t="s">
         <v>14</v>
@@ -11459,23 +11225,22 @@
     </row>
     <row r="294" spans="1:10">
       <c r="A294" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B294" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="C294" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="C294" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="D294" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="E294" s="1"/>
+        <v>281</v>
+      </c>
       <c r="H294" s="1" t="s">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="I294" s="1" t="s">
-        <v>584</v>
+        <v>14</v>
       </c>
       <c r="J294" s="1" t="s">
         <v>574</v>
@@ -11483,23 +11248,22 @@
     </row>
     <row r="295" spans="1:10">
       <c r="A295" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>232</v>
+        <v>714</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="E295" s="1"/>
+        <v>715</v>
+      </c>
       <c r="H295" s="1" t="s">
-        <v>618</v>
+        <v>595</v>
       </c>
       <c r="I295" s="1" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="J295" s="1" t="s">
         <v>574</v>
@@ -11507,20 +11271,19 @@
     </row>
     <row r="296" spans="1:10">
       <c r="A296" s="1" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="B296" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="C296" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="C296" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="D296" s="3" t="s">
-        <v>715</v>
-      </c>
-      <c r="E296" s="1"/>
+        <v>363</v>
+      </c>
       <c r="H296" s="1" t="s">
-        <v>662</v>
+        <v>718</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>14</v>
@@ -11531,23 +11294,22 @@
     </row>
     <row r="297" spans="1:10">
       <c r="A297" s="1" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>718</v>
+        <v>248</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="E297" s="1"/>
+        <v>721</v>
+      </c>
       <c r="H297" s="1" t="s">
-        <v>618</v>
+        <v>595</v>
       </c>
       <c r="I297" s="1" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="J297" s="1" t="s">
         <v>574</v>
@@ -11555,23 +11317,22 @@
     </row>
     <row r="298" spans="1:10">
       <c r="A298" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E298" s="1"/>
+        <v>725</v>
+      </c>
       <c r="H298" s="1" t="s">
-        <v>618</v>
+        <v>726</v>
       </c>
       <c r="I298" s="1" t="s">
-        <v>14</v>
+        <v>584</v>
       </c>
       <c r="J298" s="1" t="s">
         <v>574</v>
@@ -11579,20 +11340,19 @@
     </row>
     <row r="299" spans="1:10">
       <c r="A299" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>722</v>
+        <v>253</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="E299" s="1"/>
+        <v>25</v>
+      </c>
       <c r="H299" s="1" t="s">
-        <v>609</v>
+        <v>41</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>14</v>
@@ -11603,20 +11363,19 @@
     </row>
     <row r="300" spans="1:10">
       <c r="A300" s="1" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>727</v>
+        <v>262</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="E300" s="1"/>
+        <v>485</v>
+      </c>
       <c r="H300" s="1" t="s">
-        <v>595</v>
+        <v>627</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>14</v>
@@ -11627,20 +11386,19 @@
     </row>
     <row r="301" spans="1:10">
       <c r="A301" s="1" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>727</v>
+        <v>12</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="E301" s="1"/>
+        <v>28</v>
+      </c>
       <c r="H301" s="1" t="s">
-        <v>731</v>
+        <v>627</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>14</v>
@@ -11651,20 +11409,19 @@
     </row>
     <row r="302" spans="1:10">
       <c r="A302" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>248</v>
+        <v>12</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="E302" s="1"/>
+        <v>98</v>
+      </c>
       <c r="H302" s="1" t="s">
-        <v>595</v>
+        <v>41</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>93</v>
@@ -11681,14 +11438,13 @@
         <v>736</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>737</v>
+        <v>12</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="E303" s="1"/>
+        <v>68</v>
+      </c>
       <c r="H303" s="1" t="s">
-        <v>739</v>
+        <v>627</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>584</v>
@@ -11699,20 +11455,19 @@
     </row>
     <row r="304" spans="1:10">
       <c r="A304" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B304" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C304" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="D304" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="H304" s="1" t="s">
         <v>740</v>
-      </c>
-      <c r="B304" s="3" t="s">
-        <v>741</v>
-      </c>
-      <c r="C304" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="D304" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E304" s="1"/>
-      <c r="H304" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>14</v>
@@ -11723,20 +11478,19 @@
     </row>
     <row r="305" spans="1:10">
       <c r="A305" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B305" s="3" t="s">
         <v>742</v>
       </c>
-      <c r="B305" s="3" t="s">
+      <c r="C305" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="C305" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="D305" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="E305" s="1"/>
+        <v>347</v>
+      </c>
       <c r="H305" s="1" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>14</v>
@@ -11753,14 +11507,13 @@
         <v>745</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>12</v>
+        <v>292</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E306" s="1"/>
+        <v>347</v>
+      </c>
       <c r="H306" s="1" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>14</v>
@@ -11777,17 +11530,16 @@
         <v>747</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>12</v>
+        <v>292</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E307" s="1"/>
+        <v>748</v>
+      </c>
       <c r="H307" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>93</v>
+        <v>584</v>
       </c>
       <c r="J307" s="1" t="s">
         <v>574</v>
@@ -11795,23 +11547,22 @@
     </row>
     <row r="308" spans="1:10">
       <c r="A308" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>12</v>
+        <v>292</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E308" s="1"/>
+        <v>28</v>
+      </c>
       <c r="H308" s="1" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>584</v>
+        <v>14</v>
       </c>
       <c r="J308" s="1" t="s">
         <v>574</v>
@@ -11819,23 +11570,22 @@
     </row>
     <row r="309" spans="1:10">
       <c r="A309" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>752</v>
+        <v>292</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="E309" s="1"/>
+        <v>753</v>
+      </c>
       <c r="H309" s="1" t="s">
-        <v>753</v>
+        <v>41</v>
       </c>
       <c r="I309" s="1" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="J309" s="1" t="s">
         <v>574</v>
@@ -11852,11 +11602,10 @@
         <v>756</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="E310" s="1"/>
+        <v>98</v>
+      </c>
       <c r="H310" s="1" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>14</v>
@@ -11873,14 +11622,13 @@
         <v>758</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>292</v>
+        <v>756</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="E311" s="1"/>
+        <v>98</v>
+      </c>
       <c r="H311" s="1" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>14</v>
@@ -11897,17 +11645,16 @@
         <v>760</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>292</v>
+        <v>756</v>
       </c>
       <c r="D312" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="E312" s="1"/>
       <c r="H312" s="1" t="s">
-        <v>41</v>
+        <v>609</v>
       </c>
       <c r="I312" s="1" t="s">
-        <v>584</v>
+        <v>14</v>
       </c>
       <c r="J312" s="1" t="s">
         <v>574</v>
@@ -11921,14 +11668,13 @@
         <v>763</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>292</v>
+        <v>756</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E313" s="1"/>
+        <v>75</v>
+      </c>
       <c r="H313" s="1" t="s">
-        <v>618</v>
+        <v>41</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>14</v>
@@ -11945,17 +11691,16 @@
         <v>765</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>292</v>
+        <v>756</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="E314" s="1"/>
+        <v>485</v>
+      </c>
       <c r="H314" s="1" t="s">
-        <v>41</v>
+        <v>595</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="J314" s="1" t="s">
         <v>574</v>
@@ -11963,20 +11708,19 @@
     </row>
     <row r="315" spans="1:10">
       <c r="A315" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B315" s="3" t="s">
         <v>767</v>
       </c>
-      <c r="B315" s="3" t="s">
+      <c r="C315" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="D315" s="3" t="s">
         <v>768</v>
       </c>
-      <c r="C315" s="1" t="s">
-        <v>769</v>
-      </c>
-      <c r="D315" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E315" s="1"/>
       <c r="H315" s="1" t="s">
-        <v>648</v>
+        <v>627</v>
       </c>
       <c r="I315" s="1" t="s">
         <v>14</v>
@@ -11987,20 +11731,19 @@
     </row>
     <row r="316" spans="1:10">
       <c r="A316" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B316" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="B316" s="3" t="s">
+      <c r="C316" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D316" s="3" t="s">
         <v>771</v>
       </c>
-      <c r="C316" s="1" t="s">
-        <v>769</v>
-      </c>
-      <c r="D316" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E316" s="1"/>
       <c r="H316" s="1" t="s">
-        <v>648</v>
+        <v>609</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>14</v>
@@ -12017,14 +11760,13 @@
         <v>773</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>769</v>
+        <v>317</v>
       </c>
       <c r="D317" s="3" t="s">
         <v>774</v>
       </c>
-      <c r="E317" s="1"/>
       <c r="H317" s="1" t="s">
-        <v>609</v>
+        <v>41</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>14</v>
@@ -12038,20 +11780,19 @@
         <v>775</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>769</v>
+        <v>317</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E318" s="1"/>
+        <v>774</v>
+      </c>
       <c r="H318" s="1" t="s">
-        <v>41</v>
+        <v>627</v>
       </c>
       <c r="I318" s="1" t="s">
-        <v>14</v>
+        <v>584</v>
       </c>
       <c r="J318" s="1" t="s">
         <v>574</v>
@@ -12059,20 +11800,19 @@
     </row>
     <row r="319" spans="1:10">
       <c r="A319" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="B319" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="B319" s="3" t="s">
-        <v>778</v>
-      </c>
       <c r="C319" s="1" t="s">
-        <v>769</v>
+        <v>321</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="E319" s="1"/>
+        <v>41</v>
+      </c>
       <c r="H319" s="1" t="s">
-        <v>595</v>
+        <v>641</v>
       </c>
       <c r="I319" s="1" t="s">
         <v>14</v>
@@ -12083,20 +11823,19 @@
     </row>
     <row r="320" spans="1:10">
       <c r="A320" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="B320" s="3" t="s">
         <v>779</v>
       </c>
-      <c r="B320" s="3" t="s">
-        <v>780</v>
-      </c>
       <c r="C320" s="1" t="s">
-        <v>769</v>
+        <v>321</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="E320" s="1"/>
+        <v>41</v>
+      </c>
       <c r="H320" s="1" t="s">
-        <v>618</v>
+        <v>641</v>
       </c>
       <c r="I320" s="1" t="s">
         <v>14</v>
@@ -12107,20 +11846,19 @@
     </row>
     <row r="321" spans="1:10">
       <c r="A321" s="1" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>784</v>
-      </c>
-      <c r="E321" s="1"/>
+        <v>41</v>
+      </c>
       <c r="H321" s="1" t="s">
-        <v>609</v>
+        <v>641</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>14</v>
@@ -12131,23 +11869,22 @@
     </row>
     <row r="322" spans="1:10">
       <c r="A322" s="1" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="E322" s="1"/>
+        <v>25</v>
+      </c>
       <c r="H322" s="1" t="s">
-        <v>41</v>
+        <v>627</v>
       </c>
       <c r="I322" s="1" t="s">
-        <v>14</v>
+        <v>584</v>
       </c>
       <c r="J322" s="1" t="s">
         <v>574</v>
@@ -12155,23 +11892,22 @@
     </row>
     <row r="323" spans="1:10">
       <c r="A323" s="1" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="B323" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="C323" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="C323" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="D323" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="E323" s="1"/>
+        <v>363</v>
+      </c>
       <c r="H323" s="1" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>584</v>
+        <v>14</v>
       </c>
       <c r="J323" s="1" t="s">
         <v>574</v>
@@ -12179,23 +11915,22 @@
     </row>
     <row r="324" spans="1:10">
       <c r="A324" s="1" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E324" s="1"/>
+        <v>485</v>
+      </c>
       <c r="H324" s="1" t="s">
-        <v>654</v>
+        <v>635</v>
       </c>
       <c r="I324" s="1" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="J324" s="1" t="s">
         <v>574</v>
@@ -12203,20 +11938,19 @@
     </row>
     <row r="325" spans="1:10">
       <c r="A325" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="B325" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D325" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="B325" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="C325" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="D325" s="3" t="s">
+      <c r="H325" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="E325" s="1"/>
-      <c r="H325" s="1" t="s">
-        <v>654</v>
       </c>
       <c r="I325" s="1" t="s">
         <v>14</v>
@@ -12227,20 +11961,19 @@
     </row>
     <row r="326" spans="1:10">
       <c r="A326" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B326" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="B326" s="3" t="s">
-        <v>794</v>
-      </c>
       <c r="C326" s="1" t="s">
-        <v>321</v>
+        <v>391</v>
       </c>
       <c r="D326" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H326" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="E326" s="1"/>
-      <c r="H326" s="1" t="s">
-        <v>654</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>14</v>
@@ -12251,23 +11984,22 @@
     </row>
     <row r="327" spans="1:10">
       <c r="A327" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="B327" s="3" t="s">
         <v>795</v>
       </c>
-      <c r="B327" s="3" t="s">
+      <c r="C327" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D327" s="3" t="s">
         <v>796</v>
       </c>
-      <c r="C327" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D327" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E327" s="1"/>
       <c r="H327" s="1" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="I327" s="1" t="s">
-        <v>584</v>
+        <v>14</v>
       </c>
       <c r="J327" s="1" t="s">
         <v>574</v>
@@ -12281,14 +12013,13 @@
         <v>798</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>799</v>
+        <v>391</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="E328" s="1"/>
+        <v>394</v>
+      </c>
       <c r="H328" s="1" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>14</v>
@@ -12299,23 +12030,22 @@
     </row>
     <row r="329" spans="1:10">
       <c r="A329" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="B329" s="3" t="s">
         <v>800</v>
       </c>
-      <c r="B329" s="3" t="s">
-        <v>801</v>
-      </c>
       <c r="C329" s="1" t="s">
-        <v>346</v>
+        <v>391</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="E329" s="1"/>
+        <v>13</v>
+      </c>
       <c r="H329" s="1" t="s">
-        <v>648</v>
+        <v>676</v>
       </c>
       <c r="I329" s="1" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="J329" s="1" t="s">
         <v>574</v>
@@ -12323,20 +12053,19 @@
     </row>
     <row r="330" spans="1:10">
       <c r="A330" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="B330" s="3" t="s">
         <v>802</v>
       </c>
-      <c r="B330" s="3" t="s">
-        <v>803</v>
-      </c>
       <c r="C330" s="1" t="s">
-        <v>346</v>
+        <v>391</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="E330" s="1"/>
+        <v>466</v>
+      </c>
       <c r="H330" s="1" t="s">
-        <v>41</v>
+        <v>595</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>14</v>
@@ -12347,18 +12076,17 @@
     </row>
     <row r="331" spans="1:10">
       <c r="A331" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>391</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E331" s="1"/>
+        <v>98</v>
+      </c>
       <c r="H331" s="1" t="s">
         <v>41</v>
       </c>
@@ -12371,20 +12099,19 @@
     </row>
     <row r="332" spans="1:10">
       <c r="A332" s="1" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>391</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="E332" s="1"/>
+        <v>98</v>
+      </c>
       <c r="H332" s="1" t="s">
-        <v>618</v>
+        <v>41</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>14</v>
@@ -12395,20 +12122,19 @@
     </row>
     <row r="333" spans="1:10">
       <c r="A333" s="1" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>391</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="E333" s="1"/>
+        <v>98</v>
+      </c>
       <c r="H333" s="1" t="s">
-        <v>648</v>
+        <v>41</v>
       </c>
       <c r="I333" s="1" t="s">
         <v>14</v>
@@ -12419,20 +12145,19 @@
     </row>
     <row r="334" spans="1:10">
       <c r="A334" s="1" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>391</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E334" s="1"/>
+        <v>98</v>
+      </c>
       <c r="H334" s="1" t="s">
-        <v>689</v>
+        <v>41</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>14</v>
@@ -12443,20 +12168,19 @@
     </row>
     <row r="335" spans="1:10">
       <c r="A335" s="1" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>391</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="E335" s="1"/>
+        <v>98</v>
+      </c>
       <c r="H335" s="1" t="s">
-        <v>595</v>
+        <v>41</v>
       </c>
       <c r="I335" s="1" t="s">
         <v>14</v>
@@ -12467,20 +12191,19 @@
     </row>
     <row r="336" spans="1:10">
       <c r="A336" s="1" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>391</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E336" s="1"/>
+        <v>186</v>
+      </c>
       <c r="H336" s="1" t="s">
-        <v>41</v>
+        <v>595</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>14</v>
@@ -12491,20 +12214,19 @@
     </row>
     <row r="337" spans="1:10">
       <c r="A337" s="1" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>391</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E337" s="1"/>
+        <v>186</v>
+      </c>
       <c r="H337" s="1" t="s">
-        <v>41</v>
+        <v>595</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>14</v>
@@ -12515,20 +12237,19 @@
     </row>
     <row r="338" spans="1:10">
       <c r="A338" s="1" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>391</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E338" s="1"/>
+        <v>186</v>
+      </c>
       <c r="H338" s="1" t="s">
-        <v>41</v>
+        <v>595</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>14</v>
@@ -12539,20 +12260,19 @@
     </row>
     <row r="339" spans="1:10">
       <c r="A339" s="1" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>391</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E339" s="1"/>
+        <v>186</v>
+      </c>
       <c r="H339" s="1" t="s">
-        <v>41</v>
+        <v>595</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>14</v>
@@ -12563,20 +12283,19 @@
     </row>
     <row r="340" spans="1:10">
       <c r="A340" s="1" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>391</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E340" s="1"/>
+        <v>186</v>
+      </c>
       <c r="H340" s="1" t="s">
-        <v>41</v>
+        <v>595</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>14</v>
@@ -12587,20 +12306,19 @@
     </row>
     <row r="341" spans="1:10">
       <c r="A341" s="1" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>391</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E341" s="1"/>
+        <v>825</v>
+      </c>
       <c r="H341" s="1" t="s">
-        <v>595</v>
+        <v>635</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>14</v>
@@ -12611,18 +12329,17 @@
     </row>
     <row r="342" spans="1:10">
       <c r="A342" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>391</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E342" s="1"/>
+        <v>768</v>
+      </c>
       <c r="H342" s="1" t="s">
         <v>595</v>
       </c>
@@ -12635,20 +12352,19 @@
     </row>
     <row r="343" spans="1:10">
       <c r="A343" s="1" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>391</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E343" s="1"/>
+        <v>830</v>
+      </c>
       <c r="H343" s="1" t="s">
-        <v>595</v>
+        <v>635</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>14</v>
@@ -12659,20 +12375,19 @@
     </row>
     <row r="344" spans="1:10">
       <c r="A344" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="B344" s="3" t="s">
         <v>832</v>
-      </c>
-      <c r="B344" s="3" t="s">
-        <v>833</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>391</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E344" s="1"/>
+        <v>833</v>
+      </c>
       <c r="H344" s="1" t="s">
-        <v>595</v>
+        <v>676</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>14</v>
@@ -12692,11 +12407,10 @@
         <v>391</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E345" s="1"/>
+        <v>836</v>
+      </c>
       <c r="H345" s="1" t="s">
-        <v>595</v>
+        <v>41</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>14</v>
@@ -12707,23 +12421,22 @@
     </row>
     <row r="346" spans="1:10">
       <c r="A346" s="1" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>391</v>
+        <v>724</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>838</v>
-      </c>
-      <c r="E346" s="1"/>
+        <v>839</v>
+      </c>
       <c r="H346" s="1" t="s">
-        <v>648</v>
+        <v>41</v>
       </c>
       <c r="I346" s="1" t="s">
-        <v>14</v>
+        <v>584</v>
       </c>
       <c r="J346" s="1" t="s">
         <v>574</v>
@@ -12731,20 +12444,19 @@
     </row>
     <row r="347" spans="1:10">
       <c r="A347" s="1" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>391</v>
+        <v>438</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="E347" s="1"/>
+        <v>842</v>
+      </c>
       <c r="H347" s="1" t="s">
-        <v>595</v>
+        <v>627</v>
       </c>
       <c r="I347" s="1" t="s">
         <v>14</v>
@@ -12755,20 +12467,19 @@
     </row>
     <row r="348" spans="1:10">
       <c r="A348" s="1" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>391</v>
+        <v>438</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>843</v>
-      </c>
-      <c r="E348" s="1"/>
+        <v>41</v>
+      </c>
       <c r="H348" s="1" t="s">
-        <v>648</v>
+        <v>627</v>
       </c>
       <c r="I348" s="1" t="s">
         <v>14</v>
@@ -12779,20 +12490,19 @@
     </row>
     <row r="349" spans="1:10">
       <c r="A349" s="1" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>391</v>
+        <v>438</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>846</v>
-      </c>
-      <c r="E349" s="1"/>
+        <v>41</v>
+      </c>
       <c r="H349" s="1" t="s">
-        <v>689</v>
+        <v>627</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>14</v>
@@ -12809,14 +12519,13 @@
         <v>848</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>391</v>
+        <v>438</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>849</v>
-      </c>
-      <c r="E350" s="1"/>
+        <v>41</v>
+      </c>
       <c r="H350" s="1" t="s">
-        <v>41</v>
+        <v>627</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>14</v>
@@ -12827,23 +12536,22 @@
     </row>
     <row r="351" spans="1:10">
       <c r="A351" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="B351" s="3" t="s">
         <v>850</v>
       </c>
-      <c r="B351" s="3" t="s">
-        <v>851</v>
-      </c>
       <c r="C351" s="1" t="s">
-        <v>737</v>
+        <v>438</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>852</v>
-      </c>
-      <c r="E351" s="1"/>
+        <v>41</v>
+      </c>
       <c r="H351" s="1" t="s">
-        <v>41</v>
+        <v>627</v>
       </c>
       <c r="I351" s="1" t="s">
-        <v>584</v>
+        <v>14</v>
       </c>
       <c r="J351" s="1" t="s">
         <v>574</v>
@@ -12851,20 +12559,19 @@
     </row>
     <row r="352" spans="1:10">
       <c r="A352" s="1" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>438</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>855</v>
-      </c>
-      <c r="E352" s="1"/>
+        <v>41</v>
+      </c>
       <c r="H352" s="1" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>14</v>
@@ -12875,10 +12582,10 @@
     </row>
     <row r="353" spans="1:10">
       <c r="A353" s="1" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>438</v>
@@ -12886,9 +12593,8 @@
       <c r="D353" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E353" s="1"/>
       <c r="H353" s="1" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="I353" s="1" t="s">
         <v>14</v>
@@ -12899,10 +12605,10 @@
     </row>
     <row r="354" spans="1:10">
       <c r="A354" s="1" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>438</v>
@@ -12910,9 +12616,8 @@
       <c r="D354" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E354" s="1"/>
       <c r="H354" s="1" t="s">
-        <v>618</v>
+        <v>41</v>
       </c>
       <c r="I354" s="1" t="s">
         <v>14</v>
@@ -12923,10 +12628,10 @@
     </row>
     <row r="355" spans="1:10">
       <c r="A355" s="1" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>438</v>
@@ -12934,9 +12639,8 @@
       <c r="D355" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E355" s="1"/>
       <c r="H355" s="1" t="s">
-        <v>618</v>
+        <v>41</v>
       </c>
       <c r="I355" s="1" t="s">
         <v>14</v>
@@ -12947,10 +12651,10 @@
     </row>
     <row r="356" spans="1:10">
       <c r="A356" s="1" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>438</v>
@@ -12958,9 +12662,8 @@
       <c r="D356" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E356" s="1"/>
       <c r="H356" s="1" t="s">
-        <v>618</v>
+        <v>41</v>
       </c>
       <c r="I356" s="1" t="s">
         <v>14</v>
@@ -12971,10 +12674,10 @@
     </row>
     <row r="357" spans="1:10">
       <c r="A357" s="1" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>438</v>
@@ -12982,9 +12685,8 @@
       <c r="D357" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E357" s="1"/>
       <c r="H357" s="1" t="s">
-        <v>618</v>
+        <v>41</v>
       </c>
       <c r="I357" s="1" t="s">
         <v>14</v>
@@ -12995,10 +12697,10 @@
     </row>
     <row r="358" spans="1:10">
       <c r="A358" s="1" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>438</v>
@@ -13006,9 +12708,8 @@
       <c r="D358" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E358" s="1"/>
       <c r="H358" s="1" t="s">
-        <v>618</v>
+        <v>41</v>
       </c>
       <c r="I358" s="1" t="s">
         <v>14</v>
@@ -13019,10 +12720,10 @@
     </row>
     <row r="359" spans="1:10">
       <c r="A359" s="1" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>438</v>
@@ -13030,7 +12731,6 @@
       <c r="D359" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E359" s="1"/>
       <c r="H359" s="1" t="s">
         <v>41</v>
       </c>
@@ -13043,10 +12743,10 @@
     </row>
     <row r="360" spans="1:10">
       <c r="A360" s="1" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>438</v>
@@ -13054,7 +12754,6 @@
       <c r="D360" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E360" s="1"/>
       <c r="H360" s="1" t="s">
         <v>41</v>
       </c>
@@ -13067,10 +12766,10 @@
     </row>
     <row r="361" spans="1:10">
       <c r="A361" s="1" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>438</v>
@@ -13078,7 +12777,6 @@
       <c r="D361" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E361" s="1"/>
       <c r="H361" s="1" t="s">
         <v>41</v>
       </c>
@@ -13091,10 +12789,10 @@
     </row>
     <row r="362" spans="1:10">
       <c r="A362" s="1" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>438</v>
@@ -13102,7 +12800,6 @@
       <c r="D362" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E362" s="1"/>
       <c r="H362" s="1" t="s">
         <v>41</v>
       </c>
@@ -13115,10 +12812,10 @@
     </row>
     <row r="363" spans="1:10">
       <c r="A363" s="1" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>438</v>
@@ -13126,7 +12823,6 @@
       <c r="D363" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E363" s="1"/>
       <c r="H363" s="1" t="s">
         <v>41</v>
       </c>
@@ -13139,10 +12835,10 @@
     </row>
     <row r="364" spans="1:10">
       <c r="A364" s="1" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>438</v>
@@ -13150,7 +12846,6 @@
       <c r="D364" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E364" s="1"/>
       <c r="H364" s="1" t="s">
         <v>41</v>
       </c>
@@ -13163,10 +12858,10 @@
     </row>
     <row r="365" spans="1:10">
       <c r="A365" s="1" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>438</v>
@@ -13174,7 +12869,6 @@
       <c r="D365" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E365" s="1"/>
       <c r="H365" s="1" t="s">
         <v>41</v>
       </c>
@@ -13187,10 +12881,10 @@
     </row>
     <row r="366" spans="1:10">
       <c r="A366" s="1" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>438</v>
@@ -13198,7 +12892,6 @@
       <c r="D366" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E366" s="1"/>
       <c r="H366" s="1" t="s">
         <v>41</v>
       </c>
@@ -13211,20 +12904,19 @@
     </row>
     <row r="367" spans="1:10">
       <c r="A367" s="1" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>438</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E367" s="1"/>
+        <v>485</v>
+      </c>
       <c r="H367" s="1" t="s">
-        <v>41</v>
+        <v>595</v>
       </c>
       <c r="I367" s="1" t="s">
         <v>14</v>
@@ -13235,20 +12927,19 @@
     </row>
     <row r="368" spans="1:10">
       <c r="A368" s="1" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>438</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E368" s="1"/>
+        <v>885</v>
+      </c>
       <c r="H368" s="1" t="s">
-        <v>41</v>
+        <v>627</v>
       </c>
       <c r="I368" s="1" t="s">
         <v>14</v>
@@ -13259,18 +12950,17 @@
     </row>
     <row r="369" spans="1:10">
       <c r="A369" s="1" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>438</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E369" s="1"/>
+        <v>694</v>
+      </c>
       <c r="H369" s="1" t="s">
         <v>41</v>
       </c>
@@ -13283,20 +12973,19 @@
     </row>
     <row r="370" spans="1:10">
       <c r="A370" s="1" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>438</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E370" s="1"/>
+        <v>13</v>
+      </c>
       <c r="H370" s="1" t="s">
-        <v>41</v>
+        <v>609</v>
       </c>
       <c r="I370" s="1" t="s">
         <v>14</v>
@@ -13307,20 +12996,19 @@
     </row>
     <row r="371" spans="1:10">
       <c r="A371" s="1" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>438</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E371" s="1"/>
+        <v>892</v>
+      </c>
       <c r="H371" s="1" t="s">
-        <v>41</v>
+        <v>627</v>
       </c>
       <c r="I371" s="1" t="s">
         <v>14</v>
@@ -13331,20 +13019,19 @@
     </row>
     <row r="372" spans="1:10">
       <c r="A372" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="B372" s="3" t="s">
         <v>894</v>
-      </c>
-      <c r="B372" s="3" t="s">
-        <v>895</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>438</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="E372" s="1"/>
+        <v>895</v>
+      </c>
       <c r="H372" s="1" t="s">
-        <v>595</v>
+        <v>896</v>
       </c>
       <c r="I372" s="1" t="s">
         <v>14</v>
@@ -13355,20 +13042,19 @@
     </row>
     <row r="373" spans="1:10">
       <c r="A373" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>438</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>898</v>
-      </c>
-      <c r="E373" s="1"/>
+        <v>899</v>
+      </c>
       <c r="H373" s="1" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="I373" s="1" t="s">
         <v>14</v>
@@ -13379,20 +13065,19 @@
     </row>
     <row r="374" spans="1:10">
       <c r="A374" s="1" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>438</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="E374" s="1"/>
+        <v>902</v>
+      </c>
       <c r="H374" s="1" t="s">
-        <v>41</v>
+        <v>627</v>
       </c>
       <c r="I374" s="1" t="s">
         <v>14</v>
@@ -13403,20 +13088,19 @@
     </row>
     <row r="375" spans="1:10">
       <c r="A375" s="1" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>438</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E375" s="1"/>
+        <v>902</v>
+      </c>
       <c r="H375" s="1" t="s">
-        <v>609</v>
+        <v>627</v>
       </c>
       <c r="I375" s="1" t="s">
         <v>14</v>
@@ -13427,20 +13111,19 @@
     </row>
     <row r="376" spans="1:10">
       <c r="A376" s="1" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>438</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>905</v>
-      </c>
-      <c r="E376" s="1"/>
+        <v>907</v>
+      </c>
       <c r="H376" s="1" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="I376" s="1" t="s">
         <v>14</v>
@@ -13451,20 +13134,19 @@
     </row>
     <row r="377" spans="1:10">
       <c r="A377" s="1" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>438</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>908</v>
-      </c>
-      <c r="E377" s="1"/>
+        <v>25</v>
+      </c>
       <c r="H377" s="1" t="s">
-        <v>909</v>
+        <v>627</v>
       </c>
       <c r="I377" s="1" t="s">
         <v>14</v>
@@ -13481,14 +13163,13 @@
         <v>911</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>438</v>
+        <v>912</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>912</v>
-      </c>
-      <c r="E378" s="1"/>
+        <v>913</v>
+      </c>
       <c r="H378" s="1" t="s">
-        <v>618</v>
+        <v>41</v>
       </c>
       <c r="I378" s="1" t="s">
         <v>14</v>
@@ -13499,20 +13180,19 @@
     </row>
     <row r="379" spans="1:10">
       <c r="A379" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>438</v>
+        <v>484</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>915</v>
-      </c>
-      <c r="E379" s="1"/>
+        <v>916</v>
+      </c>
       <c r="H379" s="1" t="s">
-        <v>618</v>
+        <v>595</v>
       </c>
       <c r="I379" s="1" t="s">
         <v>14</v>
@@ -13523,20 +13203,19 @@
     </row>
     <row r="380" spans="1:10">
       <c r="A380" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>438</v>
+        <v>553</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>915</v>
-      </c>
-      <c r="E380" s="1"/>
+        <v>134</v>
+      </c>
       <c r="H380" s="1" t="s">
-        <v>618</v>
+        <v>641</v>
       </c>
       <c r="I380" s="1" t="s">
         <v>14</v>
@@ -13547,20 +13226,19 @@
     </row>
     <row r="381" spans="1:10">
       <c r="A381" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>438</v>
+        <v>553</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>920</v>
-      </c>
-      <c r="E381" s="1"/>
+        <v>347</v>
+      </c>
       <c r="H381" s="1" t="s">
-        <v>609</v>
+        <v>41</v>
       </c>
       <c r="I381" s="1" t="s">
         <v>14</v>
@@ -13577,17 +13255,16 @@
         <v>922</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>438</v>
+        <v>553</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E382" s="1"/>
+        <v>134</v>
+      </c>
       <c r="H382" s="1" t="s">
-        <v>618</v>
+        <v>41</v>
       </c>
       <c r="I382" s="1" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="J382" s="1" t="s">
         <v>574</v>
@@ -13601,14 +13278,13 @@
         <v>924</v>
       </c>
       <c r="C383" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="D383" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H383" s="1" t="s">
         <v>925</v>
-      </c>
-      <c r="D383" s="3" t="s">
-        <v>926</v>
-      </c>
-      <c r="E383" s="1"/>
-      <c r="H383" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="I383" s="1" t="s">
         <v>14</v>
@@ -13619,20 +13295,19 @@
     </row>
     <row r="384" spans="1:10">
       <c r="A384" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="B384" s="3" t="s">
         <v>927</v>
       </c>
-      <c r="B384" s="3" t="s">
+      <c r="C384" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="D384" s="3" t="s">
         <v>928</v>
       </c>
-      <c r="C384" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D384" s="3" t="s">
-        <v>929</v>
-      </c>
-      <c r="E384" s="1"/>
       <c r="H384" s="1" t="s">
-        <v>595</v>
+        <v>925</v>
       </c>
       <c r="I384" s="1" t="s">
         <v>14</v>
@@ -13643,20 +13318,19 @@
     </row>
     <row r="385" spans="1:10">
       <c r="A385" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="B385" s="3" t="s">
         <v>930</v>
       </c>
-      <c r="B385" s="3" t="s">
-        <v>931</v>
-      </c>
       <c r="C385" s="1" t="s">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E385" s="1"/>
+        <v>75</v>
+      </c>
       <c r="H385" s="1" t="s">
-        <v>654</v>
+        <v>925</v>
       </c>
       <c r="I385" s="1" t="s">
         <v>14</v>
@@ -13667,20 +13341,19 @@
     </row>
     <row r="386" spans="1:10">
       <c r="A386" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="B386" s="3" t="s">
         <v>932</v>
       </c>
-      <c r="B386" s="3" t="s">
-        <v>933</v>
-      </c>
       <c r="C386" s="1" t="s">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="E386" s="1"/>
+        <v>75</v>
+      </c>
       <c r="H386" s="1" t="s">
-        <v>41</v>
+        <v>925</v>
       </c>
       <c r="I386" s="1" t="s">
         <v>14</v>
@@ -13691,20 +13364,19 @@
     </row>
     <row r="387" spans="1:10">
       <c r="A387" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="B387" s="3" t="s">
         <v>934</v>
       </c>
-      <c r="B387" s="3" t="s">
-        <v>935</v>
-      </c>
       <c r="C387" s="1" t="s">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E387" s="1"/>
+        <v>355</v>
+      </c>
       <c r="H387" s="1" t="s">
-        <v>41</v>
+        <v>609</v>
       </c>
       <c r="I387" s="1" t="s">
         <v>93</v>
@@ -13715,20 +13387,19 @@
     </row>
     <row r="388" spans="1:10">
       <c r="A388" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="B388" s="3" t="s">
         <v>936</v>
       </c>
-      <c r="B388" s="3" t="s">
+      <c r="C388" s="1" t="s">
         <v>937</v>
-      </c>
-      <c r="C388" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="D388" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E388" s="1"/>
       <c r="H388" s="1" t="s">
-        <v>938</v>
+        <v>41</v>
       </c>
       <c r="I388" s="1" t="s">
         <v>14</v>
@@ -13739,237 +13410,257 @@
     </row>
     <row r="389" spans="1:10">
       <c r="A389" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="B389" s="3" t="s">
         <v>939</v>
       </c>
-      <c r="B389" s="3" t="s">
+      <c r="C389" s="1" t="s">
         <v>940</v>
       </c>
-      <c r="C389" s="1" t="s">
-        <v>570</v>
-      </c>
       <c r="D389" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H389" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I389" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J389" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10">
+      <c r="A390" s="5" t="s">
         <v>941</v>
       </c>
-      <c r="E389" s="1"/>
-      <c r="H389" s="1" t="s">
-        <v>938</v>
-      </c>
-      <c r="I389" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J389" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="390" spans="1:10">
-      <c r="A390" s="1" t="s">
+      <c r="B390" s="6" t="s">
         <v>942</v>
       </c>
-      <c r="B390" s="3" t="s">
+      <c r="C390" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="D390" s="7">
+        <v>598.5</v>
+      </c>
+      <c r="F390" s="8" t="s">
         <v>943</v>
       </c>
-      <c r="C390" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="D390" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E390" s="1"/>
-      <c r="H390" s="1" t="s">
-        <v>938</v>
-      </c>
-      <c r="I390" s="1" t="s">
-        <v>14</v>
+      <c r="G390" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="H390" s="9" t="s">
+        <v>945</v>
+      </c>
+      <c r="I390" s="10" t="s">
+        <v>946</v>
       </c>
       <c r="J390" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="391" spans="1:10">
-      <c r="A391" s="1" t="s">
+      <c r="A391" s="11" t="s">
+        <v>947</v>
+      </c>
+      <c r="B391" s="12" t="s">
+        <v>948</v>
+      </c>
+      <c r="C391" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="D391" s="14">
+        <v>64</v>
+      </c>
+      <c r="F391" s="15">
+        <v>2026</v>
+      </c>
+      <c r="G391" s="16" t="s">
         <v>944</v>
       </c>
-      <c r="B391" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="C391" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="D391" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E391" s="1"/>
-      <c r="H391" s="1" t="s">
-        <v>938</v>
-      </c>
-      <c r="I391" s="1" t="s">
-        <v>14</v>
+      <c r="H391" s="11" t="s">
+        <v>949</v>
+      </c>
+      <c r="I391" s="10" t="s">
+        <v>950</v>
       </c>
       <c r="J391" s="1" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="392" spans="1:10">
-      <c r="A392" s="1" t="s">
-        <v>946</v>
-      </c>
-      <c r="B392" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="C392" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="D392" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="E392" s="1"/>
-      <c r="H392" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="I392" s="1" t="s">
+    <row r="392" ht="26.4" spans="1:10">
+      <c r="A392" s="11" t="s">
+        <v>951</v>
+      </c>
+      <c r="B392" s="12" t="s">
+        <v>952</v>
+      </c>
+      <c r="C392" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="D392" s="14">
+        <v>128</v>
+      </c>
+      <c r="F392" s="17">
+        <v>2026</v>
+      </c>
+      <c r="G392" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="H392" s="11" t="s">
+        <v>953</v>
+      </c>
+      <c r="I392" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="J392" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="393" ht="26.4" spans="1:10">
+      <c r="A393" s="11" t="s">
+        <v>954</v>
+      </c>
+      <c r="B393" s="12" t="s">
+        <v>955</v>
+      </c>
+      <c r="C393" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="D393" s="14">
+        <v>345</v>
+      </c>
+      <c r="F393" s="15">
+        <v>2027</v>
+      </c>
+      <c r="G393" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="H393" s="11" t="s">
+        <v>956</v>
+      </c>
+      <c r="I393" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="J393" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="394" spans="1:10">
+      <c r="A394" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="B394" s="12" t="s">
+        <v>958</v>
+      </c>
+      <c r="C394" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="D394" s="14">
+        <v>72</v>
+      </c>
+      <c r="F394" s="15">
+        <v>2026</v>
+      </c>
+      <c r="G394" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="H394" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="I394" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="J394" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="395" spans="1:10">
+      <c r="A395" s="18" t="s">
+        <v>960</v>
+      </c>
+      <c r="B395" s="12" t="s">
+        <v>961</v>
+      </c>
+      <c r="C395" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="D395" s="14">
+        <v>150</v>
+      </c>
+      <c r="F395" s="15">
+        <v>2027</v>
+      </c>
+      <c r="G395" s="12" t="s">
+        <v>962</v>
+      </c>
+      <c r="H395" s="11" t="s">
+        <v>949</v>
+      </c>
+      <c r="I395" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J392" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="393" spans="1:10">
-      <c r="A393" s="1" t="s">
-        <v>948</v>
-      </c>
-      <c r="B393" s="3" t="s">
-        <v>949</v>
-      </c>
-      <c r="C393" s="1" t="s">
-        <v>950</v>
-      </c>
-      <c r="D393" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E393" s="1"/>
-      <c r="H393" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I393" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J393" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="394" spans="1:10">
-      <c r="A394" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="B394" s="3" t="s">
-        <v>952</v>
-      </c>
-      <c r="C394" s="1" t="s">
-        <v>953</v>
-      </c>
-      <c r="D394" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E394" s="1"/>
-      <c r="H394" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I394" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J394" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="395" spans="1:10">
-      <c r="A395" s="5" t="s">
-        <v>954</v>
-      </c>
-      <c r="B395" s="6" t="s">
-        <v>955</v>
-      </c>
-      <c r="C395" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="D395" s="7">
-        <v>598.5</v>
-      </c>
-      <c r="F395" s="8" t="s">
-        <v>956</v>
-      </c>
-      <c r="G395" s="9" t="s">
-        <v>957</v>
-      </c>
-      <c r="H395" s="9" t="s">
-        <v>958</v>
-      </c>
-      <c r="I395" s="10" t="s">
-        <v>959</v>
-      </c>
       <c r="J395" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="396" spans="1:10">
-      <c r="A396" s="11" t="s">
-        <v>960</v>
+      <c r="A396" s="18" t="s">
+        <v>963</v>
       </c>
       <c r="B396" s="12" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="C396" s="13" t="s">
         <v>292</v>
       </c>
       <c r="D396" s="14">
-        <v>64</v>
+        <v>304</v>
       </c>
       <c r="F396" s="15">
-        <v>2026</v>
-      </c>
-      <c r="G396" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H396" s="11" t="s">
-        <v>962</v>
-      </c>
+        <v>2028</v>
+      </c>
+      <c r="G396" s="12"/>
+      <c r="H396" s="12"/>
       <c r="I396" s="10" t="s">
-        <v>963</v>
+        <v>950</v>
       </c>
       <c r="J396" s="1" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="397" ht="26.4" spans="1:10">
-      <c r="A397" s="11" t="s">
-        <v>964</v>
+    <row r="397" spans="1:10">
+      <c r="A397" s="18" t="s">
+        <v>965</v>
       </c>
       <c r="B397" s="12" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C397" s="13" t="s">
         <v>292</v>
       </c>
       <c r="D397" s="14">
-        <v>128</v>
-      </c>
-      <c r="F397" s="17">
-        <v>2026</v>
+        <v>528</v>
+      </c>
+      <c r="F397" s="15">
+        <v>2028</v>
       </c>
       <c r="G397" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H397" s="11" t="s">
-        <v>966</v>
+        <v>944</v>
+      </c>
+      <c r="H397" s="12" t="s">
+        <v>959</v>
       </c>
       <c r="I397" s="10" t="s">
-        <v>963</v>
+        <v>950</v>
       </c>
       <c r="J397" s="1" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="398" ht="26.4" spans="1:10">
-      <c r="A398" s="11" t="s">
+    <row r="398" spans="1:10">
+      <c r="A398" s="18" t="s">
         <v>967</v>
       </c>
       <c r="B398" s="12" t="s">
@@ -13979,26 +13670,24 @@
         <v>292</v>
       </c>
       <c r="D398" s="14">
-        <v>345</v>
+        <v>200</v>
       </c>
       <c r="F398" s="15">
-        <v>2027</v>
-      </c>
-      <c r="G398" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H398" s="11" t="s">
+        <v>2028</v>
+      </c>
+      <c r="G398" s="16"/>
+      <c r="H398" s="19" t="s">
         <v>969</v>
       </c>
       <c r="I398" s="10" t="s">
-        <v>963</v>
+        <v>950</v>
       </c>
       <c r="J398" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="399" spans="1:10">
-      <c r="A399" s="11" t="s">
+      <c r="A399" s="18" t="s">
         <v>970</v>
       </c>
       <c r="B399" s="12" t="s">
@@ -14008,19 +13697,17 @@
         <v>292</v>
       </c>
       <c r="D399" s="14">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="F399" s="15">
-        <v>2026</v>
-      </c>
-      <c r="G399" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H399" s="11" t="s">
-        <v>972</v>
+        <v>2028</v>
+      </c>
+      <c r="G399" s="16"/>
+      <c r="H399" s="19" t="s">
+        <v>969</v>
       </c>
       <c r="I399" s="10" t="s">
-        <v>963</v>
+        <v>950</v>
       </c>
       <c r="J399" s="1" t="s">
         <v>574</v>
@@ -14028,28 +13715,26 @@
     </row>
     <row r="400" spans="1:10">
       <c r="A400" s="18" t="s">
+        <v>972</v>
+      </c>
+      <c r="B400" s="12" t="s">
         <v>973</v>
-      </c>
-      <c r="B400" s="12" t="s">
-        <v>974</v>
       </c>
       <c r="C400" s="13" t="s">
         <v>292</v>
       </c>
       <c r="D400" s="14">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F400" s="15">
         <v>2027</v>
       </c>
-      <c r="G400" s="12" t="s">
-        <v>975</v>
-      </c>
-      <c r="H400" s="11" t="s">
-        <v>962</v>
-      </c>
-      <c r="I400" s="1" t="s">
-        <v>93</v>
+      <c r="G400" s="16"/>
+      <c r="H400" s="19" t="s">
+        <v>974</v>
+      </c>
+      <c r="I400" s="10" t="s">
+        <v>950</v>
       </c>
       <c r="J400" s="1" t="s">
         <v>574</v>
@@ -14057,24 +13742,26 @@
     </row>
     <row r="401" spans="1:10">
       <c r="A401" s="18" t="s">
+        <v>975</v>
+      </c>
+      <c r="B401" s="12" t="s">
         <v>976</v>
-      </c>
-      <c r="B401" s="12" t="s">
-        <v>977</v>
       </c>
       <c r="C401" s="13" t="s">
         <v>292</v>
       </c>
       <c r="D401" s="14">
-        <v>304</v>
+        <v>150</v>
       </c>
       <c r="F401" s="15">
-        <v>2028</v>
-      </c>
-      <c r="G401" s="12"/>
-      <c r="H401" s="12"/>
+        <v>2029</v>
+      </c>
+      <c r="G401" s="16"/>
+      <c r="H401" s="19" t="s">
+        <v>977</v>
+      </c>
       <c r="I401" s="10" t="s">
-        <v>963</v>
+        <v>950</v>
       </c>
       <c r="J401" s="1" t="s">
         <v>574</v>
@@ -14087,50 +13774,52 @@
       <c r="B402" s="12" t="s">
         <v>979</v>
       </c>
-      <c r="C402" s="13" t="s">
-        <v>292</v>
+      <c r="C402" s="20" t="s">
+        <v>432</v>
       </c>
       <c r="D402" s="14">
-        <v>528</v>
-      </c>
-      <c r="F402" s="15">
-        <v>2028</v>
-      </c>
-      <c r="G402" s="16" t="s">
-        <v>957</v>
+        <v>50</v>
+      </c>
+      <c r="F402" s="16">
+        <v>2027</v>
+      </c>
+      <c r="G402" s="12" t="s">
+        <v>980</v>
       </c>
       <c r="H402" s="12" t="s">
-        <v>972</v>
-      </c>
-      <c r="I402" s="10" t="s">
-        <v>963</v>
+        <v>981</v>
+      </c>
+      <c r="I402" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="J402" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="403" spans="1:10">
-      <c r="A403" s="18" t="s">
+      <c r="A403" s="21" t="s">
+        <v>982</v>
+      </c>
+      <c r="B403" s="22" t="s">
+        <v>983</v>
+      </c>
+      <c r="C403" s="13" t="s">
+        <v>570</v>
+      </c>
+      <c r="D403" s="23">
+        <v>46</v>
+      </c>
+      <c r="F403" s="22">
+        <v>2026</v>
+      </c>
+      <c r="G403" s="12" t="s">
         <v>980</v>
       </c>
-      <c r="B403" s="12" t="s">
-        <v>981</v>
-      </c>
-      <c r="C403" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="D403" s="14">
-        <v>200</v>
-      </c>
-      <c r="F403" s="15">
-        <v>2028</v>
-      </c>
-      <c r="G403" s="16"/>
-      <c r="H403" s="19" t="s">
-        <v>982</v>
-      </c>
-      <c r="I403" s="10" t="s">
-        <v>963</v>
+      <c r="H403" s="24" t="s">
+        <v>984</v>
+      </c>
+      <c r="I403" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="J403" s="1" t="s">
         <v>574</v>
@@ -14138,167 +13827,171 @@
     </row>
     <row r="404" spans="1:10">
       <c r="A404" s="18" t="s">
-        <v>983</v>
-      </c>
-      <c r="B404" s="12" t="s">
-        <v>984</v>
+        <v>985</v>
+      </c>
+      <c r="B404" s="15" t="s">
+        <v>986</v>
       </c>
       <c r="C404" s="13" t="s">
-        <v>292</v>
+        <v>570</v>
       </c>
       <c r="D404" s="14">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="F404" s="15">
-        <v>2028</v>
-      </c>
-      <c r="G404" s="16"/>
-      <c r="H404" s="19" t="s">
-        <v>982</v>
-      </c>
-      <c r="I404" s="10" t="s">
-        <v>963</v>
+        <v>2026</v>
+      </c>
+      <c r="G404" s="12" t="s">
+        <v>962</v>
+      </c>
+      <c r="H404" s="12" t="s">
+        <v>987</v>
+      </c>
+      <c r="I404" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="J404" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="405" spans="1:10">
-      <c r="A405" s="18" t="s">
-        <v>985</v>
+      <c r="A405" s="11" t="s">
+        <v>988</v>
       </c>
       <c r="B405" s="12" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="C405" s="13" t="s">
-        <v>292</v>
+        <v>570</v>
       </c>
       <c r="D405" s="14">
-        <v>50</v>
-      </c>
-      <c r="F405" s="15">
-        <v>2027</v>
-      </c>
-      <c r="G405" s="16"/>
-      <c r="H405" s="19" t="s">
-        <v>987</v>
-      </c>
+        <v>85.8</v>
+      </c>
+      <c r="F405" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G405" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="H405" s="12"/>
       <c r="I405" s="10" t="s">
-        <v>963</v>
+        <v>946</v>
       </c>
       <c r="J405" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="406" spans="1:10">
-      <c r="A406" s="18" t="s">
-        <v>988</v>
+      <c r="A406" s="11" t="s">
+        <v>990</v>
       </c>
       <c r="B406" s="12" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C406" s="13" t="s">
-        <v>292</v>
+        <v>570</v>
       </c>
       <c r="D406" s="14">
-        <v>150</v>
-      </c>
-      <c r="F406" s="15">
-        <v>2029</v>
-      </c>
-      <c r="G406" s="16"/>
-      <c r="H406" s="19" t="s">
-        <v>990</v>
+        <v>72</v>
+      </c>
+      <c r="F406" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G406" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="H406" s="12" t="s">
+        <v>992</v>
       </c>
       <c r="I406" s="10" t="s">
-        <v>963</v>
+        <v>946</v>
       </c>
       <c r="J406" s="1" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="407" spans="1:10">
-      <c r="A407" s="18" t="s">
-        <v>991</v>
-      </c>
-      <c r="B407" s="12" t="s">
+    <row r="407" ht="26.4" spans="1:10">
+      <c r="A407" s="25" t="s">
+        <v>993</v>
+      </c>
+      <c r="B407" s="16" t="s">
+        <v>994</v>
+      </c>
+      <c r="C407" s="13" t="s">
+        <v>570</v>
+      </c>
+      <c r="D407" s="14">
+        <v>30</v>
+      </c>
+      <c r="F407" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G407" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="H407" s="12" t="s">
         <v>992</v>
       </c>
-      <c r="C407" s="20" t="s">
-        <v>432</v>
-      </c>
-      <c r="D407" s="14">
-        <v>50</v>
-      </c>
-      <c r="F407" s="16">
-        <v>2027</v>
-      </c>
-      <c r="G407" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="H407" s="12" t="s">
-        <v>994</v>
-      </c>
-      <c r="I407" s="1" t="s">
-        <v>93</v>
+      <c r="I407" s="10" t="s">
+        <v>946</v>
       </c>
       <c r="J407" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="408" spans="1:10">
-      <c r="A408" s="21" t="s">
+      <c r="A408" s="11" t="s">
         <v>995</v>
       </c>
-      <c r="B408" s="22" t="s">
+      <c r="B408" s="12" t="s">
         <v>996</v>
       </c>
       <c r="C408" s="13" t="s">
         <v>570</v>
       </c>
-      <c r="D408" s="23">
-        <v>46</v>
-      </c>
-      <c r="F408" s="22">
-        <v>2026</v>
-      </c>
-      <c r="G408" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="H408" s="24" t="s">
+      <c r="D408" s="14">
+        <v>28.8</v>
+      </c>
+      <c r="F408" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G408" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="H408" s="12" t="s">
         <v>997</v>
       </c>
-      <c r="I408" s="1" t="s">
-        <v>93</v>
+      <c r="I408" s="10" t="s">
+        <v>946</v>
       </c>
       <c r="J408" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="409" spans="1:10">
-      <c r="A409" s="18" t="s">
+      <c r="A409" s="11" t="s">
         <v>998</v>
       </c>
-      <c r="B409" s="15" t="s">
+      <c r="B409" s="12" t="s">
         <v>999</v>
       </c>
       <c r="C409" s="13" t="s">
         <v>570</v>
       </c>
       <c r="D409" s="14">
-        <v>128</v>
-      </c>
-      <c r="F409" s="15">
-        <v>2026</v>
-      </c>
-      <c r="G409" s="12" t="s">
-        <v>975</v>
+        <v>32</v>
+      </c>
+      <c r="F409" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G409" s="16" t="s">
+        <v>944</v>
       </c>
       <c r="H409" s="12" t="s">
-        <v>1000</v>
-      </c>
-      <c r="I409" s="1" t="s">
-        <v>93</v>
+        <v>997</v>
+      </c>
+      <c r="I409" s="10" t="s">
+        <v>946</v>
       </c>
       <c r="J409" s="1" t="s">
         <v>574</v>
@@ -14306,200 +13999,202 @@
     </row>
     <row r="410" spans="1:10">
       <c r="A410" s="11" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B410" s="12" t="s">
         <v>1001</v>
-      </c>
-      <c r="B410" s="12" t="s">
-        <v>1002</v>
       </c>
       <c r="C410" s="13" t="s">
         <v>570</v>
       </c>
       <c r="D410" s="14">
-        <v>85.8</v>
+        <v>49.5</v>
       </c>
       <c r="F410" s="15" t="s">
-        <v>956</v>
+        <v>943</v>
       </c>
       <c r="G410" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H410" s="12"/>
+        <v>944</v>
+      </c>
+      <c r="H410" s="12" t="s">
+        <v>992</v>
+      </c>
       <c r="I410" s="10" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="J410" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="411" spans="1:10">
-      <c r="A411" s="11" t="s">
+      <c r="A411" s="25" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B411" s="16" t="s">
         <v>1003</v>
-      </c>
-      <c r="B411" s="12" t="s">
-        <v>1004</v>
       </c>
       <c r="C411" s="13" t="s">
         <v>570</v>
       </c>
       <c r="D411" s="14">
-        <v>72</v>
+        <v>49.5</v>
       </c>
       <c r="F411" s="15" t="s">
-        <v>956</v>
+        <v>943</v>
       </c>
       <c r="G411" s="16" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="H411" s="12" t="s">
+        <v>992</v>
+      </c>
+      <c r="I411" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J411" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="412" spans="1:10">
+      <c r="A412" s="12" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B412" s="12" t="s">
         <v>1005</v>
-      </c>
-      <c r="I411" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J411" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="412" ht="26.4" spans="1:10">
-      <c r="A412" s="25" t="s">
-        <v>1006</v>
-      </c>
-      <c r="B412" s="16" t="s">
-        <v>1007</v>
       </c>
       <c r="C412" s="13" t="s">
         <v>570</v>
       </c>
-      <c r="D412" s="14">
-        <v>30</v>
-      </c>
-      <c r="F412" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G412" s="16" t="s">
-        <v>957</v>
+      <c r="D412" s="23">
+        <v>29.7</v>
+      </c>
+      <c r="F412" s="12">
+        <v>2026</v>
+      </c>
+      <c r="G412" s="12" t="s">
+        <v>944</v>
       </c>
       <c r="H412" s="12" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
       <c r="I412" s="10" t="s">
-        <v>959</v>
+        <v>950</v>
       </c>
       <c r="J412" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="413" spans="1:10">
-      <c r="A413" s="11" t="s">
-        <v>1008</v>
+      <c r="A413" s="12" t="s">
+        <v>1006</v>
       </c>
       <c r="B413" s="12" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C413" s="13" t="s">
         <v>570</v>
       </c>
       <c r="D413" s="14">
-        <v>28.8</v>
+        <v>49.6</v>
       </c>
       <c r="F413" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G413" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H413" s="12" t="s">
-        <v>1010</v>
+        <v>943</v>
+      </c>
+      <c r="G413" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="H413" s="16" t="s">
+        <v>997</v>
       </c>
       <c r="I413" s="10" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="J413" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="414" spans="1:10">
-      <c r="A414" s="11" t="s">
-        <v>1011</v>
+      <c r="A414" s="12" t="s">
+        <v>1008</v>
       </c>
       <c r="B414" s="12" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="C414" s="13" t="s">
         <v>570</v>
       </c>
       <c r="D414" s="14">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F414" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G414" s="16" t="s">
-        <v>957</v>
+        <v>943</v>
+      </c>
+      <c r="G414" s="12" t="s">
+        <v>944</v>
       </c>
       <c r="H414" s="12" t="s">
+        <v>992</v>
+      </c>
+      <c r="I414" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J414" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="415" spans="1:10">
+      <c r="A415" s="12" t="s">
         <v>1010</v>
       </c>
-      <c r="I414" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J414" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="415" spans="1:10">
-      <c r="A415" s="11" t="s">
-        <v>1013</v>
-      </c>
       <c r="B415" s="12" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="C415" s="13" t="s">
         <v>570</v>
       </c>
       <c r="D415" s="14">
-        <v>49.5</v>
+        <v>23.1</v>
       </c>
       <c r="F415" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G415" s="16" t="s">
-        <v>957</v>
+        <v>943</v>
+      </c>
+      <c r="G415" s="12" t="s">
+        <v>944</v>
       </c>
       <c r="H415" s="12" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
       <c r="I415" s="10" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="J415" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="416" spans="1:10">
-      <c r="A416" s="25" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B416" s="16" t="s">
-        <v>1016</v>
+      <c r="A416" s="12" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B416" s="12" t="s">
+        <v>1013</v>
       </c>
       <c r="C416" s="13" t="s">
         <v>570</v>
       </c>
       <c r="D416" s="14">
-        <v>49.5</v>
+        <v>48</v>
       </c>
       <c r="F416" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G416" s="16" t="s">
-        <v>957</v>
+        <v>943</v>
+      </c>
+      <c r="G416" s="12" t="s">
+        <v>944</v>
       </c>
       <c r="H416" s="12" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="I416" s="10" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="J416" s="1" t="s">
         <v>574</v>
@@ -14507,39 +14202,39 @@
     </row>
     <row r="417" spans="1:10">
       <c r="A417" s="12" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B417" s="12" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="C417" s="13" t="s">
         <v>570</v>
       </c>
-      <c r="D417" s="23">
-        <v>29.7</v>
-      </c>
-      <c r="F417" s="12">
-        <v>2026</v>
+      <c r="D417" s="14">
+        <v>26.4</v>
+      </c>
+      <c r="F417" s="15" t="s">
+        <v>943</v>
       </c>
       <c r="G417" s="12" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="H417" s="12" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
       <c r="I417" s="10" t="s">
-        <v>963</v>
+        <v>946</v>
       </c>
       <c r="J417" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="418" spans="1:10">
-      <c r="A418" s="12" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B418" s="12" t="s">
-        <v>1020</v>
+      <c r="A418" s="16" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B418" s="16" t="s">
+        <v>1007</v>
       </c>
       <c r="C418" s="13" t="s">
         <v>570</v>
@@ -14548,16 +14243,16 @@
         <v>49.6</v>
       </c>
       <c r="F418" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G418" s="12" t="s">
-        <v>957</v>
+        <v>943</v>
+      </c>
+      <c r="G418" s="16" t="s">
+        <v>944</v>
       </c>
       <c r="H418" s="16" t="s">
-        <v>1010</v>
+        <v>997</v>
       </c>
       <c r="I418" s="10" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="J418" s="1" t="s">
         <v>574</v>
@@ -14565,461 +14260,457 @@
     </row>
     <row r="419" spans="1:10">
       <c r="A419" s="12" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B419" s="11" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C419" s="20" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D419" s="14">
+        <v>66</v>
+      </c>
+      <c r="F419" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G419" s="26"/>
+      <c r="H419" s="27" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I419" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J419" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="420" spans="1:10">
+      <c r="A420" s="11" t="s">
         <v>1021</v>
       </c>
-      <c r="B419" s="12" t="s">
+      <c r="B420" s="22" t="s">
         <v>1022</v>
       </c>
-      <c r="C419" s="13" t="s">
-        <v>570</v>
-      </c>
-      <c r="D419" s="14">
-        <v>132</v>
-      </c>
-      <c r="F419" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G419" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H419" s="12" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I419" s="10" t="s">
+      <c r="C420" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="D420" s="14">
+        <v>56</v>
+      </c>
+      <c r="F420" s="15">
+        <v>2028</v>
+      </c>
+      <c r="G420" s="16" t="s">
+        <v>962</v>
+      </c>
+      <c r="H420" s="11" t="s">
         <v>959</v>
       </c>
-      <c r="J419" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="420" spans="1:10">
-      <c r="A420" s="12" t="s">
+      <c r="I420" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J420" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="421" spans="1:10">
+      <c r="A421" s="11" t="s">
         <v>1023</v>
       </c>
-      <c r="B420" s="12" t="s">
+      <c r="B421" s="6" t="s">
         <v>1024</v>
       </c>
-      <c r="C420" s="13" t="s">
-        <v>570</v>
-      </c>
-      <c r="D420" s="14">
-        <v>23.1</v>
-      </c>
-      <c r="F420" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G420" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H420" s="12" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I420" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J420" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="421" spans="1:10">
-      <c r="A421" s="12" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B421" s="12" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C421" s="13" t="s">
-        <v>570</v>
+      <c r="C421" s="20" t="s">
+        <v>228</v>
       </c>
       <c r="D421" s="14">
         <v>48</v>
       </c>
-      <c r="F421" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G421" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H421" s="12" t="s">
-        <v>1010</v>
-      </c>
-      <c r="I421" s="10" t="s">
+      <c r="F421" s="15">
+        <v>2028</v>
+      </c>
+      <c r="G421" s="16" t="s">
+        <v>962</v>
+      </c>
+      <c r="H421" s="11" t="s">
         <v>959</v>
       </c>
+      <c r="I421" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="J421" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="422" spans="1:10">
-      <c r="A422" s="12" t="s">
+      <c r="A422" s="28" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B422" s="12" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C422" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D422" s="23">
+        <v>100</v>
+      </c>
+      <c r="F422" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G422" s="12" t="s">
         <v>1027</v>
       </c>
-      <c r="B422" s="12" t="s">
+      <c r="H422" s="12" t="s">
         <v>1028</v>
       </c>
-      <c r="C422" s="13" t="s">
-        <v>570</v>
-      </c>
-      <c r="D422" s="14">
-        <v>26.4</v>
-      </c>
-      <c r="F422" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G422" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H422" s="12" t="s">
-        <v>1005</v>
-      </c>
       <c r="I422" s="10" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="J422" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="423" spans="1:10">
-      <c r="A423" s="16" t="s">
+      <c r="A423" s="29" t="s">
         <v>1029</v>
       </c>
-      <c r="B423" s="16" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C423" s="13" t="s">
-        <v>570</v>
-      </c>
-      <c r="D423" s="14">
-        <v>49.6</v>
+      <c r="B423" s="12" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C423" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D423" s="23">
+        <v>51.2</v>
       </c>
       <c r="F423" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G423" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H423" s="16" t="s">
-        <v>1010</v>
+        <v>943</v>
+      </c>
+      <c r="G423" s="12" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H423" s="12" t="s">
+        <v>997</v>
       </c>
       <c r="I423" s="10" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="J423" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="424" spans="1:10">
-      <c r="A424" s="12" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B424" s="11" t="s">
+      <c r="A424" s="28" t="s">
         <v>1031</v>
       </c>
-      <c r="C424" s="20" t="s">
+      <c r="B424" s="12" t="s">
         <v>1032</v>
       </c>
-      <c r="D424" s="14">
-        <v>66</v>
+      <c r="C424" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D424" s="23">
+        <v>51.2</v>
       </c>
       <c r="F424" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G424" s="26"/>
-      <c r="H424" s="27" t="s">
+        <v>943</v>
+      </c>
+      <c r="G424" s="12" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H424" s="12" t="s">
+        <v>997</v>
+      </c>
+      <c r="I424" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J424" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="425" spans="1:10">
+      <c r="A425" s="29" t="s">
         <v>1033</v>
       </c>
-      <c r="I424" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J424" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="425" spans="1:10">
-      <c r="A425" s="11" t="s">
+      <c r="B425" s="12" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C425" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D425" s="23">
+        <v>99.2</v>
+      </c>
+      <c r="F425" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G425" s="12" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H425" s="12" t="s">
+        <v>997</v>
+      </c>
+      <c r="I425" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J425" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10">
+      <c r="A426" s="28" t="s">
         <v>1034</v>
       </c>
-      <c r="B425" s="22" t="s">
+      <c r="B426" s="12" t="s">
         <v>1035</v>
       </c>
-      <c r="C425" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="D425" s="14">
-        <v>56</v>
-      </c>
-      <c r="F425" s="15">
+      <c r="C426" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D426" s="23">
+        <v>105.6</v>
+      </c>
+      <c r="F426" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G426" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="H426" s="12" t="s">
+        <v>1036</v>
+      </c>
+      <c r="I426" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J426" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="427" spans="1:10">
+      <c r="A427" s="11" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B427" s="12" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C427" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="D427" s="14">
+        <v>513.5</v>
+      </c>
+      <c r="F427" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G427" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="H427" s="12" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I427" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J427" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="428" spans="1:10">
+      <c r="A428" s="11" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B428" s="12" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C428" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="D428" s="14">
+        <v>513.5</v>
+      </c>
+      <c r="F428" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G428" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="H428" s="12" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I428" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J428" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="429" spans="1:10">
+      <c r="A429" s="21" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B429" s="12" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C429" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="D429" s="14">
+        <v>104</v>
+      </c>
+      <c r="F429" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G429" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="H429" s="11" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I429" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J429" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10">
+      <c r="A430" s="12" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B430" s="12" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C430" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="D430" s="14">
+        <v>52</v>
+      </c>
+      <c r="F430" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G430" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="H430" s="11" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I430" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J430" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10">
+      <c r="A431" s="12" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B431" s="12" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C431" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="D431" s="23">
+        <v>200</v>
+      </c>
+      <c r="F431" s="12">
+        <v>2026</v>
+      </c>
+      <c r="G431" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="H431" s="30" t="s">
+        <v>949</v>
+      </c>
+      <c r="I431" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="J431" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="432" spans="1:10">
+      <c r="A432" s="18" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B432" s="12" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C432" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D432" s="14">
+        <v>806</v>
+      </c>
+      <c r="F432" s="12">
         <v>2028</v>
       </c>
-      <c r="G425" s="16" t="s">
-        <v>975</v>
-      </c>
-      <c r="H425" s="11" t="s">
-        <v>972</v>
-      </c>
-      <c r="I425" s="1" t="s">
+      <c r="G432" s="12" t="s">
+        <v>980</v>
+      </c>
+      <c r="H432" s="11" t="s">
+        <v>1049</v>
+      </c>
+      <c r="I432" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J425" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="426" spans="1:10">
-      <c r="A426" s="11" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B426" s="6" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C426" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="D426" s="14">
-        <v>48</v>
-      </c>
-      <c r="F426" s="15">
-        <v>2028</v>
-      </c>
-      <c r="G426" s="16" t="s">
-        <v>975</v>
-      </c>
-      <c r="H426" s="11" t="s">
-        <v>972</v>
-      </c>
-      <c r="I426" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J426" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="427" spans="1:10">
-      <c r="A427" s="28" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B427" s="12" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C427" s="1" t="s">
+      <c r="J432" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="433" ht="15" spans="1:10">
+      <c r="A433" s="31" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B433" s="12" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C433" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D427" s="23">
-        <v>100</v>
-      </c>
-      <c r="F427" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G427" s="12" t="s">
-        <v>1040</v>
-      </c>
-      <c r="H427" s="12" t="s">
-        <v>1041</v>
-      </c>
-      <c r="I427" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J427" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="428" spans="1:10">
-      <c r="A428" s="29" t="s">
-        <v>1042</v>
-      </c>
-      <c r="B428" s="12" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C428" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D428" s="23">
-        <v>51.2</v>
-      </c>
-      <c r="F428" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G428" s="12" t="s">
-        <v>1040</v>
-      </c>
-      <c r="H428" s="12" t="s">
-        <v>1010</v>
-      </c>
-      <c r="I428" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J428" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="429" spans="1:10">
-      <c r="A429" s="28" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B429" s="12" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C429" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D429" s="23">
-        <v>51.2</v>
-      </c>
-      <c r="F429" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G429" s="12" t="s">
-        <v>1040</v>
-      </c>
-      <c r="H429" s="12" t="s">
-        <v>1010</v>
-      </c>
-      <c r="I429" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J429" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="430" spans="1:10">
-      <c r="A430" s="29" t="s">
-        <v>1046</v>
-      </c>
-      <c r="B430" s="12" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C430" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D430" s="23">
-        <v>99.2</v>
-      </c>
-      <c r="F430" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G430" s="12" t="s">
-        <v>1040</v>
-      </c>
-      <c r="H430" s="12" t="s">
-        <v>1010</v>
-      </c>
-      <c r="I430" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J430" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="431" spans="1:10">
-      <c r="A431" s="28" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B431" s="12" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C431" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D431" s="23">
-        <v>105.6</v>
-      </c>
-      <c r="F431" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G431" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H431" s="12" t="s">
-        <v>1049</v>
-      </c>
-      <c r="I431" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J431" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="432" spans="1:10">
-      <c r="A432" s="11" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B432" s="12" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C432" s="13" t="s">
-        <v>553</v>
-      </c>
-      <c r="D432" s="14">
-        <v>513.5</v>
-      </c>
-      <c r="F432" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G432" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H432" s="12" t="s">
-        <v>1052</v>
-      </c>
-      <c r="I432" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J432" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="433" spans="1:10">
-      <c r="A433" s="11" t="s">
-        <v>1053</v>
-      </c>
-      <c r="B433" s="12" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C433" s="13" t="s">
-        <v>553</v>
-      </c>
       <c r="D433" s="14">
-        <v>513.5</v>
+        <v>50</v>
       </c>
       <c r="F433" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G433" s="16" t="s">
-        <v>957</v>
-      </c>
+        <v>943</v>
+      </c>
+      <c r="G433" s="12"/>
       <c r="H433" s="12" t="s">
         <v>1052</v>
       </c>
       <c r="I433" s="10" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="J433" s="1" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="434" spans="1:10">
-      <c r="A434" s="21" t="s">
-        <v>1055</v>
+    <row r="434" ht="15" spans="1:10">
+      <c r="A434" s="31" t="s">
+        <v>1053</v>
       </c>
       <c r="B434" s="12" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C434" s="13" t="s">
-        <v>553</v>
+        <v>1054</v>
+      </c>
+      <c r="C434" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="D434" s="14">
-        <v>104</v>
-      </c>
-      <c r="F434" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G434" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H434" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F434" s="15">
+        <v>2026</v>
+      </c>
+      <c r="G434" s="12"/>
+      <c r="H434" s="12" t="s">
         <v>1052</v>
       </c>
       <c r="I434" s="10" t="s">
-        <v>959</v>
+        <v>950</v>
       </c>
       <c r="J434" s="1" t="s">
         <v>574</v>
@@ -15027,254 +14718,258 @@
     </row>
     <row r="435" spans="1:10">
       <c r="A435" s="12" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B435" s="12" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C435" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D435" s="14">
+        <v>100</v>
+      </c>
+      <c r="F435" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G435" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="H435" s="12" t="s">
+        <v>1052</v>
+      </c>
+      <c r="I435" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J435" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10">
+      <c r="A436" s="16" t="s">
         <v>1057</v>
       </c>
-      <c r="B435" s="12" t="s">
+      <c r="B436" s="12" t="s">
         <v>1054</v>
       </c>
-      <c r="C435" s="13" t="s">
-        <v>553</v>
-      </c>
-      <c r="D435" s="14">
-        <v>52</v>
-      </c>
-      <c r="F435" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G435" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H435" s="11" t="s">
+      <c r="C436" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D436" s="14">
+        <v>50</v>
+      </c>
+      <c r="F436" s="15">
+        <v>2026</v>
+      </c>
+      <c r="G436" s="16"/>
+      <c r="H436" s="16" t="s">
         <v>1052</v>
       </c>
-      <c r="I435" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J435" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="436" spans="1:10">
-      <c r="A436" s="12" t="s">
+      <c r="I436" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="J436" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10">
+      <c r="A437" s="21" t="s">
         <v>1058</v>
       </c>
-      <c r="B436" s="12" t="s">
+      <c r="B437" s="32" t="s">
         <v>1059</v>
       </c>
-      <c r="C436" s="13" t="s">
-        <v>553</v>
-      </c>
-      <c r="D436" s="23">
-        <v>200</v>
-      </c>
-      <c r="F436" s="12">
+      <c r="C437" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D437" s="23">
+        <v>241</v>
+      </c>
+      <c r="F437" s="32">
         <v>2026</v>
       </c>
-      <c r="G436" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H436" s="30" t="s">
-        <v>962</v>
-      </c>
-      <c r="I436" s="10" t="s">
-        <v>963</v>
-      </c>
-      <c r="J436" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="437" spans="1:10">
-      <c r="A437" s="18" t="s">
-        <v>1060</v>
-      </c>
-      <c r="B437" s="12" t="s">
+      <c r="G437" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="H437" s="11" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I437" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J437" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="438" ht="26.4" spans="1:10">
+      <c r="A438" s="11" t="s">
         <v>1061</v>
       </c>
-      <c r="C437" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D437" s="14">
-        <v>806</v>
-      </c>
-      <c r="F437" s="12">
+      <c r="B438" s="16" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C438" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D438" s="14">
+        <v>552</v>
+      </c>
+      <c r="F438" s="16">
+        <v>2026</v>
+      </c>
+      <c r="G438" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="H438" s="11" t="s">
+        <v>1063</v>
+      </c>
+      <c r="I438" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="J438" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="439" spans="1:10">
+      <c r="A439" s="11" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B439" s="16" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C439" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D439" s="14">
+        <v>552</v>
+      </c>
+      <c r="F439" s="16">
+        <v>2027</v>
+      </c>
+      <c r="G439" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="H439" s="11" t="s">
+        <v>949</v>
+      </c>
+      <c r="I439" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="J439" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10">
+      <c r="A440" s="28" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B440" s="12" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C440" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D440" s="14">
+        <v>500.5</v>
+      </c>
+      <c r="F440" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G440" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="H440" s="12" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I440" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J440" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="441" spans="1:10">
+      <c r="A441" s="12" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B441" s="6" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C441" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D441" s="14">
+        <v>253</v>
+      </c>
+      <c r="F441" s="32">
+        <v>2027</v>
+      </c>
+      <c r="G441" s="12" t="s">
+        <v>980</v>
+      </c>
+      <c r="H441" s="11" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I441" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J441" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="442" ht="26.4" spans="1:10">
+      <c r="A442" s="18" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B442" s="16" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C442" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="D442" s="14">
+        <v>466</v>
+      </c>
+      <c r="F442" s="32">
         <v>2028</v>
       </c>
-      <c r="G437" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="H437" s="11" t="s">
-        <v>1062</v>
-      </c>
-      <c r="I437" s="1" t="s">
+      <c r="G442" s="12" t="s">
+        <v>980</v>
+      </c>
+      <c r="H442" s="11" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I442" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J437" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="438" ht="15" spans="1:10">
-      <c r="A438" s="31" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B438" s="12" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C438" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D438" s="14">
-        <v>50</v>
-      </c>
-      <c r="F438" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G438" s="12"/>
-      <c r="H438" s="12" t="s">
-        <v>1065</v>
-      </c>
-      <c r="I438" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J438" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="439" ht="15" spans="1:10">
-      <c r="A439" s="31" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B439" s="12" t="s">
-        <v>1067</v>
-      </c>
-      <c r="C439" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D439" s="14">
-        <v>50</v>
-      </c>
-      <c r="F439" s="15">
-        <v>2026</v>
-      </c>
-      <c r="G439" s="12"/>
-      <c r="H439" s="12" t="s">
-        <v>1065</v>
-      </c>
-      <c r="I439" s="10" t="s">
-        <v>963</v>
-      </c>
-      <c r="J439" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="440" spans="1:10">
-      <c r="A440" s="12" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B440" s="12" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C440" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D440" s="14">
-        <v>100</v>
-      </c>
-      <c r="F440" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G440" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H440" s="12" t="s">
-        <v>1065</v>
-      </c>
-      <c r="I440" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J440" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="441" spans="1:10">
-      <c r="A441" s="16" t="s">
-        <v>1070</v>
-      </c>
-      <c r="B441" s="12" t="s">
-        <v>1067</v>
-      </c>
-      <c r="C441" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D441" s="14">
-        <v>50</v>
-      </c>
-      <c r="F441" s="15">
-        <v>2026</v>
-      </c>
-      <c r="G441" s="16"/>
-      <c r="H441" s="16" t="s">
-        <v>1065</v>
-      </c>
-      <c r="I441" s="10" t="s">
-        <v>963</v>
-      </c>
-      <c r="J441" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="442" spans="1:10">
-      <c r="A442" s="21" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B442" s="32" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C442" s="1" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D442" s="23">
-        <v>241</v>
-      </c>
-      <c r="F442" s="32">
-        <v>2026</v>
-      </c>
-      <c r="G442" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H442" s="11" t="s">
-        <v>1052</v>
-      </c>
-      <c r="I442" s="10" t="s">
-        <v>959</v>
-      </c>
       <c r="J442" s="1" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="443" ht="26.4" spans="1:10">
-      <c r="A443" s="11" t="s">
+    <row r="443" spans="1:10">
+      <c r="A443" s="18" t="s">
         <v>1074</v>
       </c>
       <c r="B443" s="16" t="s">
         <v>1075</v>
       </c>
-      <c r="C443" s="1" t="s">
-        <v>133</v>
+      <c r="C443" s="13" t="s">
+        <v>346</v>
       </c>
       <c r="D443" s="14">
-        <v>552</v>
-      </c>
-      <c r="F443" s="16">
-        <v>2026</v>
+        <v>264</v>
+      </c>
+      <c r="F443" s="32">
+        <v>2028</v>
       </c>
       <c r="G443" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H443" s="11" t="s">
-        <v>1076</v>
-      </c>
-      <c r="I443" s="10" t="s">
-        <v>963</v>
+        <v>980</v>
+      </c>
+      <c r="H443" s="12" t="s">
+        <v>949</v>
+      </c>
+      <c r="I443" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="J443" s="1" t="s">
         <v>574</v>
@@ -15282,86 +14977,86 @@
     </row>
     <row r="444" spans="1:10">
       <c r="A444" s="11" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B444" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B444" s="16" t="s">
+      <c r="C444" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D444" s="14">
+        <v>1670.5</v>
+      </c>
+      <c r="F444" s="12">
+        <v>2027</v>
+      </c>
+      <c r="G444" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="H444" s="12" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I444" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="J444" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="445" spans="1:10">
+      <c r="A445" s="18" t="s">
         <v>1078</v>
       </c>
-      <c r="C444" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D444" s="14">
-        <v>552</v>
-      </c>
-      <c r="F444" s="16">
+      <c r="B445" s="16" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C445" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D445" s="14">
+        <v>144</v>
+      </c>
+      <c r="F445" s="16">
         <v>2027</v>
       </c>
-      <c r="G444" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H444" s="11" t="s">
-        <v>962</v>
-      </c>
-      <c r="I444" s="10" t="s">
-        <v>963</v>
-      </c>
-      <c r="J444" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="445" spans="1:10">
-      <c r="A445" s="28" t="s">
-        <v>1079</v>
-      </c>
-      <c r="B445" s="12" t="s">
+      <c r="G445" s="12" t="s">
+        <v>980</v>
+      </c>
+      <c r="H445" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="I445" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J445" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="446" spans="1:10">
+      <c r="A446" s="11" t="s">
         <v>1080</v>
       </c>
-      <c r="C445" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D445" s="14">
-        <v>500.5</v>
-      </c>
-      <c r="F445" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G445" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H445" s="12" t="s">
-        <v>1052</v>
-      </c>
-      <c r="I445" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J445" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="446" spans="1:10">
-      <c r="A446" s="12" t="s">
+      <c r="B446" s="12" t="s">
         <v>1081</v>
       </c>
-      <c r="B446" s="6" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C446" s="1" t="s">
-        <v>133</v>
+      <c r="C446" s="13" t="s">
+        <v>12</v>
       </c>
       <c r="D446" s="14">
-        <v>253</v>
-      </c>
-      <c r="F446" s="32">
-        <v>2027</v>
+        <v>78</v>
+      </c>
+      <c r="F446" s="15" t="s">
+        <v>943</v>
       </c>
       <c r="G446" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="H446" s="11" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I446" s="1" t="s">
-        <v>93</v>
+        <v>944</v>
+      </c>
+      <c r="H446" s="12" t="s">
+        <v>984</v>
+      </c>
+      <c r="I446" s="10" t="s">
+        <v>946</v>
       </c>
       <c r="J446" s="1" t="s">
         <v>574</v>
@@ -15369,25 +15064,25 @@
     </row>
     <row r="447" ht="26.4" spans="1:10">
       <c r="A447" s="18" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B447" s="11" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C447" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="D447" s="14">
+        <v>24</v>
+      </c>
+      <c r="F447" s="33">
+        <v>2028</v>
+      </c>
+      <c r="G447" s="12" t="s">
+        <v>980</v>
+      </c>
+      <c r="H447" s="11" t="s">
         <v>1084</v>
-      </c>
-      <c r="B447" s="16" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C447" s="13" t="s">
-        <v>346</v>
-      </c>
-      <c r="D447" s="14">
-        <v>466</v>
-      </c>
-      <c r="F447" s="32">
-        <v>2028</v>
-      </c>
-      <c r="G447" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="H447" s="11" t="s">
-        <v>1086</v>
       </c>
       <c r="I447" s="1" t="s">
         <v>93</v>
@@ -15398,57 +15093,57 @@
     </row>
     <row r="448" spans="1:10">
       <c r="A448" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B448" s="12" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C448" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="D448" s="14">
+        <v>232</v>
+      </c>
+      <c r="F448" s="16">
+        <v>2027</v>
+      </c>
+      <c r="G448" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="H448" s="12" t="s">
+        <v>949</v>
+      </c>
+      <c r="I448" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="J448" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="449" spans="1:10">
+      <c r="A449" s="18" t="s">
         <v>1087</v>
       </c>
-      <c r="B448" s="16" t="s">
+      <c r="B449" s="12" t="s">
         <v>1088</v>
       </c>
-      <c r="C448" s="13" t="s">
-        <v>346</v>
-      </c>
-      <c r="D448" s="14">
-        <v>264</v>
-      </c>
-      <c r="F448" s="32">
+      <c r="C449" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="D449" s="14">
+        <v>64</v>
+      </c>
+      <c r="F449" s="33">
         <v>2028</v>
       </c>
-      <c r="G448" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="H448" s="12" t="s">
-        <v>962</v>
-      </c>
-      <c r="I448" s="1" t="s">
+      <c r="G449" s="12" t="s">
+        <v>980</v>
+      </c>
+      <c r="H449" s="24" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I449" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="J448" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="449" spans="1:10">
-      <c r="A449" s="11" t="s">
-        <v>1089</v>
-      </c>
-      <c r="B449" s="12" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C449" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="D449" s="14">
-        <v>1670.5</v>
-      </c>
-      <c r="F449" s="12">
-        <v>2027</v>
-      </c>
-      <c r="G449" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H449" s="12" t="s">
-        <v>1052</v>
-      </c>
-      <c r="I449" s="10" t="s">
-        <v>963</v>
       </c>
       <c r="J449" s="1" t="s">
         <v>574</v>
@@ -15456,25 +15151,25 @@
     </row>
     <row r="450" spans="1:10">
       <c r="A450" s="18" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B450" s="16" t="s">
         <v>1091</v>
       </c>
-      <c r="B450" s="16" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C450" s="13" t="s">
-        <v>12</v>
+      <c r="C450" s="20" t="s">
+        <v>660</v>
       </c>
       <c r="D450" s="14">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="F450" s="16">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="G450" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="H450" s="11" t="s">
-        <v>972</v>
+        <v>980</v>
+      </c>
+      <c r="H450" s="12" t="s">
+        <v>959</v>
       </c>
       <c r="I450" s="1" t="s">
         <v>93</v>
@@ -15484,87 +15179,87 @@
       </c>
     </row>
     <row r="451" spans="1:10">
-      <c r="A451" s="11" t="s">
+      <c r="A451" s="18" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B451" s="34" t="s">
         <v>1093</v>
       </c>
-      <c r="B451" s="12" t="s">
+      <c r="C451" s="20" t="s">
         <v>1094</v>
       </c>
-      <c r="C451" s="13" t="s">
-        <v>12</v>
-      </c>
       <c r="D451" s="14">
-        <v>78</v>
-      </c>
-      <c r="F451" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G451" s="12" t="s">
-        <v>957</v>
+        <v>118.8</v>
+      </c>
+      <c r="F451" s="16">
+        <v>2028</v>
+      </c>
+      <c r="G451" s="9" t="s">
+        <v>980</v>
       </c>
       <c r="H451" s="12" t="s">
-        <v>997</v>
-      </c>
-      <c r="I451" s="10" t="s">
         <v>959</v>
       </c>
+      <c r="I451" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="J451" s="1" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="452" ht="26.4" spans="1:10">
-      <c r="A452" s="18" t="s">
+    <row r="452" spans="1:10">
+      <c r="A452" s="16" t="s">
         <v>1095</v>
       </c>
-      <c r="B452" s="11" t="s">
+      <c r="B452" s="35" t="s">
         <v>1096</v>
       </c>
       <c r="C452" s="20" t="s">
-        <v>438</v>
+        <v>1094</v>
       </c>
       <c r="D452" s="14">
-        <v>24</v>
-      </c>
-      <c r="F452" s="33">
+        <v>50.6</v>
+      </c>
+      <c r="F452" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G452" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="H452" s="12" t="s">
+        <v>1097</v>
+      </c>
+      <c r="I452" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J452" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="453" spans="1:10">
+      <c r="A453" s="36" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B453" s="34" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C453" s="20" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D453" s="14">
+        <v>120</v>
+      </c>
+      <c r="F453" s="16">
         <v>2028</v>
       </c>
-      <c r="G452" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="H452" s="11" t="s">
-        <v>1097</v>
-      </c>
-      <c r="I452" s="1" t="s">
+      <c r="G453" s="12" t="s">
+        <v>980</v>
+      </c>
+      <c r="H453" s="12" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I453" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="J452" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="453" spans="1:10">
-      <c r="A453" s="18" t="s">
-        <v>1098</v>
-      </c>
-      <c r="B453" s="12" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C453" s="20" t="s">
-        <v>438</v>
-      </c>
-      <c r="D453" s="14">
-        <v>232</v>
-      </c>
-      <c r="F453" s="16">
-        <v>2027</v>
-      </c>
-      <c r="G453" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H453" s="12" t="s">
-        <v>962</v>
-      </c>
-      <c r="I453" s="10" t="s">
-        <v>963</v>
       </c>
       <c r="J453" s="1" t="s">
         <v>574</v>
@@ -15572,25 +15267,25 @@
     </row>
     <row r="454" spans="1:10">
       <c r="A454" s="18" t="s">
-        <v>1100</v>
-      </c>
-      <c r="B454" s="12" t="s">
         <v>1101</v>
       </c>
+      <c r="B454" s="34" t="s">
+        <v>1102</v>
+      </c>
       <c r="C454" s="20" t="s">
-        <v>438</v>
+        <v>786</v>
       </c>
       <c r="D454" s="14">
-        <v>64</v>
-      </c>
-      <c r="F454" s="33">
+        <v>124</v>
+      </c>
+      <c r="F454" s="16">
         <v>2028</v>
       </c>
       <c r="G454" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="H454" s="24" t="s">
-        <v>1102</v>
+        <v>980</v>
+      </c>
+      <c r="H454" s="12" t="s">
+        <v>1039</v>
       </c>
       <c r="I454" s="1" t="s">
         <v>93</v>
@@ -15599,27 +15294,27 @@
         <v>574</v>
       </c>
     </row>
-    <row r="455" spans="1:10">
+    <row r="455" ht="26.4" spans="1:10">
       <c r="A455" s="18" t="s">
         <v>1103</v>
       </c>
-      <c r="B455" s="16" t="s">
+      <c r="B455" s="34" t="s">
         <v>1104</v>
       </c>
       <c r="C455" s="20" t="s">
-        <v>673</v>
+        <v>391</v>
       </c>
       <c r="D455" s="14">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="F455" s="16">
-        <v>2028</v>
-      </c>
-      <c r="G455" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="H455" s="12" t="s">
-        <v>972</v>
+        <v>2027</v>
+      </c>
+      <c r="G455" s="34" t="s">
+        <v>980</v>
+      </c>
+      <c r="H455" s="11" t="s">
+        <v>1105</v>
       </c>
       <c r="I455" s="1" t="s">
         <v>93</v>
@@ -15629,259 +15324,259 @@
       </c>
     </row>
     <row r="456" spans="1:10">
-      <c r="A456" s="18" t="s">
-        <v>1105</v>
-      </c>
-      <c r="B456" s="34" t="s">
+      <c r="A456" s="28" t="s">
         <v>1106</v>
       </c>
+      <c r="B456" s="12" t="s">
+        <v>1107</v>
+      </c>
       <c r="C456" s="20" t="s">
-        <v>1107</v>
+        <v>156</v>
       </c>
       <c r="D456" s="14">
-        <v>118.8</v>
-      </c>
-      <c r="F456" s="16">
+        <v>42.5</v>
+      </c>
+      <c r="F456" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G456" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="H456" s="12" t="s">
+        <v>1108</v>
+      </c>
+      <c r="I456" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J456" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="457" spans="1:10">
+      <c r="A457" s="29" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B457" s="12" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C457" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="D457" s="14">
+        <v>23.63</v>
+      </c>
+      <c r="F457" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G457" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="H457" s="12" t="s">
+        <v>1108</v>
+      </c>
+      <c r="I457" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J457" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="458" spans="1:10">
+      <c r="A458" s="12" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B458" s="12" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C458" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="D458" s="14">
+        <v>15.75</v>
+      </c>
+      <c r="F458" s="37">
         <v>2028</v>
       </c>
-      <c r="G456" s="9" t="s">
-        <v>993</v>
-      </c>
-      <c r="H456" s="12" t="s">
-        <v>972</v>
-      </c>
-      <c r="I456" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J456" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="457" spans="1:10">
-      <c r="A457" s="16" t="s">
+      <c r="G458" s="12"/>
+      <c r="H458" s="12" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I458" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="J458" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="459" spans="1:10">
+      <c r="A459" s="29" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B459" s="12" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C459" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="D459" s="14">
+        <v>40</v>
+      </c>
+      <c r="F459" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G459" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="H459" s="12" t="s">
         <v>1108</v>
       </c>
-      <c r="B457" s="35" t="s">
-        <v>1109</v>
-      </c>
-      <c r="C457" s="20" t="s">
-        <v>1107</v>
-      </c>
-      <c r="D457" s="14">
-        <v>50.6</v>
-      </c>
-      <c r="F457" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G457" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H457" s="12" t="s">
-        <v>1110</v>
-      </c>
-      <c r="I457" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J457" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="458" spans="1:10">
-      <c r="A458" s="36" t="s">
-        <v>1111</v>
-      </c>
-      <c r="B458" s="34" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C458" s="20" t="s">
-        <v>1113</v>
-      </c>
-      <c r="D458" s="14">
-        <v>120</v>
-      </c>
-      <c r="F458" s="16">
-        <v>2028</v>
-      </c>
-      <c r="G458" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="H458" s="12" t="s">
-        <v>1102</v>
-      </c>
-      <c r="I458" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J458" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="459" spans="1:10">
-      <c r="A459" s="18" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B459" s="34" t="s">
+      <c r="I459" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J459" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="460" spans="1:10">
+      <c r="A460" s="18" t="s">
         <v>1115</v>
       </c>
-      <c r="C459" s="20" t="s">
-        <v>799</v>
-      </c>
-      <c r="D459" s="14">
-        <v>124</v>
-      </c>
-      <c r="F459" s="16">
-        <v>2028</v>
-      </c>
-      <c r="G459" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="H459" s="12" t="s">
-        <v>1052</v>
-      </c>
-      <c r="I459" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J459" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="460" ht="26.4" spans="1:10">
-      <c r="A460" s="18" t="s">
+      <c r="B460" s="47" t="s">
         <v>1116</v>
       </c>
-      <c r="B460" s="34" t="s">
+      <c r="C460" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D460" s="14">
+        <v>132</v>
+      </c>
+      <c r="F460" s="12">
+        <v>2026</v>
+      </c>
+      <c r="G460" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="H460" s="11" t="s">
         <v>1117</v>
       </c>
-      <c r="C460" s="20" t="s">
-        <v>391</v>
-      </c>
-      <c r="D460" s="14">
-        <v>176</v>
-      </c>
-      <c r="F460" s="16">
-        <v>2027</v>
-      </c>
-      <c r="G460" s="34" t="s">
-        <v>993</v>
-      </c>
-      <c r="H460" s="11" t="s">
+      <c r="I460" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="J460" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="461" spans="1:10">
+      <c r="A461" s="39" t="s">
         <v>1118</v>
       </c>
-      <c r="I460" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J460" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="461" spans="1:10">
-      <c r="A461" s="28" t="s">
+      <c r="B461" s="12" t="s">
         <v>1119</v>
       </c>
-      <c r="B461" s="12" t="s">
+      <c r="C461" s="20" t="s">
         <v>1120</v>
       </c>
-      <c r="C461" s="20" t="s">
-        <v>156</v>
-      </c>
       <c r="D461" s="14">
-        <v>42.5</v>
+        <v>10</v>
       </c>
       <c r="F461" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G461" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H461" s="12" t="s">
+        <v>943</v>
+      </c>
+      <c r="G461" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="H461" s="11" t="s">
         <v>1121</v>
       </c>
       <c r="I461" s="10" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="J461" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="462" spans="1:10">
-      <c r="A462" s="29" t="s">
+      <c r="A462" s="31" t="s">
         <v>1122</v>
       </c>
       <c r="B462" s="12" t="s">
         <v>1123</v>
       </c>
       <c r="C462" s="20" t="s">
-        <v>156</v>
+        <v>1120</v>
       </c>
       <c r="D462" s="14">
-        <v>23.63</v>
+        <v>50</v>
       </c>
       <c r="F462" s="15" t="s">
-        <v>956</v>
+        <v>943</v>
       </c>
       <c r="G462" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H462" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="H462" s="16" t="s">
         <v>1121</v>
       </c>
       <c r="I462" s="10" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="J462" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="463" spans="1:10">
-      <c r="A463" s="12" t="s">
+      <c r="A463" s="18" t="s">
         <v>1124</v>
       </c>
       <c r="B463" s="12" t="s">
         <v>1125</v>
       </c>
       <c r="C463" s="20" t="s">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="D463" s="14">
-        <v>15.75</v>
-      </c>
-      <c r="F463" s="37">
-        <v>2028</v>
-      </c>
-      <c r="G463" s="12"/>
+        <v>210</v>
+      </c>
+      <c r="F463" s="12">
+        <v>2027</v>
+      </c>
+      <c r="G463" s="16" t="s">
+        <v>944</v>
+      </c>
       <c r="H463" s="12" t="s">
-        <v>1041</v>
+        <v>949</v>
       </c>
       <c r="I463" s="10" t="s">
-        <v>963</v>
+        <v>950</v>
       </c>
       <c r="J463" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="464" spans="1:10">
-      <c r="A464" s="29" t="s">
+      <c r="A464" s="18" t="s">
         <v>1126</v>
       </c>
       <c r="B464" s="12" t="s">
         <v>1127</v>
       </c>
       <c r="C464" s="20" t="s">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="D464" s="14">
-        <v>40</v>
-      </c>
-      <c r="F464" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G464" s="12" t="s">
-        <v>957</v>
+        <v>420</v>
+      </c>
+      <c r="F464" s="12">
+        <v>2027</v>
+      </c>
+      <c r="G464" s="16" t="s">
+        <v>944</v>
       </c>
       <c r="H464" s="12" t="s">
-        <v>1121</v>
+        <v>949</v>
       </c>
       <c r="I464" s="10" t="s">
-        <v>959</v>
+        <v>950</v>
       </c>
       <c r="J464" s="1" t="s">
         <v>574</v>
@@ -15891,290 +15586,481 @@
       <c r="A465" s="18" t="s">
         <v>1128</v>
       </c>
-      <c r="B465" s="44" t="s">
+      <c r="B465" s="12" t="s">
         <v>1129</v>
       </c>
       <c r="C465" s="20" t="s">
-        <v>18</v>
+        <v>253</v>
       </c>
       <c r="D465" s="14">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="F465" s="12">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="G465" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H465" s="11" t="s">
+        <v>944</v>
+      </c>
+      <c r="H465" s="12" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I465" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="J465" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="466" spans="1:10">
+      <c r="A466" s="28" t="s">
         <v>1130</v>
       </c>
-      <c r="I465" s="10" t="s">
-        <v>963</v>
-      </c>
-      <c r="J465" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="466" spans="1:10">
-      <c r="A466" s="39" t="s">
+      <c r="B466" s="21" t="s">
         <v>1131</v>
       </c>
-      <c r="B466" s="12" t="s">
+      <c r="C466" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="D466" s="14">
+        <v>70</v>
+      </c>
+      <c r="F466" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G466" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="H466" s="12" t="s">
+        <v>1121</v>
+      </c>
+      <c r="I466" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J466" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="467" spans="1:10">
+      <c r="A467" s="29" t="s">
         <v>1132</v>
       </c>
-      <c r="C466" s="20" t="s">
+      <c r="B467" s="21" t="s">
         <v>1133</v>
       </c>
-      <c r="D466" s="14">
-        <v>10</v>
-      </c>
-      <c r="F466" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G466" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H466" s="11" t="s">
+      <c r="C467" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="D467" s="14">
+        <v>90</v>
+      </c>
+      <c r="F467" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G467" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="H467" s="12" t="s">
+        <v>1121</v>
+      </c>
+      <c r="I467" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J467" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="468" spans="1:10">
+      <c r="A468" s="28" t="s">
         <v>1134</v>
       </c>
-      <c r="I466" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J466" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="467" spans="1:10">
-      <c r="A467" s="31" t="s">
+      <c r="B468" s="12" t="s">
         <v>1135</v>
       </c>
-      <c r="B467" s="12" t="s">
+      <c r="C468" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D468" s="14">
+        <v>10.5</v>
+      </c>
+      <c r="F468" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G468" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="H468" s="12" t="s">
         <v>1136</v>
       </c>
-      <c r="C467" s="20" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D467" s="14">
-        <v>50</v>
-      </c>
-      <c r="F467" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G467" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H467" s="16" t="s">
-        <v>1134</v>
-      </c>
-      <c r="I467" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J467" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="468" spans="1:10">
-      <c r="A468" s="18" t="s">
+      <c r="I468" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J468" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="469" spans="1:10">
+      <c r="A469" s="40" t="s">
         <v>1137</v>
       </c>
-      <c r="B468" s="12" t="s">
+      <c r="B469" s="16" t="s">
         <v>1138</v>
       </c>
-      <c r="C468" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D468" s="14">
-        <v>210</v>
-      </c>
-      <c r="F468" s="12">
-        <v>2027</v>
-      </c>
-      <c r="G468" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H468" s="12" t="s">
-        <v>962</v>
-      </c>
-      <c r="I468" s="10" t="s">
-        <v>963</v>
-      </c>
-      <c r="J468" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="469" spans="1:10">
-      <c r="A469" s="18" t="s">
+      <c r="C469" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D469" s="41">
+        <v>10.5</v>
+      </c>
+      <c r="E469" s="42"/>
+      <c r="F469" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="G469" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="H469" s="16" t="s">
+        <v>1136</v>
+      </c>
+      <c r="I469" s="43" t="s">
+        <v>946</v>
+      </c>
+      <c r="J469" s="42" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="470" spans="1:10">
+      <c r="A470" s="6" t="s">
         <v>1139</v>
       </c>
-      <c r="B469" s="12" t="s">
+      <c r="B470" s="6" t="s">
         <v>1140</v>
       </c>
-      <c r="C469" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D469" s="14">
-        <v>420</v>
-      </c>
-      <c r="F469" s="12">
-        <v>2027</v>
-      </c>
-      <c r="G469" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H469" s="12" t="s">
-        <v>962</v>
-      </c>
-      <c r="I469" s="10" t="s">
-        <v>963</v>
-      </c>
-      <c r="J469" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="470" spans="1:10">
-      <c r="A470" s="18" t="s">
+      <c r="C470" s="1" t="s">
         <v>1141</v>
       </c>
-      <c r="B470" s="12" t="s">
+      <c r="D470" s="44">
+        <v>3200</v>
+      </c>
+      <c r="E470" s="1"/>
+      <c r="F470" s="1"/>
+      <c r="G470" s="1"/>
+      <c r="H470" s="1"/>
+      <c r="I470" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J470" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="471" spans="1:10">
+      <c r="A471" s="6" t="s">
         <v>1142</v>
       </c>
-      <c r="C470" s="20" t="s">
-        <v>253</v>
-      </c>
-      <c r="D470" s="14">
-        <v>75</v>
-      </c>
-      <c r="F470" s="12">
-        <v>2027</v>
-      </c>
-      <c r="G470" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H470" s="12" t="s">
-        <v>1052</v>
-      </c>
-      <c r="I470" s="10" t="s">
-        <v>963</v>
-      </c>
-      <c r="J470" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="471" spans="1:10">
-      <c r="A471" s="28" t="s">
+      <c r="B471" s="45" t="s">
         <v>1143</v>
       </c>
-      <c r="B471" s="21" t="s">
+      <c r="C471" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D471" s="44">
+        <v>200</v>
+      </c>
+      <c r="E471" s="1"/>
+      <c r="F471" s="1"/>
+      <c r="G471" s="1"/>
+      <c r="H471" s="1"/>
+      <c r="I471" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J471" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="472" spans="1:10">
+      <c r="A472" s="6" t="s">
         <v>1144</v>
       </c>
-      <c r="C471" s="20" t="s">
-        <v>253</v>
-      </c>
-      <c r="D471" s="14">
-        <v>70</v>
-      </c>
-      <c r="F471" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G471" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H471" s="12" t="s">
-        <v>1134</v>
-      </c>
-      <c r="I471" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J471" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="472" spans="1:10">
-      <c r="A472" s="29" t="s">
+      <c r="B472" s="45" t="s">
         <v>1145</v>
       </c>
-      <c r="B472" s="21" t="s">
+      <c r="C472" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D472" s="44">
+        <v>140</v>
+      </c>
+      <c r="E472" s="1"/>
+      <c r="F472" s="1"/>
+      <c r="G472" s="1"/>
+      <c r="H472" s="1"/>
+      <c r="I472" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J472" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="473" spans="1:10">
+      <c r="A473" s="6" t="s">
         <v>1146</v>
       </c>
-      <c r="C472" s="20" t="s">
-        <v>253</v>
-      </c>
-      <c r="D472" s="14">
-        <v>90</v>
-      </c>
-      <c r="F472" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G472" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H472" s="12" t="s">
-        <v>1134</v>
-      </c>
-      <c r="I472" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J472" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="473" spans="1:10">
-      <c r="A473" s="28" t="s">
+      <c r="B473" s="45" t="s">
         <v>1147</v>
       </c>
-      <c r="B473" s="12" t="s">
+      <c r="C473" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D473" s="44">
+        <v>200</v>
+      </c>
+      <c r="E473" s="1"/>
+      <c r="F473" s="1"/>
+      <c r="G473" s="1"/>
+      <c r="H473" s="1"/>
+      <c r="I473" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J473" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="474" spans="1:10">
+      <c r="A474" s="6" t="s">
         <v>1148</v>
       </c>
-      <c r="C473" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D473" s="14">
-        <v>10.5</v>
-      </c>
-      <c r="F473" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G473" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="H473" s="12" t="s">
+      <c r="B474" s="45" t="s">
         <v>1149</v>
       </c>
-      <c r="I473" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="J473" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="474" spans="1:10">
-      <c r="A474" s="40" t="s">
+      <c r="C474" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D474" s="44">
+        <v>94</v>
+      </c>
+      <c r="E474" s="1"/>
+      <c r="F474" s="1"/>
+      <c r="G474" s="1"/>
+      <c r="H474" s="1"/>
+      <c r="I474" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J474" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="475" spans="1:10">
+      <c r="A475" s="6" t="s">
         <v>1150</v>
       </c>
-      <c r="B474" s="16" t="s">
+      <c r="B475" s="6" t="s">
         <v>1151</v>
       </c>
-      <c r="C474" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D474" s="41">
-        <v>10.5</v>
-      </c>
-      <c r="E474" s="42"/>
-      <c r="F474" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="G474" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="H474" s="16" t="s">
-        <v>1149</v>
-      </c>
-      <c r="I474" s="43" t="s">
-        <v>959</v>
-      </c>
-      <c r="J474" s="42" t="s">
+      <c r="C475" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D475" s="44">
+        <v>105</v>
+      </c>
+      <c r="E475" s="1"/>
+      <c r="F475" s="1"/>
+      <c r="G475" s="1"/>
+      <c r="H475" s="1"/>
+      <c r="I475" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J475" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="476" spans="1:10">
+      <c r="A476" s="6" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B476" s="6" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C476" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D476" s="44">
+        <v>500</v>
+      </c>
+      <c r="E476" s="1"/>
+      <c r="F476" s="1"/>
+      <c r="G476" s="1"/>
+      <c r="H476" s="1"/>
+      <c r="I476" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J476" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="477" spans="1:10">
+      <c r="A477" s="6" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B477" s="45" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C477" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D477" s="44">
+        <v>192</v>
+      </c>
+      <c r="E477" s="1"/>
+      <c r="F477" s="1"/>
+      <c r="G477" s="1"/>
+      <c r="H477" s="1"/>
+      <c r="I477" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J477" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="478" spans="1:10">
+      <c r="A478" s="6" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B478" s="45" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C478" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D478" s="44">
+        <v>192</v>
+      </c>
+      <c r="E478" s="1"/>
+      <c r="F478" s="1"/>
+      <c r="G478" s="1"/>
+      <c r="H478" s="1"/>
+      <c r="I478" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J478" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="479" spans="1:10">
+      <c r="A479" s="6" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B479" s="45" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C479" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D479" s="44">
+        <v>192</v>
+      </c>
+      <c r="E479" s="1"/>
+      <c r="F479" s="1"/>
+      <c r="G479" s="1"/>
+      <c r="H479" s="1"/>
+      <c r="I479" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J479" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="480" spans="1:10">
+      <c r="A480" s="6" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B480" s="45" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C480" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D480" s="44">
+        <v>192</v>
+      </c>
+      <c r="E480" s="1"/>
+      <c r="F480" s="1"/>
+      <c r="G480" s="1"/>
+      <c r="H480" s="1"/>
+      <c r="I480" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J480" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="481" spans="1:10">
+      <c r="A481" s="6" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B481" s="6" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C481" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D481" s="44">
+        <v>100</v>
+      </c>
+      <c r="E481" s="1"/>
+      <c r="F481" s="1"/>
+      <c r="G481" s="1"/>
+      <c r="H481" s="1"/>
+      <c r="I481" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J481" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="482" spans="1:10">
+      <c r="A482" s="6" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B482" s="45" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C482" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D482" s="44">
+        <v>200</v>
+      </c>
+      <c r="E482" s="1"/>
+      <c r="F482" s="1"/>
+      <c r="G482" s="1"/>
+      <c r="H482" s="1"/>
+      <c r="I482" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J482" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="483" spans="1:10">
+      <c r="A483" s="6" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B483" s="46" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C483" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D483" s="44">
+        <v>200</v>
+      </c>
+      <c r="E483" s="1"/>
+      <c r="F483" s="1"/>
+      <c r="G483" s="1"/>
+      <c r="H483" s="1"/>
+      <c r="I483" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J483" s="1" t="s">
         <v>574</v>
       </c>
     </row>
